--- a/engine/amoc_study/AMOC_Valuation_Model_03092026_public.xlsx
+++ b/engine/amoc_study/AMOC_Valuation_Model_03092026_public.xlsx
@@ -35973,7 +35973,7 @@
     <row r="23" ht="44" customHeight="1">
       <c r="A23" s="19" t="inlineStr">
         <is>
-          <t>The bear and bull columns of each lens are the blue cells here and the only pasted figures on the sheet: each is a complete re-run of the model at that scenario, computed in compute.py and reproduced in formulas on the Sensitivity sheet. The weighted row is a live formula across them, because the defect being closed was a sheet that labelled a row weighted and then took the minimum and maximum across four lenses.</t>
+          <t>The bear and bull columns of each lens are the blue cells here and the only pasted figures on the sheet: each is a complete re-run of the model at that scenario, computed in compute.py and reproduced in formulas on the Sensitivity sheet. The central row is a live formula across them, because the defect being closed was a sheet that labelled a row weighted and then took the minimum and maximum across four lenses.</t>
         </is>
       </c>
     </row>

--- a/engine/amoc_study/AMOC_Valuation_Model_03092026_public.xlsx
+++ b/engine/amoc_study/AMOC_Valuation_Model_03092026_public.xlsx
@@ -3386,23 +3386,23 @@
         </is>
       </c>
       <c r="C62" s="18">
-        <f>C52*('Segments'!$D$27*C51*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*C50+0.4357405005*C50+0.0330936548*C51+0.0328406739))+C53*('Segments'!$D$28*C51*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*C50+0.4357405005*C50+0.0330936548*C51+0.0328406739))+C54*('Segments'!$D$29*C51*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*C50+0.4357405005*C50+0.0330936548*C51+0.0328406739))+C55*('Segments'!$D$30*C51*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*C50+0.4357405005*C50+0.0330936548*C51+0.0328406739))+C56*('Segments'!$D$31*C51*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*C50+0.4357405005*C50+0.0330936548*C51+0.0328406739))+C57*('Segments'!$D$32*C51*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*C50+0.4357405005*C50+0.0330936548*C51+0.0328406739))+C58*('Segments'!$D$33*C51*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*C50+0.4357405005*C50+0.0330936548*C51+0.0328406739))+C59*('Segments'!$D$34*C51*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*C50+0.4357405005*C50+0.0330936548*C51+0.0328406739))</f>
+        <f>C52*('Segments'!$D$27*C51*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*C51+0.4357405005*C51+0.0330936548*C51+0.0328406739))+C53*('Segments'!$D$28*C51*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*C51+0.4357405005*C51+0.0330936548*C51+0.0328406739))+C54*('Segments'!$D$29*C51*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*C51+0.4357405005*C51+0.0330936548*C51+0.0328406739))+C55*('Segments'!$D$30*C51*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*C51+0.4357405005*C51+0.0330936548*C51+0.0328406739))+C56*('Segments'!$D$31*C51*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*C51+0.4357405005*C51+0.0330936548*C51+0.0328406739))+C57*('Segments'!$D$32*C51*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*C51+0.4357405005*C51+0.0330936548*C51+0.0328406739))+C58*('Segments'!$D$33*C51*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*C51+0.4357405005*C51+0.0330936548*C51+0.0328406739))+C59*('Segments'!$D$34*C51*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*C51+0.4357405005*C51+0.0330936548*C51+0.0328406739))</f>
         <v/>
       </c>
       <c r="D62" s="18">
-        <f>D52*('Segments'!$D$27*D51*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*D50+0.4357405005*D50+0.0330936548*D51+0.0328406739))+D53*('Segments'!$D$28*D51*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*D50+0.4357405005*D50+0.0330936548*D51+0.0328406739))+D54*('Segments'!$D$29*D51*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*D50+0.4357405005*D50+0.0330936548*D51+0.0328406739))+D55*('Segments'!$D$30*D51*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*D50+0.4357405005*D50+0.0330936548*D51+0.0328406739))+D56*('Segments'!$D$31*D51*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*D50+0.4357405005*D50+0.0330936548*D51+0.0328406739))+D57*('Segments'!$D$32*D51*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*D50+0.4357405005*D50+0.0330936548*D51+0.0328406739))+D58*('Segments'!$D$33*D51*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*D50+0.4357405005*D50+0.0330936548*D51+0.0328406739))+D59*('Segments'!$D$34*D51*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*D50+0.4357405005*D50+0.0330936548*D51+0.0328406739))</f>
+        <f>D52*('Segments'!$D$27*D51*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*D51+0.4357405005*D51+0.0330936548*D51+0.0328406739))+D53*('Segments'!$D$28*D51*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*D51+0.4357405005*D51+0.0330936548*D51+0.0328406739))+D54*('Segments'!$D$29*D51*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*D51+0.4357405005*D51+0.0330936548*D51+0.0328406739))+D55*('Segments'!$D$30*D51*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*D51+0.4357405005*D51+0.0330936548*D51+0.0328406739))+D56*('Segments'!$D$31*D51*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*D51+0.4357405005*D51+0.0330936548*D51+0.0328406739))+D57*('Segments'!$D$32*D51*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*D51+0.4357405005*D51+0.0330936548*D51+0.0328406739))+D58*('Segments'!$D$33*D51*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*D51+0.4357405005*D51+0.0330936548*D51+0.0328406739))+D59*('Segments'!$D$34*D51*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*D51+0.4357405005*D51+0.0330936548*D51+0.0328406739))</f>
         <v/>
       </c>
       <c r="E62" s="18">
-        <f>E52*('Segments'!$D$27*E51*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*E50+0.4357405005*E50+0.0330936548*E51+0.0328406739))+E53*('Segments'!$D$28*E51*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*E50+0.4357405005*E50+0.0330936548*E51+0.0328406739))+E54*('Segments'!$D$29*E51*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*E50+0.4357405005*E50+0.0330936548*E51+0.0328406739))+E55*('Segments'!$D$30*E51*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*E50+0.4357405005*E50+0.0330936548*E51+0.0328406739))+E56*('Segments'!$D$31*E51*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*E50+0.4357405005*E50+0.0330936548*E51+0.0328406739))+E57*('Segments'!$D$32*E51*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*E50+0.4357405005*E50+0.0330936548*E51+0.0328406739))+E58*('Segments'!$D$33*E51*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*E50+0.4357405005*E50+0.0330936548*E51+0.0328406739))+E59*('Segments'!$D$34*E51*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*E50+0.4357405005*E50+0.0330936548*E51+0.0328406739))</f>
+        <f>E52*('Segments'!$D$27*E51*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*E51+0.4357405005*E51+0.0330936548*E51+0.0328406739))+E53*('Segments'!$D$28*E51*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*E51+0.4357405005*E51+0.0330936548*E51+0.0328406739))+E54*('Segments'!$D$29*E51*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*E51+0.4357405005*E51+0.0330936548*E51+0.0328406739))+E55*('Segments'!$D$30*E51*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*E51+0.4357405005*E51+0.0330936548*E51+0.0328406739))+E56*('Segments'!$D$31*E51*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*E51+0.4357405005*E51+0.0330936548*E51+0.0328406739))+E57*('Segments'!$D$32*E51*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*E51+0.4357405005*E51+0.0330936548*E51+0.0328406739))+E58*('Segments'!$D$33*E51*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*E51+0.4357405005*E51+0.0330936548*E51+0.0328406739))+E59*('Segments'!$D$34*E51*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*E51+0.4357405005*E51+0.0330936548*E51+0.0328406739))</f>
         <v/>
       </c>
       <c r="F62" s="18">
-        <f>F52*('Segments'!$D$27*F51*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*F50+0.4357405005*F50+0.0330936548*F51+0.0328406739))+F53*('Segments'!$D$28*F51*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*F50+0.4357405005*F50+0.0330936548*F51+0.0328406739))+F54*('Segments'!$D$29*F51*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*F50+0.4357405005*F50+0.0330936548*F51+0.0328406739))+F55*('Segments'!$D$30*F51*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*F50+0.4357405005*F50+0.0330936548*F51+0.0328406739))+F56*('Segments'!$D$31*F51*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*F50+0.4357405005*F50+0.0330936548*F51+0.0328406739))+F57*('Segments'!$D$32*F51*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*F50+0.4357405005*F50+0.0330936548*F51+0.0328406739))+F58*('Segments'!$D$33*F51*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*F50+0.4357405005*F50+0.0330936548*F51+0.0328406739))+F59*('Segments'!$D$34*F51*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*F50+0.4357405005*F50+0.0330936548*F51+0.0328406739))</f>
+        <f>F52*('Segments'!$D$27*F51*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*F51+0.4357405005*F51+0.0330936548*F51+0.0328406739))+F53*('Segments'!$D$28*F51*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*F51+0.4357405005*F51+0.0330936548*F51+0.0328406739))+F54*('Segments'!$D$29*F51*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*F51+0.4357405005*F51+0.0330936548*F51+0.0328406739))+F55*('Segments'!$D$30*F51*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*F51+0.4357405005*F51+0.0330936548*F51+0.0328406739))+F56*('Segments'!$D$31*F51*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*F51+0.4357405005*F51+0.0330936548*F51+0.0328406739))+F57*('Segments'!$D$32*F51*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*F51+0.4357405005*F51+0.0330936548*F51+0.0328406739))+F58*('Segments'!$D$33*F51*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*F51+0.4357405005*F51+0.0330936548*F51+0.0328406739))+F59*('Segments'!$D$34*F51*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*F51+0.4357405005*F51+0.0330936548*F51+0.0328406739))</f>
         <v/>
       </c>
       <c r="G62" s="18">
-        <f>G52*('Segments'!$D$27*G51*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*G50+0.4357405005*G50+0.0330936548*G51+0.0328406739))+G53*('Segments'!$D$28*G51*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*G50+0.4357405005*G50+0.0330936548*G51+0.0328406739))+G54*('Segments'!$D$29*G51*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*G50+0.4357405005*G50+0.0330936548*G51+0.0328406739))+G55*('Segments'!$D$30*G51*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*G50+0.4357405005*G50+0.0330936548*G51+0.0328406739))+G56*('Segments'!$D$31*G51*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*G50+0.4357405005*G50+0.0330936548*G51+0.0328406739))+G57*('Segments'!$D$32*G51*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*G50+0.4357405005*G50+0.0330936548*G51+0.0328406739))+G58*('Segments'!$D$33*G51*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*G50+0.4357405005*G50+0.0330936548*G51+0.0328406739))+G59*('Segments'!$D$34*G51*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*G50+0.4357405005*G50+0.0330936548*G51+0.0328406739))</f>
+        <f>G52*('Segments'!$D$27*G51*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*G51+0.4357405005*G51+0.0330936548*G51+0.0328406739))+G53*('Segments'!$D$28*G51*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*G51+0.4357405005*G51+0.0330936548*G51+0.0328406739))+G54*('Segments'!$D$29*G51*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*G51+0.4357405005*G51+0.0330936548*G51+0.0328406739))+G55*('Segments'!$D$30*G51*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*G51+0.4357405005*G51+0.0330936548*G51+0.0328406739))+G56*('Segments'!$D$31*G51*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*G51+0.4357405005*G51+0.0330936548*G51+0.0328406739))+G57*('Segments'!$D$32*G51*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*G51+0.4357405005*G51+0.0330936548*G51+0.0328406739))+G58*('Segments'!$D$33*G51*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*G51+0.4357405005*G51+0.0330936548*G51+0.0328406739))+G59*('Segments'!$D$34*G51*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*G51+0.4357405005*G51+0.0330936548*G51+0.0328406739))</f>
         <v/>
       </c>
     </row>
@@ -4456,23 +4456,23 @@
         </is>
       </c>
       <c r="C111" s="18">
-        <f>C101*('Segments'!$D$27*C100*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*C99+0.4357405005*C99+0.0330936548*C100+0.0328406739))+C102*('Segments'!$D$28*C100*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*C99+0.4357405005*C99+0.0330936548*C100+0.0328406739))+C103*('Segments'!$D$29*C100*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*C99+0.4357405005*C99+0.0330936548*C100+0.0328406739))+C104*('Segments'!$D$30*C100*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*C99+0.4357405005*C99+0.0330936548*C100+0.0328406739))+C105*('Segments'!$D$31*C100*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*C99+0.4357405005*C99+0.0330936548*C100+0.0328406739))+C106*('Segments'!$D$32*C100*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*C99+0.4357405005*C99+0.0330936548*C100+0.0328406739))+C107*('Segments'!$D$33*C100*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*C99+0.4357405005*C99+0.0330936548*C100+0.0328406739))+C108*('Segments'!$D$34*C100*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*C99+0.4357405005*C99+0.0330936548*C100+0.0328406739))</f>
+        <f>C101*('Segments'!$D$27*C100*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*C100+0.4357405005*C100+0.0330936548*C100+0.0328406739))+C102*('Segments'!$D$28*C100*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*C100+0.4357405005*C100+0.0330936548*C100+0.0328406739))+C103*('Segments'!$D$29*C100*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*C100+0.4357405005*C100+0.0330936548*C100+0.0328406739))+C104*('Segments'!$D$30*C100*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*C100+0.4357405005*C100+0.0330936548*C100+0.0328406739))+C105*('Segments'!$D$31*C100*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*C100+0.4357405005*C100+0.0330936548*C100+0.0328406739))+C106*('Segments'!$D$32*C100*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*C100+0.4357405005*C100+0.0330936548*C100+0.0328406739))+C107*('Segments'!$D$33*C100*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*C100+0.4357405005*C100+0.0330936548*C100+0.0328406739))+C108*('Segments'!$D$34*C100*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*C100+0.4357405005*C100+0.0330936548*C100+0.0328406739))</f>
         <v/>
       </c>
       <c r="D111" s="18">
-        <f>D101*('Segments'!$D$27*D100*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*D99+0.4357405005*D99+0.0330936548*D100+0.0328406739))+D102*('Segments'!$D$28*D100*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*D99+0.4357405005*D99+0.0330936548*D100+0.0328406739))+D103*('Segments'!$D$29*D100*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*D99+0.4357405005*D99+0.0330936548*D100+0.0328406739))+D104*('Segments'!$D$30*D100*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*D99+0.4357405005*D99+0.0330936548*D100+0.0328406739))+D105*('Segments'!$D$31*D100*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*D99+0.4357405005*D99+0.0330936548*D100+0.0328406739))+D106*('Segments'!$D$32*D100*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*D99+0.4357405005*D99+0.0330936548*D100+0.0328406739))+D107*('Segments'!$D$33*D100*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*D99+0.4357405005*D99+0.0330936548*D100+0.0328406739))+D108*('Segments'!$D$34*D100*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*D99+0.4357405005*D99+0.0330936548*D100+0.0328406739))</f>
+        <f>D101*('Segments'!$D$27*D100*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*D100+0.4357405005*D100+0.0330936548*D100+0.0328406739))+D102*('Segments'!$D$28*D100*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*D100+0.4357405005*D100+0.0330936548*D100+0.0328406739))+D103*('Segments'!$D$29*D100*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*D100+0.4357405005*D100+0.0330936548*D100+0.0328406739))+D104*('Segments'!$D$30*D100*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*D100+0.4357405005*D100+0.0330936548*D100+0.0328406739))+D105*('Segments'!$D$31*D100*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*D100+0.4357405005*D100+0.0330936548*D100+0.0328406739))+D106*('Segments'!$D$32*D100*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*D100+0.4357405005*D100+0.0330936548*D100+0.0328406739))+D107*('Segments'!$D$33*D100*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*D100+0.4357405005*D100+0.0330936548*D100+0.0328406739))+D108*('Segments'!$D$34*D100*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*D100+0.4357405005*D100+0.0330936548*D100+0.0328406739))</f>
         <v/>
       </c>
       <c r="E111" s="18">
-        <f>E101*('Segments'!$D$27*E100*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*E99+0.4357405005*E99+0.0330936548*E100+0.0328406739))+E102*('Segments'!$D$28*E100*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*E99+0.4357405005*E99+0.0330936548*E100+0.0328406739))+E103*('Segments'!$D$29*E100*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*E99+0.4357405005*E99+0.0330936548*E100+0.0328406739))+E104*('Segments'!$D$30*E100*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*E99+0.4357405005*E99+0.0330936548*E100+0.0328406739))+E105*('Segments'!$D$31*E100*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*E99+0.4357405005*E99+0.0330936548*E100+0.0328406739))+E106*('Segments'!$D$32*E100*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*E99+0.4357405005*E99+0.0330936548*E100+0.0328406739))+E107*('Segments'!$D$33*E100*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*E99+0.4357405005*E99+0.0330936548*E100+0.0328406739))+E108*('Segments'!$D$34*E100*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*E99+0.4357405005*E99+0.0330936548*E100+0.0328406739))</f>
+        <f>E101*('Segments'!$D$27*E100*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*E100+0.4357405005*E100+0.0330936548*E100+0.0328406739))+E102*('Segments'!$D$28*E100*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*E100+0.4357405005*E100+0.0330936548*E100+0.0328406739))+E103*('Segments'!$D$29*E100*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*E100+0.4357405005*E100+0.0330936548*E100+0.0328406739))+E104*('Segments'!$D$30*E100*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*E100+0.4357405005*E100+0.0330936548*E100+0.0328406739))+E105*('Segments'!$D$31*E100*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*E100+0.4357405005*E100+0.0330936548*E100+0.0328406739))+E106*('Segments'!$D$32*E100*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*E100+0.4357405005*E100+0.0330936548*E100+0.0328406739))+E107*('Segments'!$D$33*E100*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*E100+0.4357405005*E100+0.0330936548*E100+0.0328406739))+E108*('Segments'!$D$34*E100*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*E100+0.4357405005*E100+0.0330936548*E100+0.0328406739))</f>
         <v/>
       </c>
       <c r="F111" s="18">
-        <f>F101*('Segments'!$D$27*F100*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*F99+0.4357405005*F99+0.0330936548*F100+0.0328406739))+F102*('Segments'!$D$28*F100*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*F99+0.4357405005*F99+0.0330936548*F100+0.0328406739))+F103*('Segments'!$D$29*F100*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*F99+0.4357405005*F99+0.0330936548*F100+0.0328406739))+F104*('Segments'!$D$30*F100*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*F99+0.4357405005*F99+0.0330936548*F100+0.0328406739))+F105*('Segments'!$D$31*F100*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*F99+0.4357405005*F99+0.0330936548*F100+0.0328406739))+F106*('Segments'!$D$32*F100*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*F99+0.4357405005*F99+0.0330936548*F100+0.0328406739))+F107*('Segments'!$D$33*F100*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*F99+0.4357405005*F99+0.0330936548*F100+0.0328406739))+F108*('Segments'!$D$34*F100*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*F99+0.4357405005*F99+0.0330936548*F100+0.0328406739))</f>
+        <f>F101*('Segments'!$D$27*F100*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*F100+0.4357405005*F100+0.0330936548*F100+0.0328406739))+F102*('Segments'!$D$28*F100*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*F100+0.4357405005*F100+0.0330936548*F100+0.0328406739))+F103*('Segments'!$D$29*F100*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*F100+0.4357405005*F100+0.0330936548*F100+0.0328406739))+F104*('Segments'!$D$30*F100*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*F100+0.4357405005*F100+0.0330936548*F100+0.0328406739))+F105*('Segments'!$D$31*F100*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*F100+0.4357405005*F100+0.0330936548*F100+0.0328406739))+F106*('Segments'!$D$32*F100*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*F100+0.4357405005*F100+0.0330936548*F100+0.0328406739))+F107*('Segments'!$D$33*F100*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*F100+0.4357405005*F100+0.0330936548*F100+0.0328406739))+F108*('Segments'!$D$34*F100*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*F100+0.4357405005*F100+0.0330936548*F100+0.0328406739))</f>
         <v/>
       </c>
       <c r="G111" s="18">
-        <f>G101*('Segments'!$D$27*G100*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*G99+0.4357405005*G99+0.0330936548*G100+0.0328406739))+G102*('Segments'!$D$28*G100*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*G99+0.4357405005*G99+0.0330936548*G100+0.0328406739))+G103*('Segments'!$D$29*G100*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*G99+0.4357405005*G99+0.0330936548*G100+0.0328406739))+G104*('Segments'!$D$30*G100*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*G99+0.4357405005*G99+0.0330936548*G100+0.0328406739))+G105*('Segments'!$D$31*G100*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*G99+0.4357405005*G99+0.0330936548*G100+0.0328406739))+G106*('Segments'!$D$32*G100*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*G99+0.4357405005*G99+0.0330936548*G100+0.0328406739))+G107*('Segments'!$D$33*G100*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*G99+0.4357405005*G99+0.0330936548*G100+0.0328406739))+G108*('Segments'!$D$34*G100*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*G99+0.4357405005*G99+0.0330936548*G100+0.0328406739))</f>
+        <f>G101*('Segments'!$D$27*G100*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*G100+0.4357405005*G100+0.0330936548*G100+0.0328406739))+G102*('Segments'!$D$28*G100*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*G100+0.4357405005*G100+0.0330936548*G100+0.0328406739))+G103*('Segments'!$D$29*G100*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*G100+0.4357405005*G100+0.0330936548*G100+0.0328406739))+G104*('Segments'!$D$30*G100*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*G100+0.4357405005*G100+0.0330936548*G100+0.0328406739))+G105*('Segments'!$D$31*G100*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*G100+0.4357405005*G100+0.0330936548*G100+0.0328406739))+G106*('Segments'!$D$32*G100*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*G100+0.4357405005*G100+0.0330936548*G100+0.0328406739))+G107*('Segments'!$D$33*G100*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*G100+0.4357405005*G100+0.0330936548*G100+0.0328406739))+G108*('Segments'!$D$34*G100*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*G100+0.4357405005*G100+0.0330936548*G100+0.0328406739))</f>
         <v/>
       </c>
     </row>
@@ -5526,23 +5526,23 @@
         </is>
       </c>
       <c r="C160" s="18">
-        <f>C150*('Segments'!$D$27*C149*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*C148+0.4357405005*C148+0.0330936548*C149+0.0328406739))+C151*('Segments'!$D$28*C149*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*C148+0.4357405005*C148+0.0330936548*C149+0.0328406739))+C152*('Segments'!$D$29*C149*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*C148+0.4357405005*C148+0.0330936548*C149+0.0328406739))+C153*('Segments'!$D$30*C149*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*C148+0.4357405005*C148+0.0330936548*C149+0.0328406739))+C154*('Segments'!$D$31*C149*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*C148+0.4357405005*C148+0.0330936548*C149+0.0328406739))+C155*('Segments'!$D$32*C149*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*C148+0.4357405005*C148+0.0330936548*C149+0.0328406739))+C156*('Segments'!$D$33*C149*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*C148+0.4357405005*C148+0.0330936548*C149+0.0328406739))+C157*('Segments'!$D$34*C149*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*C148+0.4357405005*C148+0.0330936548*C149+0.0328406739))</f>
+        <f>C150*('Segments'!$D$27*C149*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*C149+0.4357405005*C149+0.0330936548*C149+0.0328406739))+C151*('Segments'!$D$28*C149*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*C149+0.4357405005*C149+0.0330936548*C149+0.0328406739))+C152*('Segments'!$D$29*C149*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*C149+0.4357405005*C149+0.0330936548*C149+0.0328406739))+C153*('Segments'!$D$30*C149*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*C149+0.4357405005*C149+0.0330936548*C149+0.0328406739))+C154*('Segments'!$D$31*C149*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*C149+0.4357405005*C149+0.0330936548*C149+0.0328406739))+C155*('Segments'!$D$32*C149*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*C149+0.4357405005*C149+0.0330936548*C149+0.0328406739))+C156*('Segments'!$D$33*C149*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*C149+0.4357405005*C149+0.0330936548*C149+0.0328406739))+C157*('Segments'!$D$34*C149*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*C149+0.4357405005*C149+0.0330936548*C149+0.0328406739))</f>
         <v/>
       </c>
       <c r="D160" s="18">
-        <f>D150*('Segments'!$D$27*D149*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*D148+0.4357405005*D148+0.0330936548*D149+0.0328406739))+D151*('Segments'!$D$28*D149*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*D148+0.4357405005*D148+0.0330936548*D149+0.0328406739))+D152*('Segments'!$D$29*D149*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*D148+0.4357405005*D148+0.0330936548*D149+0.0328406739))+D153*('Segments'!$D$30*D149*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*D148+0.4357405005*D148+0.0330936548*D149+0.0328406739))+D154*('Segments'!$D$31*D149*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*D148+0.4357405005*D148+0.0330936548*D149+0.0328406739))+D155*('Segments'!$D$32*D149*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*D148+0.4357405005*D148+0.0330936548*D149+0.0328406739))+D156*('Segments'!$D$33*D149*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*D148+0.4357405005*D148+0.0330936548*D149+0.0328406739))+D157*('Segments'!$D$34*D149*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*D148+0.4357405005*D148+0.0330936548*D149+0.0328406739))</f>
+        <f>D150*('Segments'!$D$27*D149*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*D149+0.4357405005*D149+0.0330936548*D149+0.0328406739))+D151*('Segments'!$D$28*D149*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*D149+0.4357405005*D149+0.0330936548*D149+0.0328406739))+D152*('Segments'!$D$29*D149*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*D149+0.4357405005*D149+0.0330936548*D149+0.0328406739))+D153*('Segments'!$D$30*D149*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*D149+0.4357405005*D149+0.0330936548*D149+0.0328406739))+D154*('Segments'!$D$31*D149*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*D149+0.4357405005*D149+0.0330936548*D149+0.0328406739))+D155*('Segments'!$D$32*D149*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*D149+0.4357405005*D149+0.0330936548*D149+0.0328406739))+D156*('Segments'!$D$33*D149*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*D149+0.4357405005*D149+0.0330936548*D149+0.0328406739))+D157*('Segments'!$D$34*D149*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*D149+0.4357405005*D149+0.0330936548*D149+0.0328406739))</f>
         <v/>
       </c>
       <c r="E160" s="18">
-        <f>E150*('Segments'!$D$27*E149*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*E148+0.4357405005*E148+0.0330936548*E149+0.0328406739))+E151*('Segments'!$D$28*E149*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*E148+0.4357405005*E148+0.0330936548*E149+0.0328406739))+E152*('Segments'!$D$29*E149*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*E148+0.4357405005*E148+0.0330936548*E149+0.0328406739))+E153*('Segments'!$D$30*E149*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*E148+0.4357405005*E148+0.0330936548*E149+0.0328406739))+E154*('Segments'!$D$31*E149*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*E148+0.4357405005*E148+0.0330936548*E149+0.0328406739))+E155*('Segments'!$D$32*E149*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*E148+0.4357405005*E148+0.0330936548*E149+0.0328406739))+E156*('Segments'!$D$33*E149*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*E148+0.4357405005*E148+0.0330936548*E149+0.0328406739))+E157*('Segments'!$D$34*E149*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*E148+0.4357405005*E148+0.0330936548*E149+0.0328406739))</f>
+        <f>E150*('Segments'!$D$27*E149*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*E149+0.4357405005*E149+0.0330936548*E149+0.0328406739))+E151*('Segments'!$D$28*E149*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*E149+0.4357405005*E149+0.0330936548*E149+0.0328406739))+E152*('Segments'!$D$29*E149*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*E149+0.4357405005*E149+0.0330936548*E149+0.0328406739))+E153*('Segments'!$D$30*E149*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*E149+0.4357405005*E149+0.0330936548*E149+0.0328406739))+E154*('Segments'!$D$31*E149*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*E149+0.4357405005*E149+0.0330936548*E149+0.0328406739))+E155*('Segments'!$D$32*E149*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*E149+0.4357405005*E149+0.0330936548*E149+0.0328406739))+E156*('Segments'!$D$33*E149*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*E149+0.4357405005*E149+0.0330936548*E149+0.0328406739))+E157*('Segments'!$D$34*E149*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*E149+0.4357405005*E149+0.0330936548*E149+0.0328406739))</f>
         <v/>
       </c>
       <c r="F160" s="18">
-        <f>F150*('Segments'!$D$27*F149*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*F148+0.4357405005*F148+0.0330936548*F149+0.0328406739))+F151*('Segments'!$D$28*F149*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*F148+0.4357405005*F148+0.0330936548*F149+0.0328406739))+F152*('Segments'!$D$29*F149*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*F148+0.4357405005*F148+0.0330936548*F149+0.0328406739))+F153*('Segments'!$D$30*F149*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*F148+0.4357405005*F148+0.0330936548*F149+0.0328406739))+F154*('Segments'!$D$31*F149*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*F148+0.4357405005*F148+0.0330936548*F149+0.0328406739))+F155*('Segments'!$D$32*F149*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*F148+0.4357405005*F148+0.0330936548*F149+0.0328406739))+F156*('Segments'!$D$33*F149*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*F148+0.4357405005*F148+0.0330936548*F149+0.0328406739))+F157*('Segments'!$D$34*F149*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*F148+0.4357405005*F148+0.0330936548*F149+0.0328406739))</f>
+        <f>F150*('Segments'!$D$27*F149*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*F149+0.4357405005*F149+0.0330936548*F149+0.0328406739))+F151*('Segments'!$D$28*F149*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*F149+0.4357405005*F149+0.0330936548*F149+0.0328406739))+F152*('Segments'!$D$29*F149*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*F149+0.4357405005*F149+0.0330936548*F149+0.0328406739))+F153*('Segments'!$D$30*F149*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*F149+0.4357405005*F149+0.0330936548*F149+0.0328406739))+F154*('Segments'!$D$31*F149*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*F149+0.4357405005*F149+0.0330936548*F149+0.0328406739))+F155*('Segments'!$D$32*F149*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*F149+0.4357405005*F149+0.0330936548*F149+0.0328406739))+F156*('Segments'!$D$33*F149*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*F149+0.4357405005*F149+0.0330936548*F149+0.0328406739))+F157*('Segments'!$D$34*F149*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*F149+0.4357405005*F149+0.0330936548*F149+0.0328406739))</f>
         <v/>
       </c>
       <c r="G160" s="18">
-        <f>G150*('Segments'!$D$27*G149*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*G148+0.4357405005*G148+0.0330936548*G149+0.0328406739))+G151*('Segments'!$D$28*G149*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*G148+0.4357405005*G148+0.0330936548*G149+0.0328406739))+G152*('Segments'!$D$29*G149*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*G148+0.4357405005*G148+0.0330936548*G149+0.0328406739))+G153*('Segments'!$D$30*G149*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*G148+0.4357405005*G148+0.0330936548*G149+0.0328406739))+G154*('Segments'!$D$31*G149*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*G148+0.4357405005*G148+0.0330936548*G149+0.0328406739))+G155*('Segments'!$D$32*G149*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*G148+0.4357405005*G148+0.0330936548*G149+0.0328406739))+G156*('Segments'!$D$33*G149*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*G148+0.4357405005*G148+0.0330936548*G149+0.0328406739))+G157*('Segments'!$D$34*G149*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*G148+0.4357405005*G148+0.0330936548*G149+0.0328406739))</f>
+        <f>G150*('Segments'!$D$27*G149*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*G149+0.4357405005*G149+0.0330936548*G149+0.0328406739))+G151*('Segments'!$D$28*G149*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*G149+0.4357405005*G149+0.0330936548*G149+0.0328406739))+G152*('Segments'!$D$29*G149*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*G149+0.4357405005*G149+0.0330936548*G149+0.0328406739))+G153*('Segments'!$D$30*G149*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*G149+0.4357405005*G149+0.0330936548*G149+0.0328406739))+G154*('Segments'!$D$31*G149*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*G149+0.4357405005*G149+0.0330936548*G149+0.0328406739))+G155*('Segments'!$D$32*G149*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*G149+0.4357405005*G149+0.0330936548*G149+0.0328406739))+G156*('Segments'!$D$33*G149*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*G149+0.4357405005*G149+0.0330936548*G149+0.0328406739))+G157*('Segments'!$D$34*G149*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*G149+0.4357405005*G149+0.0330936548*G149+0.0328406739))</f>
         <v/>
       </c>
     </row>
@@ -6596,23 +6596,23 @@
         </is>
       </c>
       <c r="C209" s="18">
-        <f>C199*('Segments'!$D$27*C198*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*C197+0.4357405005*C197+0.0330936548*C198+0.0328406739))+C200*('Segments'!$D$28*C198*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*C197+0.4357405005*C197+0.0330936548*C198+0.0328406739))+C201*('Segments'!$D$29*C198*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*C197+0.4357405005*C197+0.0330936548*C198+0.0328406739))+C202*('Segments'!$D$30*C198*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*C197+0.4357405005*C197+0.0330936548*C198+0.0328406739))+C203*('Segments'!$D$31*C198*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*C197+0.4357405005*C197+0.0330936548*C198+0.0328406739))+C204*('Segments'!$D$32*C198*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*C197+0.4357405005*C197+0.0330936548*C198+0.0328406739))+C205*('Segments'!$D$33*C198*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*C197+0.4357405005*C197+0.0330936548*C198+0.0328406739))+C206*('Segments'!$D$34*C198*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*C197+0.4357405005*C197+0.0330936548*C198+0.0328406739))</f>
+        <f>C199*('Segments'!$D$27*C198*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*C198+0.4357405005*C198+0.0330936548*C198+0.0328406739))+C200*('Segments'!$D$28*C198*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*C198+0.4357405005*C198+0.0330936548*C198+0.0328406739))+C201*('Segments'!$D$29*C198*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*C198+0.4357405005*C198+0.0330936548*C198+0.0328406739))+C202*('Segments'!$D$30*C198*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*C198+0.4357405005*C198+0.0330936548*C198+0.0328406739))+C203*('Segments'!$D$31*C198*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*C198+0.4357405005*C198+0.0330936548*C198+0.0328406739))+C204*('Segments'!$D$32*C198*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*C198+0.4357405005*C198+0.0330936548*C198+0.0328406739))+C205*('Segments'!$D$33*C198*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*C198+0.4357405005*C198+0.0330936548*C198+0.0328406739))+C206*('Segments'!$D$34*C198*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*C198+0.4357405005*C198+0.0330936548*C198+0.0328406739))</f>
         <v/>
       </c>
       <c r="D209" s="18">
-        <f>D199*('Segments'!$D$27*D198*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*D197+0.4357405005*D197+0.0330936548*D198+0.0328406739))+D200*('Segments'!$D$28*D198*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*D197+0.4357405005*D197+0.0330936548*D198+0.0328406739))+D201*('Segments'!$D$29*D198*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*D197+0.4357405005*D197+0.0330936548*D198+0.0328406739))+D202*('Segments'!$D$30*D198*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*D197+0.4357405005*D197+0.0330936548*D198+0.0328406739))+D203*('Segments'!$D$31*D198*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*D197+0.4357405005*D197+0.0330936548*D198+0.0328406739))+D204*('Segments'!$D$32*D198*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*D197+0.4357405005*D197+0.0330936548*D198+0.0328406739))+D205*('Segments'!$D$33*D198*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*D197+0.4357405005*D197+0.0330936548*D198+0.0328406739))+D206*('Segments'!$D$34*D198*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*D197+0.4357405005*D197+0.0330936548*D198+0.0328406739))</f>
+        <f>D199*('Segments'!$D$27*D198*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*D198+0.4357405005*D198+0.0330936548*D198+0.0328406739))+D200*('Segments'!$D$28*D198*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*D198+0.4357405005*D198+0.0330936548*D198+0.0328406739))+D201*('Segments'!$D$29*D198*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*D198+0.4357405005*D198+0.0330936548*D198+0.0328406739))+D202*('Segments'!$D$30*D198*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*D198+0.4357405005*D198+0.0330936548*D198+0.0328406739))+D203*('Segments'!$D$31*D198*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*D198+0.4357405005*D198+0.0330936548*D198+0.0328406739))+D204*('Segments'!$D$32*D198*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*D198+0.4357405005*D198+0.0330936548*D198+0.0328406739))+D205*('Segments'!$D$33*D198*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*D198+0.4357405005*D198+0.0330936548*D198+0.0328406739))+D206*('Segments'!$D$34*D198*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*D198+0.4357405005*D198+0.0330936548*D198+0.0328406739))</f>
         <v/>
       </c>
       <c r="E209" s="18">
-        <f>E199*('Segments'!$D$27*E198*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*E197+0.4357405005*E197+0.0330936548*E198+0.0328406739))+E200*('Segments'!$D$28*E198*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*E197+0.4357405005*E197+0.0330936548*E198+0.0328406739))+E201*('Segments'!$D$29*E198*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*E197+0.4357405005*E197+0.0330936548*E198+0.0328406739))+E202*('Segments'!$D$30*E198*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*E197+0.4357405005*E197+0.0330936548*E198+0.0328406739))+E203*('Segments'!$D$31*E198*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*E197+0.4357405005*E197+0.0330936548*E198+0.0328406739))+E204*('Segments'!$D$32*E198*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*E197+0.4357405005*E197+0.0330936548*E198+0.0328406739))+E205*('Segments'!$D$33*E198*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*E197+0.4357405005*E197+0.0330936548*E198+0.0328406739))+E206*('Segments'!$D$34*E198*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*E197+0.4357405005*E197+0.0330936548*E198+0.0328406739))</f>
+        <f>E199*('Segments'!$D$27*E198*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*E198+0.4357405005*E198+0.0330936548*E198+0.0328406739))+E200*('Segments'!$D$28*E198*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*E198+0.4357405005*E198+0.0330936548*E198+0.0328406739))+E201*('Segments'!$D$29*E198*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*E198+0.4357405005*E198+0.0330936548*E198+0.0328406739))+E202*('Segments'!$D$30*E198*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*E198+0.4357405005*E198+0.0330936548*E198+0.0328406739))+E203*('Segments'!$D$31*E198*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*E198+0.4357405005*E198+0.0330936548*E198+0.0328406739))+E204*('Segments'!$D$32*E198*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*E198+0.4357405005*E198+0.0330936548*E198+0.0328406739))+E205*('Segments'!$D$33*E198*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*E198+0.4357405005*E198+0.0330936548*E198+0.0328406739))+E206*('Segments'!$D$34*E198*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*E198+0.4357405005*E198+0.0330936548*E198+0.0328406739))</f>
         <v/>
       </c>
       <c r="F209" s="18">
-        <f>F199*('Segments'!$D$27*F198*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*F197+0.4357405005*F197+0.0330936548*F198+0.0328406739))+F200*('Segments'!$D$28*F198*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*F197+0.4357405005*F197+0.0330936548*F198+0.0328406739))+F201*('Segments'!$D$29*F198*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*F197+0.4357405005*F197+0.0330936548*F198+0.0328406739))+F202*('Segments'!$D$30*F198*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*F197+0.4357405005*F197+0.0330936548*F198+0.0328406739))+F203*('Segments'!$D$31*F198*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*F197+0.4357405005*F197+0.0330936548*F198+0.0328406739))+F204*('Segments'!$D$32*F198*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*F197+0.4357405005*F197+0.0330936548*F198+0.0328406739))+F205*('Segments'!$D$33*F198*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*F197+0.4357405005*F197+0.0330936548*F198+0.0328406739))+F206*('Segments'!$D$34*F198*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*F197+0.4357405005*F197+0.0330936548*F198+0.0328406739))</f>
+        <f>F199*('Segments'!$D$27*F198*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*F198+0.4357405005*F198+0.0330936548*F198+0.0328406739))+F200*('Segments'!$D$28*F198*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*F198+0.4357405005*F198+0.0330936548*F198+0.0328406739))+F201*('Segments'!$D$29*F198*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*F198+0.4357405005*F198+0.0330936548*F198+0.0328406739))+F202*('Segments'!$D$30*F198*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*F198+0.4357405005*F198+0.0330936548*F198+0.0328406739))+F203*('Segments'!$D$31*F198*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*F198+0.4357405005*F198+0.0330936548*F198+0.0328406739))+F204*('Segments'!$D$32*F198*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*F198+0.4357405005*F198+0.0330936548*F198+0.0328406739))+F205*('Segments'!$D$33*F198*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*F198+0.4357405005*F198+0.0330936548*F198+0.0328406739))+F206*('Segments'!$D$34*F198*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*F198+0.4357405005*F198+0.0330936548*F198+0.0328406739))</f>
         <v/>
       </c>
       <c r="G209" s="18">
-        <f>G199*('Segments'!$D$27*G198*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*G197+0.4357405005*G197+0.0330936548*G198+0.0328406739))+G200*('Segments'!$D$28*G198*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*G197+0.4357405005*G197+0.0330936548*G198+0.0328406739))+G201*('Segments'!$D$29*G198*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*G197+0.4357405005*G197+0.0330936548*G198+0.0328406739))+G202*('Segments'!$D$30*G198*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*G197+0.4357405005*G197+0.0330936548*G198+0.0328406739))+G203*('Segments'!$D$31*G198*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*G197+0.4357405005*G197+0.0330936548*G198+0.0328406739))+G204*('Segments'!$D$32*G198*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*G197+0.4357405005*G197+0.0330936548*G198+0.0328406739))+G205*('Segments'!$D$33*G198*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*G197+0.4357405005*G197+0.0330936548*G198+0.0328406739))+G206*('Segments'!$D$34*G198*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*G197+0.4357405005*G197+0.0330936548*G198+0.0328406739))</f>
+        <f>G199*('Segments'!$D$27*G198*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*G198+0.4357405005*G198+0.0330936548*G198+0.0328406739))+G200*('Segments'!$D$28*G198*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*G198+0.4357405005*G198+0.0330936548*G198+0.0328406739))+G201*('Segments'!$D$29*G198*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*G198+0.4357405005*G198+0.0330936548*G198+0.0328406739))+G202*('Segments'!$D$30*G198*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*G198+0.4357405005*G198+0.0330936548*G198+0.0328406739))+G203*('Segments'!$D$31*G198*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*G198+0.4357405005*G198+0.0330936548*G198+0.0328406739))+G204*('Segments'!$D$32*G198*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*G198+0.4357405005*G198+0.0330936548*G198+0.0328406739))+G205*('Segments'!$D$33*G198*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*G198+0.4357405005*G198+0.0330936548*G198+0.0328406739))+G206*('Segments'!$D$34*G198*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*G198+0.4357405005*G198+0.0330936548*G198+0.0328406739))</f>
         <v/>
       </c>
     </row>
@@ -7666,23 +7666,23 @@
         </is>
       </c>
       <c r="C258" s="18">
-        <f>C248*('Segments'!$D$27*C247*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*C246+0.4357405005*C246+0.0330936548*C247+0.0328406739))+C249*('Segments'!$D$28*C247*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*C246+0.4357405005*C246+0.0330936548*C247+0.0328406739))+C250*('Segments'!$D$29*C247*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*C246+0.4357405005*C246+0.0330936548*C247+0.0328406739))+C251*('Segments'!$D$30*C247*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*C246+0.4357405005*C246+0.0330936548*C247+0.0328406739))+C252*('Segments'!$D$31*C247*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*C246+0.4357405005*C246+0.0330936548*C247+0.0328406739))+C253*('Segments'!$D$32*C247*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*C246+0.4357405005*C246+0.0330936548*C247+0.0328406739))+C254*('Segments'!$D$33*C247*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*C246+0.4357405005*C246+0.0330936548*C247+0.0328406739))+C255*('Segments'!$D$34*C247*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*C246+0.4357405005*C246+0.0330936548*C247+0.0328406739))</f>
+        <f>C248*('Segments'!$D$27*C247*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*C247+0.4357405005*C247+0.0330936548*C247+0.0328406739))+C249*('Segments'!$D$28*C247*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*C247+0.4357405005*C247+0.0330936548*C247+0.0328406739))+C250*('Segments'!$D$29*C247*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*C247+0.4357405005*C247+0.0330936548*C247+0.0328406739))+C251*('Segments'!$D$30*C247*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*C247+0.4357405005*C247+0.0330936548*C247+0.0328406739))+C252*('Segments'!$D$31*C247*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*C247+0.4357405005*C247+0.0330936548*C247+0.0328406739))+C253*('Segments'!$D$32*C247*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*C247+0.4357405005*C247+0.0330936548*C247+0.0328406739))+C254*('Segments'!$D$33*C247*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*C247+0.4357405005*C247+0.0330936548*C247+0.0328406739))+C255*('Segments'!$D$34*C247*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*C247+0.4357405005*C247+0.0330936548*C247+0.0328406739))</f>
         <v/>
       </c>
       <c r="D258" s="18">
-        <f>D248*('Segments'!$D$27*D247*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*D246+0.4357405005*D246+0.0330936548*D247+0.0328406739))+D249*('Segments'!$D$28*D247*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*D246+0.4357405005*D246+0.0330936548*D247+0.0328406739))+D250*('Segments'!$D$29*D247*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*D246+0.4357405005*D246+0.0330936548*D247+0.0328406739))+D251*('Segments'!$D$30*D247*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*D246+0.4357405005*D246+0.0330936548*D247+0.0328406739))+D252*('Segments'!$D$31*D247*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*D246+0.4357405005*D246+0.0330936548*D247+0.0328406739))+D253*('Segments'!$D$32*D247*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*D246+0.4357405005*D246+0.0330936548*D247+0.0328406739))+D254*('Segments'!$D$33*D247*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*D246+0.4357405005*D246+0.0330936548*D247+0.0328406739))+D255*('Segments'!$D$34*D247*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*D246+0.4357405005*D246+0.0330936548*D247+0.0328406739))</f>
+        <f>D248*('Segments'!$D$27*D247*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*D247+0.4357405005*D247+0.0330936548*D247+0.0328406739))+D249*('Segments'!$D$28*D247*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*D247+0.4357405005*D247+0.0330936548*D247+0.0328406739))+D250*('Segments'!$D$29*D247*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*D247+0.4357405005*D247+0.0330936548*D247+0.0328406739))+D251*('Segments'!$D$30*D247*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*D247+0.4357405005*D247+0.0330936548*D247+0.0328406739))+D252*('Segments'!$D$31*D247*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*D247+0.4357405005*D247+0.0330936548*D247+0.0328406739))+D253*('Segments'!$D$32*D247*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*D247+0.4357405005*D247+0.0330936548*D247+0.0328406739))+D254*('Segments'!$D$33*D247*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*D247+0.4357405005*D247+0.0330936548*D247+0.0328406739))+D255*('Segments'!$D$34*D247*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*D247+0.4357405005*D247+0.0330936548*D247+0.0328406739))</f>
         <v/>
       </c>
       <c r="E258" s="18">
-        <f>E248*('Segments'!$D$27*E247*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*E246+0.4357405005*E246+0.0330936548*E247+0.0328406739))+E249*('Segments'!$D$28*E247*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*E246+0.4357405005*E246+0.0330936548*E247+0.0328406739))+E250*('Segments'!$D$29*E247*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*E246+0.4357405005*E246+0.0330936548*E247+0.0328406739))+E251*('Segments'!$D$30*E247*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*E246+0.4357405005*E246+0.0330936548*E247+0.0328406739))+E252*('Segments'!$D$31*E247*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*E246+0.4357405005*E246+0.0330936548*E247+0.0328406739))+E253*('Segments'!$D$32*E247*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*E246+0.4357405005*E246+0.0330936548*E247+0.0328406739))+E254*('Segments'!$D$33*E247*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*E246+0.4357405005*E246+0.0330936548*E247+0.0328406739))+E255*('Segments'!$D$34*E247*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*E246+0.4357405005*E246+0.0330936548*E247+0.0328406739))</f>
+        <f>E248*('Segments'!$D$27*E247*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*E247+0.4357405005*E247+0.0330936548*E247+0.0328406739))+E249*('Segments'!$D$28*E247*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*E247+0.4357405005*E247+0.0330936548*E247+0.0328406739))+E250*('Segments'!$D$29*E247*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*E247+0.4357405005*E247+0.0330936548*E247+0.0328406739))+E251*('Segments'!$D$30*E247*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*E247+0.4357405005*E247+0.0330936548*E247+0.0328406739))+E252*('Segments'!$D$31*E247*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*E247+0.4357405005*E247+0.0330936548*E247+0.0328406739))+E253*('Segments'!$D$32*E247*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*E247+0.4357405005*E247+0.0330936548*E247+0.0328406739))+E254*('Segments'!$D$33*E247*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*E247+0.4357405005*E247+0.0330936548*E247+0.0328406739))+E255*('Segments'!$D$34*E247*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*E247+0.4357405005*E247+0.0330936548*E247+0.0328406739))</f>
         <v/>
       </c>
       <c r="F258" s="18">
-        <f>F248*('Segments'!$D$27*F247*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*F246+0.4357405005*F246+0.0330936548*F247+0.0328406739))+F249*('Segments'!$D$28*F247*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*F246+0.4357405005*F246+0.0330936548*F247+0.0328406739))+F250*('Segments'!$D$29*F247*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*F246+0.4357405005*F246+0.0330936548*F247+0.0328406739))+F251*('Segments'!$D$30*F247*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*F246+0.4357405005*F246+0.0330936548*F247+0.0328406739))+F252*('Segments'!$D$31*F247*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*F246+0.4357405005*F246+0.0330936548*F247+0.0328406739))+F253*('Segments'!$D$32*F247*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*F246+0.4357405005*F246+0.0330936548*F247+0.0328406739))+F254*('Segments'!$D$33*F247*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*F246+0.4357405005*F246+0.0330936548*F247+0.0328406739))+F255*('Segments'!$D$34*F247*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*F246+0.4357405005*F246+0.0330936548*F247+0.0328406739))</f>
+        <f>F248*('Segments'!$D$27*F247*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*F247+0.4357405005*F247+0.0330936548*F247+0.0328406739))+F249*('Segments'!$D$28*F247*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*F247+0.4357405005*F247+0.0330936548*F247+0.0328406739))+F250*('Segments'!$D$29*F247*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*F247+0.4357405005*F247+0.0330936548*F247+0.0328406739))+F251*('Segments'!$D$30*F247*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*F247+0.4357405005*F247+0.0330936548*F247+0.0328406739))+F252*('Segments'!$D$31*F247*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*F247+0.4357405005*F247+0.0330936548*F247+0.0328406739))+F253*('Segments'!$D$32*F247*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*F247+0.4357405005*F247+0.0330936548*F247+0.0328406739))+F254*('Segments'!$D$33*F247*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*F247+0.4357405005*F247+0.0330936548*F247+0.0328406739))+F255*('Segments'!$D$34*F247*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*F247+0.4357405005*F247+0.0330936548*F247+0.0328406739))</f>
         <v/>
       </c>
       <c r="G258" s="18">
-        <f>G248*('Segments'!$D$27*G247*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*G246+0.4357405005*G246+0.0330936548*G247+0.0328406739))+G249*('Segments'!$D$28*G247*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*G246+0.4357405005*G246+0.0330936548*G247+0.0328406739))+G250*('Segments'!$D$29*G247*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*G246+0.4357405005*G246+0.0330936548*G247+0.0328406739))+G251*('Segments'!$D$30*G247*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*G246+0.4357405005*G246+0.0330936548*G247+0.0328406739))+G252*('Segments'!$D$31*G247*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*G246+0.4357405005*G246+0.0330936548*G247+0.0328406739))+G253*('Segments'!$D$32*G247*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*G246+0.4357405005*G246+0.0330936548*G247+0.0328406739))+G254*('Segments'!$D$33*G247*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*G246+0.4357405005*G246+0.0330936548*G247+0.0328406739))+G255*('Segments'!$D$34*G247*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*G246+0.4357405005*G246+0.0330936548*G247+0.0328406739))</f>
+        <f>G248*('Segments'!$D$27*G247*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*G247+0.4357405005*G247+0.0330936548*G247+0.0328406739))+G249*('Segments'!$D$28*G247*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*G247+0.4357405005*G247+0.0330936548*G247+0.0328406739))+G250*('Segments'!$D$29*G247*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*G247+0.4357405005*G247+0.0330936548*G247+0.0328406739))+G251*('Segments'!$D$30*G247*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*G247+0.4357405005*G247+0.0330936548*G247+0.0328406739))+G252*('Segments'!$D$31*G247*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*G247+0.4357405005*G247+0.0330936548*G247+0.0328406739))+G253*('Segments'!$D$32*G247*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*G247+0.4357405005*G247+0.0330936548*G247+0.0328406739))+G254*('Segments'!$D$33*G247*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*G247+0.4357405005*G247+0.0330936548*G247+0.0328406739))+G255*('Segments'!$D$34*G247*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*G247+0.4357405005*G247+0.0330936548*G247+0.0328406739))</f>
         <v/>
       </c>
     </row>
@@ -8736,23 +8736,23 @@
         </is>
       </c>
       <c r="C307" s="18">
-        <f>C297*('Segments'!$D$27*C296*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*C295+0.4357405005*C295+0.0330936548*C296+0.0328406739))+C298*('Segments'!$D$28*C296*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*C295+0.4357405005*C295+0.0330936548*C296+0.0328406739))+C299*('Segments'!$D$29*C296*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*C295+0.4357405005*C295+0.0330936548*C296+0.0328406739))+C300*('Segments'!$D$30*C296*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*C295+0.4357405005*C295+0.0330936548*C296+0.0328406739))+C301*('Segments'!$D$31*C296*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*C295+0.4357405005*C295+0.0330936548*C296+0.0328406739))+C302*('Segments'!$D$32*C296*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*C295+0.4357405005*C295+0.0330936548*C296+0.0328406739))+C303*('Segments'!$D$33*C296*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*C295+0.4357405005*C295+0.0330936548*C296+0.0328406739))+C304*('Segments'!$D$34*C296*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*C295+0.4357405005*C295+0.0330936548*C296+0.0328406739))</f>
+        <f>C297*('Segments'!$D$27*C296*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*C296+0.4357405005*C296+0.0330936548*C296+0.0328406739))+C298*('Segments'!$D$28*C296*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*C296+0.4357405005*C296+0.0330936548*C296+0.0328406739))+C299*('Segments'!$D$29*C296*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*C296+0.4357405005*C296+0.0330936548*C296+0.0328406739))+C300*('Segments'!$D$30*C296*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*C296+0.4357405005*C296+0.0330936548*C296+0.0328406739))+C301*('Segments'!$D$31*C296*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*C296+0.4357405005*C296+0.0330936548*C296+0.0328406739))+C302*('Segments'!$D$32*C296*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*C296+0.4357405005*C296+0.0330936548*C296+0.0328406739))+C303*('Segments'!$D$33*C296*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*C296+0.4357405005*C296+0.0330936548*C296+0.0328406739))+C304*('Segments'!$D$34*C296*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*C296+0.4357405005*C296+0.0330936548*C296+0.0328406739))</f>
         <v/>
       </c>
       <c r="D307" s="18">
-        <f>D297*('Segments'!$D$27*D296*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*D295+0.4357405005*D295+0.0330936548*D296+0.0328406739))+D298*('Segments'!$D$28*D296*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*D295+0.4357405005*D295+0.0330936548*D296+0.0328406739))+D299*('Segments'!$D$29*D296*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*D295+0.4357405005*D295+0.0330936548*D296+0.0328406739))+D300*('Segments'!$D$30*D296*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*D295+0.4357405005*D295+0.0330936548*D296+0.0328406739))+D301*('Segments'!$D$31*D296*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*D295+0.4357405005*D295+0.0330936548*D296+0.0328406739))+D302*('Segments'!$D$32*D296*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*D295+0.4357405005*D295+0.0330936548*D296+0.0328406739))+D303*('Segments'!$D$33*D296*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*D295+0.4357405005*D295+0.0330936548*D296+0.0328406739))+D304*('Segments'!$D$34*D296*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*D295+0.4357405005*D295+0.0330936548*D296+0.0328406739))</f>
+        <f>D297*('Segments'!$D$27*D296*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*D296+0.4357405005*D296+0.0330936548*D296+0.0328406739))+D298*('Segments'!$D$28*D296*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*D296+0.4357405005*D296+0.0330936548*D296+0.0328406739))+D299*('Segments'!$D$29*D296*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*D296+0.4357405005*D296+0.0330936548*D296+0.0328406739))+D300*('Segments'!$D$30*D296*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*D296+0.4357405005*D296+0.0330936548*D296+0.0328406739))+D301*('Segments'!$D$31*D296*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*D296+0.4357405005*D296+0.0330936548*D296+0.0328406739))+D302*('Segments'!$D$32*D296*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*D296+0.4357405005*D296+0.0330936548*D296+0.0328406739))+D303*('Segments'!$D$33*D296*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*D296+0.4357405005*D296+0.0330936548*D296+0.0328406739))+D304*('Segments'!$D$34*D296*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*D296+0.4357405005*D296+0.0330936548*D296+0.0328406739))</f>
         <v/>
       </c>
       <c r="E307" s="18">
-        <f>E297*('Segments'!$D$27*E296*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*E295+0.4357405005*E295+0.0330936548*E296+0.0328406739))+E298*('Segments'!$D$28*E296*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*E295+0.4357405005*E295+0.0330936548*E296+0.0328406739))+E299*('Segments'!$D$29*E296*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*E295+0.4357405005*E295+0.0330936548*E296+0.0328406739))+E300*('Segments'!$D$30*E296*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*E295+0.4357405005*E295+0.0330936548*E296+0.0328406739))+E301*('Segments'!$D$31*E296*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*E295+0.4357405005*E295+0.0330936548*E296+0.0328406739))+E302*('Segments'!$D$32*E296*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*E295+0.4357405005*E295+0.0330936548*E296+0.0328406739))+E303*('Segments'!$D$33*E296*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*E295+0.4357405005*E295+0.0330936548*E296+0.0328406739))+E304*('Segments'!$D$34*E296*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*E295+0.4357405005*E295+0.0330936548*E296+0.0328406739))</f>
+        <f>E297*('Segments'!$D$27*E296*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*E296+0.4357405005*E296+0.0330936548*E296+0.0328406739))+E298*('Segments'!$D$28*E296*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*E296+0.4357405005*E296+0.0330936548*E296+0.0328406739))+E299*('Segments'!$D$29*E296*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*E296+0.4357405005*E296+0.0330936548*E296+0.0328406739))+E300*('Segments'!$D$30*E296*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*E296+0.4357405005*E296+0.0330936548*E296+0.0328406739))+E301*('Segments'!$D$31*E296*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*E296+0.4357405005*E296+0.0330936548*E296+0.0328406739))+E302*('Segments'!$D$32*E296*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*E296+0.4357405005*E296+0.0330936548*E296+0.0328406739))+E303*('Segments'!$D$33*E296*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*E296+0.4357405005*E296+0.0330936548*E296+0.0328406739))+E304*('Segments'!$D$34*E296*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*E296+0.4357405005*E296+0.0330936548*E296+0.0328406739))</f>
         <v/>
       </c>
       <c r="F307" s="18">
-        <f>F297*('Segments'!$D$27*F296*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*F295+0.4357405005*F295+0.0330936548*F296+0.0328406739))+F298*('Segments'!$D$28*F296*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*F295+0.4357405005*F295+0.0330936548*F296+0.0328406739))+F299*('Segments'!$D$29*F296*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*F295+0.4357405005*F295+0.0330936548*F296+0.0328406739))+F300*('Segments'!$D$30*F296*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*F295+0.4357405005*F295+0.0330936548*F296+0.0328406739))+F301*('Segments'!$D$31*F296*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*F295+0.4357405005*F295+0.0330936548*F296+0.0328406739))+F302*('Segments'!$D$32*F296*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*F295+0.4357405005*F295+0.0330936548*F296+0.0328406739))+F303*('Segments'!$D$33*F296*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*F295+0.4357405005*F295+0.0330936548*F296+0.0328406739))+F304*('Segments'!$D$34*F296*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*F295+0.4357405005*F295+0.0330936548*F296+0.0328406739))</f>
+        <f>F297*('Segments'!$D$27*F296*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*F296+0.4357405005*F296+0.0330936548*F296+0.0328406739))+F298*('Segments'!$D$28*F296*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*F296+0.4357405005*F296+0.0330936548*F296+0.0328406739))+F299*('Segments'!$D$29*F296*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*F296+0.4357405005*F296+0.0330936548*F296+0.0328406739))+F300*('Segments'!$D$30*F296*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*F296+0.4357405005*F296+0.0330936548*F296+0.0328406739))+F301*('Segments'!$D$31*F296*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*F296+0.4357405005*F296+0.0330936548*F296+0.0328406739))+F302*('Segments'!$D$32*F296*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*F296+0.4357405005*F296+0.0330936548*F296+0.0328406739))+F303*('Segments'!$D$33*F296*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*F296+0.4357405005*F296+0.0330936548*F296+0.0328406739))+F304*('Segments'!$D$34*F296*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*F296+0.4357405005*F296+0.0330936548*F296+0.0328406739))</f>
         <v/>
       </c>
       <c r="G307" s="18">
-        <f>G297*('Segments'!$D$27*G296*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*G295+0.4357405005*G295+0.0330936548*G296+0.0328406739))+G298*('Segments'!$D$28*G296*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*G295+0.4357405005*G295+0.0330936548*G296+0.0328406739))+G299*('Segments'!$D$29*G296*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*G295+0.4357405005*G295+0.0330936548*G296+0.0328406739))+G300*('Segments'!$D$30*G296*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*G295+0.4357405005*G295+0.0330936548*G296+0.0328406739))+G301*('Segments'!$D$31*G296*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*G295+0.4357405005*G295+0.0330936548*G296+0.0328406739))+G302*('Segments'!$D$32*G296*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*G295+0.4357405005*G295+0.0330936548*G296+0.0328406739))+G303*('Segments'!$D$33*G296*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*G295+0.4357405005*G295+0.0330936548*G296+0.0328406739))+G304*('Segments'!$D$34*G296*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*G295+0.4357405005*G295+0.0330936548*G296+0.0328406739))</f>
+        <f>G297*('Segments'!$D$27*G296*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*G296+0.4357405005*G296+0.0330936548*G296+0.0328406739))+G298*('Segments'!$D$28*G296*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*G296+0.4357405005*G296+0.0330936548*G296+0.0328406739))+G299*('Segments'!$D$29*G296*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*G296+0.4357405005*G296+0.0330936548*G296+0.0328406739))+G300*('Segments'!$D$30*G296*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*G296+0.4357405005*G296+0.0330936548*G296+0.0328406739))+G301*('Segments'!$D$31*G296*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*G296+0.4357405005*G296+0.0330936548*G296+0.0328406739))+G302*('Segments'!$D$32*G296*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*G296+0.4357405005*G296+0.0330936548*G296+0.0328406739))+G303*('Segments'!$D$33*G296*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*G296+0.4357405005*G296+0.0330936548*G296+0.0328406739))+G304*('Segments'!$D$34*G296*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*G296+0.4357405005*G296+0.0330936548*G296+0.0328406739))</f>
         <v/>
       </c>
     </row>
@@ -9806,23 +9806,23 @@
         </is>
       </c>
       <c r="C356" s="18">
-        <f>C346*('Segments'!$D$27*C345*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*C344+0.4357405005*C344+0.0330936548*C345+0.0328406739))+C347*('Segments'!$D$28*C345*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*C344+0.4357405005*C344+0.0330936548*C345+0.0328406739))+C348*('Segments'!$D$29*C345*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*C344+0.4357405005*C344+0.0330936548*C345+0.0328406739))+C349*('Segments'!$D$30*C345*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*C344+0.4357405005*C344+0.0330936548*C345+0.0328406739))+C350*('Segments'!$D$31*C345*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*C344+0.4357405005*C344+0.0330936548*C345+0.0328406739))+C351*('Segments'!$D$32*C345*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*C344+0.4357405005*C344+0.0330936548*C345+0.0328406739))+C352*('Segments'!$D$33*C345*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*C344+0.4357405005*C344+0.0330936548*C345+0.0328406739))+C353*('Segments'!$D$34*C345*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*C344+0.4357405005*C344+0.0330936548*C345+0.0328406739))</f>
+        <f>C346*('Segments'!$D$27*C345*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*C345+0.4357405005*C345+0.0330936548*C345+0.0328406739))+C347*('Segments'!$D$28*C345*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*C345+0.4357405005*C345+0.0330936548*C345+0.0328406739))+C348*('Segments'!$D$29*C345*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*C345+0.4357405005*C345+0.0330936548*C345+0.0328406739))+C349*('Segments'!$D$30*C345*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*C345+0.4357405005*C345+0.0330936548*C345+0.0328406739))+C350*('Segments'!$D$31*C345*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*C345+0.4357405005*C345+0.0330936548*C345+0.0328406739))+C351*('Segments'!$D$32*C345*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*C345+0.4357405005*C345+0.0330936548*C345+0.0328406739))+C352*('Segments'!$D$33*C345*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*C345+0.4357405005*C345+0.0330936548*C345+0.0328406739))+C353*('Segments'!$D$34*C345*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*C345+0.4357405005*C345+0.0330936548*C345+0.0328406739))</f>
         <v/>
       </c>
       <c r="D356" s="18">
-        <f>D346*('Segments'!$D$27*D345*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*D344+0.4357405005*D344+0.0330936548*D345+0.0328406739))+D347*('Segments'!$D$28*D345*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*D344+0.4357405005*D344+0.0330936548*D345+0.0328406739))+D348*('Segments'!$D$29*D345*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*D344+0.4357405005*D344+0.0330936548*D345+0.0328406739))+D349*('Segments'!$D$30*D345*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*D344+0.4357405005*D344+0.0330936548*D345+0.0328406739))+D350*('Segments'!$D$31*D345*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*D344+0.4357405005*D344+0.0330936548*D345+0.0328406739))+D351*('Segments'!$D$32*D345*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*D344+0.4357405005*D344+0.0330936548*D345+0.0328406739))+D352*('Segments'!$D$33*D345*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*D344+0.4357405005*D344+0.0330936548*D345+0.0328406739))+D353*('Segments'!$D$34*D345*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*D344+0.4357405005*D344+0.0330936548*D345+0.0328406739))</f>
+        <f>D346*('Segments'!$D$27*D345*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*D345+0.4357405005*D345+0.0330936548*D345+0.0328406739))+D347*('Segments'!$D$28*D345*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*D345+0.4357405005*D345+0.0330936548*D345+0.0328406739))+D348*('Segments'!$D$29*D345*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*D345+0.4357405005*D345+0.0330936548*D345+0.0328406739))+D349*('Segments'!$D$30*D345*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*D345+0.4357405005*D345+0.0330936548*D345+0.0328406739))+D350*('Segments'!$D$31*D345*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*D345+0.4357405005*D345+0.0330936548*D345+0.0328406739))+D351*('Segments'!$D$32*D345*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*D345+0.4357405005*D345+0.0330936548*D345+0.0328406739))+D352*('Segments'!$D$33*D345*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*D345+0.4357405005*D345+0.0330936548*D345+0.0328406739))+D353*('Segments'!$D$34*D345*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*D345+0.4357405005*D345+0.0330936548*D345+0.0328406739))</f>
         <v/>
       </c>
       <c r="E356" s="18">
-        <f>E346*('Segments'!$D$27*E345*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*E344+0.4357405005*E344+0.0330936548*E345+0.0328406739))+E347*('Segments'!$D$28*E345*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*E344+0.4357405005*E344+0.0330936548*E345+0.0328406739))+E348*('Segments'!$D$29*E345*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*E344+0.4357405005*E344+0.0330936548*E345+0.0328406739))+E349*('Segments'!$D$30*E345*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*E344+0.4357405005*E344+0.0330936548*E345+0.0328406739))+E350*('Segments'!$D$31*E345*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*E344+0.4357405005*E344+0.0330936548*E345+0.0328406739))+E351*('Segments'!$D$32*E345*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*E344+0.4357405005*E344+0.0330936548*E345+0.0328406739))+E352*('Segments'!$D$33*E345*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*E344+0.4357405005*E344+0.0330936548*E345+0.0328406739))+E353*('Segments'!$D$34*E345*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*E344+0.4357405005*E344+0.0330936548*E345+0.0328406739))</f>
+        <f>E346*('Segments'!$D$27*E345*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*E345+0.4357405005*E345+0.0330936548*E345+0.0328406739))+E347*('Segments'!$D$28*E345*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*E345+0.4357405005*E345+0.0330936548*E345+0.0328406739))+E348*('Segments'!$D$29*E345*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*E345+0.4357405005*E345+0.0330936548*E345+0.0328406739))+E349*('Segments'!$D$30*E345*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*E345+0.4357405005*E345+0.0330936548*E345+0.0328406739))+E350*('Segments'!$D$31*E345*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*E345+0.4357405005*E345+0.0330936548*E345+0.0328406739))+E351*('Segments'!$D$32*E345*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*E345+0.4357405005*E345+0.0330936548*E345+0.0328406739))+E352*('Segments'!$D$33*E345*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*E345+0.4357405005*E345+0.0330936548*E345+0.0328406739))+E353*('Segments'!$D$34*E345*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*E345+0.4357405005*E345+0.0330936548*E345+0.0328406739))</f>
         <v/>
       </c>
       <c r="F356" s="18">
-        <f>F346*('Segments'!$D$27*F345*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*F344+0.4357405005*F344+0.0330936548*F345+0.0328406739))+F347*('Segments'!$D$28*F345*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*F344+0.4357405005*F344+0.0330936548*F345+0.0328406739))+F348*('Segments'!$D$29*F345*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*F344+0.4357405005*F344+0.0330936548*F345+0.0328406739))+F349*('Segments'!$D$30*F345*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*F344+0.4357405005*F344+0.0330936548*F345+0.0328406739))+F350*('Segments'!$D$31*F345*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*F344+0.4357405005*F344+0.0330936548*F345+0.0328406739))+F351*('Segments'!$D$32*F345*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*F344+0.4357405005*F344+0.0330936548*F345+0.0328406739))+F352*('Segments'!$D$33*F345*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*F344+0.4357405005*F344+0.0330936548*F345+0.0328406739))+F353*('Segments'!$D$34*F345*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*F344+0.4357405005*F344+0.0330936548*F345+0.0328406739))</f>
+        <f>F346*('Segments'!$D$27*F345*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*F345+0.4357405005*F345+0.0330936548*F345+0.0328406739))+F347*('Segments'!$D$28*F345*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*F345+0.4357405005*F345+0.0330936548*F345+0.0328406739))+F348*('Segments'!$D$29*F345*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*F345+0.4357405005*F345+0.0330936548*F345+0.0328406739))+F349*('Segments'!$D$30*F345*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*F345+0.4357405005*F345+0.0330936548*F345+0.0328406739))+F350*('Segments'!$D$31*F345*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*F345+0.4357405005*F345+0.0330936548*F345+0.0328406739))+F351*('Segments'!$D$32*F345*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*F345+0.4357405005*F345+0.0330936548*F345+0.0328406739))+F352*('Segments'!$D$33*F345*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*F345+0.4357405005*F345+0.0330936548*F345+0.0328406739))+F353*('Segments'!$D$34*F345*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*F345+0.4357405005*F345+0.0330936548*F345+0.0328406739))</f>
         <v/>
       </c>
       <c r="G356" s="18">
-        <f>G346*('Segments'!$D$27*G345*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*G344+0.4357405005*G344+0.0330936548*G345+0.0328406739))+G347*('Segments'!$D$28*G345*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*G344+0.4357405005*G344+0.0330936548*G345+0.0328406739))+G348*('Segments'!$D$29*G345*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*G344+0.4357405005*G344+0.0330936548*G345+0.0328406739))+G349*('Segments'!$D$30*G345*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*G344+0.4357405005*G344+0.0330936548*G345+0.0328406739))+G350*('Segments'!$D$31*G345*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*G344+0.4357405005*G344+0.0330936548*G345+0.0328406739))+G351*('Segments'!$D$32*G345*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*G344+0.4357405005*G344+0.0330936548*G345+0.0328406739))+G352*('Segments'!$D$33*G345*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*G344+0.4357405005*G344+0.0330936548*G345+0.0328406739))+G353*('Segments'!$D$34*G345*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*G344+0.4357405005*G344+0.0330936548*G345+0.0328406739))</f>
+        <f>G346*('Segments'!$D$27*G345*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*G345+0.4357405005*G345+0.0330936548*G345+0.0328406739))+G347*('Segments'!$D$28*G345*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*G345+0.4357405005*G345+0.0330936548*G345+0.0328406739))+G348*('Segments'!$D$29*G345*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*G345+0.4357405005*G345+0.0330936548*G345+0.0328406739))+G349*('Segments'!$D$30*G345*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*G345+0.4357405005*G345+0.0330936548*G345+0.0328406739))+G350*('Segments'!$D$31*G345*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*G345+0.4357405005*G345+0.0330936548*G345+0.0328406739))+G351*('Segments'!$D$32*G345*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*G345+0.4357405005*G345+0.0330936548*G345+0.0328406739))+G352*('Segments'!$D$33*G345*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*G345+0.4357405005*G345+0.0330936548*G345+0.0328406739))+G353*('Segments'!$D$34*G345*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*G345+0.4357405005*G345+0.0330936548*G345+0.0328406739))</f>
         <v/>
       </c>
     </row>
@@ -10876,23 +10876,23 @@
         </is>
       </c>
       <c r="C405" s="18">
-        <f>C395*('Segments'!$D$27*C394*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*C393+0.4357405005*C393+0.0330936548*C394+0.0328406739))+C396*('Segments'!$D$28*C394*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*C393+0.4357405005*C393+0.0330936548*C394+0.0328406739))+C397*('Segments'!$D$29*C394*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*C393+0.4357405005*C393+0.0330936548*C394+0.0328406739))+C398*('Segments'!$D$30*C394*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*C393+0.4357405005*C393+0.0330936548*C394+0.0328406739))+C399*('Segments'!$D$31*C394*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*C393+0.4357405005*C393+0.0330936548*C394+0.0328406739))+C400*('Segments'!$D$32*C394*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*C393+0.4357405005*C393+0.0330936548*C394+0.0328406739))+C401*('Segments'!$D$33*C394*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*C393+0.4357405005*C393+0.0330936548*C394+0.0328406739))+C402*('Segments'!$D$34*C394*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*C393+0.4357405005*C393+0.0330936548*C394+0.0328406739))</f>
+        <f>C395*('Segments'!$D$27*C394*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*C394+0.4357405005*C394+0.0330936548*C394+0.0328406739))+C396*('Segments'!$D$28*C394*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*C394+0.4357405005*C394+0.0330936548*C394+0.0328406739))+C397*('Segments'!$D$29*C394*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*C394+0.4357405005*C394+0.0330936548*C394+0.0328406739))+C398*('Segments'!$D$30*C394*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*C394+0.4357405005*C394+0.0330936548*C394+0.0328406739))+C399*('Segments'!$D$31*C394*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*C394+0.4357405005*C394+0.0330936548*C394+0.0328406739))+C400*('Segments'!$D$32*C394*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*C394+0.4357405005*C394+0.0330936548*C394+0.0328406739))+C401*('Segments'!$D$33*C394*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*C394+0.4357405005*C394+0.0330936548*C394+0.0328406739))+C402*('Segments'!$D$34*C394*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*C394+0.4357405005*C394+0.0330936548*C394+0.0328406739))</f>
         <v/>
       </c>
       <c r="D405" s="18">
-        <f>D395*('Segments'!$D$27*D394*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*D393+0.4357405005*D393+0.0330936548*D394+0.0328406739))+D396*('Segments'!$D$28*D394*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*D393+0.4357405005*D393+0.0330936548*D394+0.0328406739))+D397*('Segments'!$D$29*D394*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*D393+0.4357405005*D393+0.0330936548*D394+0.0328406739))+D398*('Segments'!$D$30*D394*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*D393+0.4357405005*D393+0.0330936548*D394+0.0328406739))+D399*('Segments'!$D$31*D394*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*D393+0.4357405005*D393+0.0330936548*D394+0.0328406739))+D400*('Segments'!$D$32*D394*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*D393+0.4357405005*D393+0.0330936548*D394+0.0328406739))+D401*('Segments'!$D$33*D394*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*D393+0.4357405005*D393+0.0330936548*D394+0.0328406739))+D402*('Segments'!$D$34*D394*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*D393+0.4357405005*D393+0.0330936548*D394+0.0328406739))</f>
+        <f>D395*('Segments'!$D$27*D394*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*D394+0.4357405005*D394+0.0330936548*D394+0.0328406739))+D396*('Segments'!$D$28*D394*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*D394+0.4357405005*D394+0.0330936548*D394+0.0328406739))+D397*('Segments'!$D$29*D394*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*D394+0.4357405005*D394+0.0330936548*D394+0.0328406739))+D398*('Segments'!$D$30*D394*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*D394+0.4357405005*D394+0.0330936548*D394+0.0328406739))+D399*('Segments'!$D$31*D394*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*D394+0.4357405005*D394+0.0330936548*D394+0.0328406739))+D400*('Segments'!$D$32*D394*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*D394+0.4357405005*D394+0.0330936548*D394+0.0328406739))+D401*('Segments'!$D$33*D394*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*D394+0.4357405005*D394+0.0330936548*D394+0.0328406739))+D402*('Segments'!$D$34*D394*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*D394+0.4357405005*D394+0.0330936548*D394+0.0328406739))</f>
         <v/>
       </c>
       <c r="E405" s="18">
-        <f>E395*('Segments'!$D$27*E394*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*E393+0.4357405005*E393+0.0330936548*E394+0.0328406739))+E396*('Segments'!$D$28*E394*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*E393+0.4357405005*E393+0.0330936548*E394+0.0328406739))+E397*('Segments'!$D$29*E394*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*E393+0.4357405005*E393+0.0330936548*E394+0.0328406739))+E398*('Segments'!$D$30*E394*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*E393+0.4357405005*E393+0.0330936548*E394+0.0328406739))+E399*('Segments'!$D$31*E394*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*E393+0.4357405005*E393+0.0330936548*E394+0.0328406739))+E400*('Segments'!$D$32*E394*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*E393+0.4357405005*E393+0.0330936548*E394+0.0328406739))+E401*('Segments'!$D$33*E394*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*E393+0.4357405005*E393+0.0330936548*E394+0.0328406739))+E402*('Segments'!$D$34*E394*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*E393+0.4357405005*E393+0.0330936548*E394+0.0328406739))</f>
+        <f>E395*('Segments'!$D$27*E394*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*E394+0.4357405005*E394+0.0330936548*E394+0.0328406739))+E396*('Segments'!$D$28*E394*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*E394+0.4357405005*E394+0.0330936548*E394+0.0328406739))+E397*('Segments'!$D$29*E394*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*E394+0.4357405005*E394+0.0330936548*E394+0.0328406739))+E398*('Segments'!$D$30*E394*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*E394+0.4357405005*E394+0.0330936548*E394+0.0328406739))+E399*('Segments'!$D$31*E394*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*E394+0.4357405005*E394+0.0330936548*E394+0.0328406739))+E400*('Segments'!$D$32*E394*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*E394+0.4357405005*E394+0.0330936548*E394+0.0328406739))+E401*('Segments'!$D$33*E394*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*E394+0.4357405005*E394+0.0330936548*E394+0.0328406739))+E402*('Segments'!$D$34*E394*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*E394+0.4357405005*E394+0.0330936548*E394+0.0328406739))</f>
         <v/>
       </c>
       <c r="F405" s="18">
-        <f>F395*('Segments'!$D$27*F394*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*F393+0.4357405005*F393+0.0330936548*F394+0.0328406739))+F396*('Segments'!$D$28*F394*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*F393+0.4357405005*F393+0.0330936548*F394+0.0328406739))+F397*('Segments'!$D$29*F394*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*F393+0.4357405005*F393+0.0330936548*F394+0.0328406739))+F398*('Segments'!$D$30*F394*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*F393+0.4357405005*F393+0.0330936548*F394+0.0328406739))+F399*('Segments'!$D$31*F394*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*F393+0.4357405005*F393+0.0330936548*F394+0.0328406739))+F400*('Segments'!$D$32*F394*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*F393+0.4357405005*F393+0.0330936548*F394+0.0328406739))+F401*('Segments'!$D$33*F394*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*F393+0.4357405005*F393+0.0330936548*F394+0.0328406739))+F402*('Segments'!$D$34*F394*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*F393+0.4357405005*F393+0.0330936548*F394+0.0328406739))</f>
+        <f>F395*('Segments'!$D$27*F394*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*F394+0.4357405005*F394+0.0330936548*F394+0.0328406739))+F396*('Segments'!$D$28*F394*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*F394+0.4357405005*F394+0.0330936548*F394+0.0328406739))+F397*('Segments'!$D$29*F394*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*F394+0.4357405005*F394+0.0330936548*F394+0.0328406739))+F398*('Segments'!$D$30*F394*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*F394+0.4357405005*F394+0.0330936548*F394+0.0328406739))+F399*('Segments'!$D$31*F394*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*F394+0.4357405005*F394+0.0330936548*F394+0.0328406739))+F400*('Segments'!$D$32*F394*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*F394+0.4357405005*F394+0.0330936548*F394+0.0328406739))+F401*('Segments'!$D$33*F394*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*F394+0.4357405005*F394+0.0330936548*F394+0.0328406739))+F402*('Segments'!$D$34*F394*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*F394+0.4357405005*F394+0.0330936548*F394+0.0328406739))</f>
         <v/>
       </c>
       <c r="G405" s="18">
-        <f>G395*('Segments'!$D$27*G394*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*G393+0.4357405005*G393+0.0330936548*G394+0.0328406739))+G396*('Segments'!$D$28*G394*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*G393+0.4357405005*G393+0.0330936548*G394+0.0328406739))+G397*('Segments'!$D$29*G394*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*G393+0.4357405005*G393+0.0330936548*G394+0.0328406739))+G398*('Segments'!$D$30*G394*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*G393+0.4357405005*G393+0.0330936548*G394+0.0328406739))+G399*('Segments'!$D$31*G394*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*G393+0.4357405005*G393+0.0330936548*G394+0.0328406739))+G400*('Segments'!$D$32*G394*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*G393+0.4357405005*G393+0.0330936548*G394+0.0328406739))+G401*('Segments'!$D$33*G394*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*G393+0.4357405005*G393+0.0330936548*G394+0.0328406739))+G402*('Segments'!$D$34*G394*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*G393+0.4357405005*G393+0.0330936548*G394+0.0328406739))</f>
+        <f>G395*('Segments'!$D$27*G394*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*G394+0.4357405005*G394+0.0330936548*G394+0.0328406739))+G396*('Segments'!$D$28*G394*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*G394+0.4357405005*G394+0.0330936548*G394+0.0328406739))+G397*('Segments'!$D$29*G394*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*G394+0.4357405005*G394+0.0330936548*G394+0.0328406739))+G398*('Segments'!$D$30*G394*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*G394+0.4357405005*G394+0.0330936548*G394+0.0328406739))+G399*('Segments'!$D$31*G394*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*G394+0.4357405005*G394+0.0330936548*G394+0.0328406739))+G400*('Segments'!$D$32*G394*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*G394+0.4357405005*G394+0.0330936548*G394+0.0328406739))+G401*('Segments'!$D$33*G394*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*G394+0.4357405005*G394+0.0330936548*G394+0.0328406739))+G402*('Segments'!$D$34*G394*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*G394+0.4357405005*G394+0.0330936548*G394+0.0328406739))</f>
         <v/>
       </c>
     </row>
@@ -11946,23 +11946,23 @@
         </is>
       </c>
       <c r="C454" s="18">
-        <f>C444*('Segments'!$D$27*C443*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*C442+0.4357405005*C442+0.0330936548*C443+0.0328406739))+C445*('Segments'!$D$28*C443*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*C442+0.4357405005*C442+0.0330936548*C443+0.0328406739))+C446*('Segments'!$D$29*C443*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*C442+0.4357405005*C442+0.0330936548*C443+0.0328406739))+C447*('Segments'!$D$30*C443*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*C442+0.4357405005*C442+0.0330936548*C443+0.0328406739))+C448*('Segments'!$D$31*C443*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*C442+0.4357405005*C442+0.0330936548*C443+0.0328406739))+C449*('Segments'!$D$32*C443*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*C442+0.4357405005*C442+0.0330936548*C443+0.0328406739))+C450*('Segments'!$D$33*C443*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*C442+0.4357405005*C442+0.0330936548*C443+0.0328406739))+C451*('Segments'!$D$34*C443*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*C442+0.4357405005*C442+0.0330936548*C443+0.0328406739))</f>
+        <f>C444*('Segments'!$D$27*C443*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*C443+0.4357405005*C443+0.0330936548*C443+0.0328406739))+C445*('Segments'!$D$28*C443*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*C443+0.4357405005*C443+0.0330936548*C443+0.0328406739))+C446*('Segments'!$D$29*C443*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*C443+0.4357405005*C443+0.0330936548*C443+0.0328406739))+C447*('Segments'!$D$30*C443*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*C443+0.4357405005*C443+0.0330936548*C443+0.0328406739))+C448*('Segments'!$D$31*C443*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*C443+0.4357405005*C443+0.0330936548*C443+0.0328406739))+C449*('Segments'!$D$32*C443*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*C443+0.4357405005*C443+0.0330936548*C443+0.0328406739))+C450*('Segments'!$D$33*C443*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*C443+0.4357405005*C443+0.0330936548*C443+0.0328406739))+C451*('Segments'!$D$34*C443*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*C443+0.4357405005*C443+0.0330936548*C443+0.0328406739))</f>
         <v/>
       </c>
       <c r="D454" s="18">
-        <f>D444*('Segments'!$D$27*D443*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*D442+0.4357405005*D442+0.0330936548*D443+0.0328406739))+D445*('Segments'!$D$28*D443*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*D442+0.4357405005*D442+0.0330936548*D443+0.0328406739))+D446*('Segments'!$D$29*D443*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*D442+0.4357405005*D442+0.0330936548*D443+0.0328406739))+D447*('Segments'!$D$30*D443*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*D442+0.4357405005*D442+0.0330936548*D443+0.0328406739))+D448*('Segments'!$D$31*D443*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*D442+0.4357405005*D442+0.0330936548*D443+0.0328406739))+D449*('Segments'!$D$32*D443*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*D442+0.4357405005*D442+0.0330936548*D443+0.0328406739))+D450*('Segments'!$D$33*D443*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*D442+0.4357405005*D442+0.0330936548*D443+0.0328406739))+D451*('Segments'!$D$34*D443*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*D442+0.4357405005*D442+0.0330936548*D443+0.0328406739))</f>
+        <f>D444*('Segments'!$D$27*D443*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*D443+0.4357405005*D443+0.0330936548*D443+0.0328406739))+D445*('Segments'!$D$28*D443*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*D443+0.4357405005*D443+0.0330936548*D443+0.0328406739))+D446*('Segments'!$D$29*D443*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*D443+0.4357405005*D443+0.0330936548*D443+0.0328406739))+D447*('Segments'!$D$30*D443*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*D443+0.4357405005*D443+0.0330936548*D443+0.0328406739))+D448*('Segments'!$D$31*D443*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*D443+0.4357405005*D443+0.0330936548*D443+0.0328406739))+D449*('Segments'!$D$32*D443*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*D443+0.4357405005*D443+0.0330936548*D443+0.0328406739))+D450*('Segments'!$D$33*D443*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*D443+0.4357405005*D443+0.0330936548*D443+0.0328406739))+D451*('Segments'!$D$34*D443*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*D443+0.4357405005*D443+0.0330936548*D443+0.0328406739))</f>
         <v/>
       </c>
       <c r="E454" s="18">
-        <f>E444*('Segments'!$D$27*E443*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*E442+0.4357405005*E442+0.0330936548*E443+0.0328406739))+E445*('Segments'!$D$28*E443*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*E442+0.4357405005*E442+0.0330936548*E443+0.0328406739))+E446*('Segments'!$D$29*E443*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*E442+0.4357405005*E442+0.0330936548*E443+0.0328406739))+E447*('Segments'!$D$30*E443*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*E442+0.4357405005*E442+0.0330936548*E443+0.0328406739))+E448*('Segments'!$D$31*E443*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*E442+0.4357405005*E442+0.0330936548*E443+0.0328406739))+E449*('Segments'!$D$32*E443*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*E442+0.4357405005*E442+0.0330936548*E443+0.0328406739))+E450*('Segments'!$D$33*E443*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*E442+0.4357405005*E442+0.0330936548*E443+0.0328406739))+E451*('Segments'!$D$34*E443*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*E442+0.4357405005*E442+0.0330936548*E443+0.0328406739))</f>
+        <f>E444*('Segments'!$D$27*E443*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*E443+0.4357405005*E443+0.0330936548*E443+0.0328406739))+E445*('Segments'!$D$28*E443*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*E443+0.4357405005*E443+0.0330936548*E443+0.0328406739))+E446*('Segments'!$D$29*E443*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*E443+0.4357405005*E443+0.0330936548*E443+0.0328406739))+E447*('Segments'!$D$30*E443*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*E443+0.4357405005*E443+0.0330936548*E443+0.0328406739))+E448*('Segments'!$D$31*E443*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*E443+0.4357405005*E443+0.0330936548*E443+0.0328406739))+E449*('Segments'!$D$32*E443*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*E443+0.4357405005*E443+0.0330936548*E443+0.0328406739))+E450*('Segments'!$D$33*E443*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*E443+0.4357405005*E443+0.0330936548*E443+0.0328406739))+E451*('Segments'!$D$34*E443*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*E443+0.4357405005*E443+0.0330936548*E443+0.0328406739))</f>
         <v/>
       </c>
       <c r="F454" s="18">
-        <f>F444*('Segments'!$D$27*F443*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*F442+0.4357405005*F442+0.0330936548*F443+0.0328406739))+F445*('Segments'!$D$28*F443*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*F442+0.4357405005*F442+0.0330936548*F443+0.0328406739))+F446*('Segments'!$D$29*F443*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*F442+0.4357405005*F442+0.0330936548*F443+0.0328406739))+F447*('Segments'!$D$30*F443*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*F442+0.4357405005*F442+0.0330936548*F443+0.0328406739))+F448*('Segments'!$D$31*F443*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*F442+0.4357405005*F442+0.0330936548*F443+0.0328406739))+F449*('Segments'!$D$32*F443*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*F442+0.4357405005*F442+0.0330936548*F443+0.0328406739))+F450*('Segments'!$D$33*F443*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*F442+0.4357405005*F442+0.0330936548*F443+0.0328406739))+F451*('Segments'!$D$34*F443*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*F442+0.4357405005*F442+0.0330936548*F443+0.0328406739))</f>
+        <f>F444*('Segments'!$D$27*F443*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*F443+0.4357405005*F443+0.0330936548*F443+0.0328406739))+F445*('Segments'!$D$28*F443*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*F443+0.4357405005*F443+0.0330936548*F443+0.0328406739))+F446*('Segments'!$D$29*F443*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*F443+0.4357405005*F443+0.0330936548*F443+0.0328406739))+F447*('Segments'!$D$30*F443*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*F443+0.4357405005*F443+0.0330936548*F443+0.0328406739))+F448*('Segments'!$D$31*F443*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*F443+0.4357405005*F443+0.0330936548*F443+0.0328406739))+F449*('Segments'!$D$32*F443*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*F443+0.4357405005*F443+0.0330936548*F443+0.0328406739))+F450*('Segments'!$D$33*F443*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*F443+0.4357405005*F443+0.0330936548*F443+0.0328406739))+F451*('Segments'!$D$34*F443*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*F443+0.4357405005*F443+0.0330936548*F443+0.0328406739))</f>
         <v/>
       </c>
       <c r="G454" s="18">
-        <f>G444*('Segments'!$D$27*G443*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*G442+0.4357405005*G442+0.0330936548*G443+0.0328406739))+G445*('Segments'!$D$28*G443*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*G442+0.4357405005*G442+0.0330936548*G443+0.0328406739))+G446*('Segments'!$D$29*G443*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*G442+0.4357405005*G442+0.0330936548*G443+0.0328406739))+G447*('Segments'!$D$30*G443*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*G442+0.4357405005*G442+0.0330936548*G443+0.0328406739))+G448*('Segments'!$D$31*G443*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*G442+0.4357405005*G442+0.0330936548*G443+0.0328406739))+G449*('Segments'!$D$32*G443*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*G442+0.4357405005*G442+0.0330936548*G443+0.0328406739))+G450*('Segments'!$D$33*G443*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*G442+0.4357405005*G442+0.0330936548*G443+0.0328406739))+G451*('Segments'!$D$34*G443*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*G442+0.4357405005*G442+0.0330936548*G443+0.0328406739))</f>
+        <f>G444*('Segments'!$D$27*G443*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*G443+0.4357405005*G443+0.0330936548*G443+0.0328406739))+G445*('Segments'!$D$28*G443*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*G443+0.4357405005*G443+0.0330936548*G443+0.0328406739))+G446*('Segments'!$D$29*G443*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*G443+0.4357405005*G443+0.0330936548*G443+0.0328406739))+G447*('Segments'!$D$30*G443*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*G443+0.4357405005*G443+0.0330936548*G443+0.0328406739))+G448*('Segments'!$D$31*G443*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*G443+0.4357405005*G443+0.0330936548*G443+0.0328406739))+G449*('Segments'!$D$32*G443*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*G443+0.4357405005*G443+0.0330936548*G443+0.0328406739))+G450*('Segments'!$D$33*G443*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*G443+0.4357405005*G443+0.0330936548*G443+0.0328406739))+G451*('Segments'!$D$34*G443*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*G443+0.4357405005*G443+0.0330936548*G443+0.0328406739))</f>
         <v/>
       </c>
     </row>
@@ -13016,23 +13016,23 @@
         </is>
       </c>
       <c r="C503" s="18">
-        <f>C493*('Segments'!$D$27*C492*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*C491+0.4357405005*C491+0.0330936548*C492+0.0328406739))+C494*('Segments'!$D$28*C492*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*C491+0.4357405005*C491+0.0330936548*C492+0.0328406739))+C495*('Segments'!$D$29*C492*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*C491+0.4357405005*C491+0.0330936548*C492+0.0328406739))+C496*('Segments'!$D$30*C492*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*C491+0.4357405005*C491+0.0330936548*C492+0.0328406739))+C497*('Segments'!$D$31*C492*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*C491+0.4357405005*C491+0.0330936548*C492+0.0328406739))+C498*('Segments'!$D$32*C492*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*C491+0.4357405005*C491+0.0330936548*C492+0.0328406739))+C499*('Segments'!$D$33*C492*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*C491+0.4357405005*C491+0.0330936548*C492+0.0328406739))+C500*('Segments'!$D$34*C492*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*C491+0.4357405005*C491+0.0330936548*C492+0.0328406739))</f>
+        <f>C493*('Segments'!$D$27*C492*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*C492+0.4357405005*C492+0.0330936548*C492+0.0328406739))+C494*('Segments'!$D$28*C492*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*C492+0.4357405005*C492+0.0330936548*C492+0.0328406739))+C495*('Segments'!$D$29*C492*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*C492+0.4357405005*C492+0.0330936548*C492+0.0328406739))+C496*('Segments'!$D$30*C492*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*C492+0.4357405005*C492+0.0330936548*C492+0.0328406739))+C497*('Segments'!$D$31*C492*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*C492+0.4357405005*C492+0.0330936548*C492+0.0328406739))+C498*('Segments'!$D$32*C492*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*C492+0.4357405005*C492+0.0330936548*C492+0.0328406739))+C499*('Segments'!$D$33*C492*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*C492+0.4357405005*C492+0.0330936548*C492+0.0328406739))+C500*('Segments'!$D$34*C492*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*C492+0.4357405005*C492+0.0330936548*C492+0.0328406739))</f>
         <v/>
       </c>
       <c r="D503" s="18">
-        <f>D493*('Segments'!$D$27*D492*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*D491+0.4357405005*D491+0.0330936548*D492+0.0328406739))+D494*('Segments'!$D$28*D492*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*D491+0.4357405005*D491+0.0330936548*D492+0.0328406739))+D495*('Segments'!$D$29*D492*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*D491+0.4357405005*D491+0.0330936548*D492+0.0328406739))+D496*('Segments'!$D$30*D492*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*D491+0.4357405005*D491+0.0330936548*D492+0.0328406739))+D497*('Segments'!$D$31*D492*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*D491+0.4357405005*D491+0.0330936548*D492+0.0328406739))+D498*('Segments'!$D$32*D492*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*D491+0.4357405005*D491+0.0330936548*D492+0.0328406739))+D499*('Segments'!$D$33*D492*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*D491+0.4357405005*D491+0.0330936548*D492+0.0328406739))+D500*('Segments'!$D$34*D492*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*D491+0.4357405005*D491+0.0330936548*D492+0.0328406739))</f>
+        <f>D493*('Segments'!$D$27*D492*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*D492+0.4357405005*D492+0.0330936548*D492+0.0328406739))+D494*('Segments'!$D$28*D492*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*D492+0.4357405005*D492+0.0330936548*D492+0.0328406739))+D495*('Segments'!$D$29*D492*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*D492+0.4357405005*D492+0.0330936548*D492+0.0328406739))+D496*('Segments'!$D$30*D492*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*D492+0.4357405005*D492+0.0330936548*D492+0.0328406739))+D497*('Segments'!$D$31*D492*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*D492+0.4357405005*D492+0.0330936548*D492+0.0328406739))+D498*('Segments'!$D$32*D492*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*D492+0.4357405005*D492+0.0330936548*D492+0.0328406739))+D499*('Segments'!$D$33*D492*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*D492+0.4357405005*D492+0.0330936548*D492+0.0328406739))+D500*('Segments'!$D$34*D492*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*D492+0.4357405005*D492+0.0330936548*D492+0.0328406739))</f>
         <v/>
       </c>
       <c r="E503" s="18">
-        <f>E493*('Segments'!$D$27*E492*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*E491+0.4357405005*E491+0.0330936548*E492+0.0328406739))+E494*('Segments'!$D$28*E492*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*E491+0.4357405005*E491+0.0330936548*E492+0.0328406739))+E495*('Segments'!$D$29*E492*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*E491+0.4357405005*E491+0.0330936548*E492+0.0328406739))+E496*('Segments'!$D$30*E492*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*E491+0.4357405005*E491+0.0330936548*E492+0.0328406739))+E497*('Segments'!$D$31*E492*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*E491+0.4357405005*E491+0.0330936548*E492+0.0328406739))+E498*('Segments'!$D$32*E492*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*E491+0.4357405005*E491+0.0330936548*E492+0.0328406739))+E499*('Segments'!$D$33*E492*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*E491+0.4357405005*E491+0.0330936548*E492+0.0328406739))+E500*('Segments'!$D$34*E492*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*E491+0.4357405005*E491+0.0330936548*E492+0.0328406739))</f>
+        <f>E493*('Segments'!$D$27*E492*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*E492+0.4357405005*E492+0.0330936548*E492+0.0328406739))+E494*('Segments'!$D$28*E492*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*E492+0.4357405005*E492+0.0330936548*E492+0.0328406739))+E495*('Segments'!$D$29*E492*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*E492+0.4357405005*E492+0.0330936548*E492+0.0328406739))+E496*('Segments'!$D$30*E492*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*E492+0.4357405005*E492+0.0330936548*E492+0.0328406739))+E497*('Segments'!$D$31*E492*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*E492+0.4357405005*E492+0.0330936548*E492+0.0328406739))+E498*('Segments'!$D$32*E492*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*E492+0.4357405005*E492+0.0330936548*E492+0.0328406739))+E499*('Segments'!$D$33*E492*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*E492+0.4357405005*E492+0.0330936548*E492+0.0328406739))+E500*('Segments'!$D$34*E492*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*E492+0.4357405005*E492+0.0330936548*E492+0.0328406739))</f>
         <v/>
       </c>
       <c r="F503" s="18">
-        <f>F493*('Segments'!$D$27*F492*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*F491+0.4357405005*F491+0.0330936548*F492+0.0328406739))+F494*('Segments'!$D$28*F492*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*F491+0.4357405005*F491+0.0330936548*F492+0.0328406739))+F495*('Segments'!$D$29*F492*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*F491+0.4357405005*F491+0.0330936548*F492+0.0328406739))+F496*('Segments'!$D$30*F492*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*F491+0.4357405005*F491+0.0330936548*F492+0.0328406739))+F497*('Segments'!$D$31*F492*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*F491+0.4357405005*F491+0.0330936548*F492+0.0328406739))+F498*('Segments'!$D$32*F492*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*F491+0.4357405005*F491+0.0330936548*F492+0.0328406739))+F499*('Segments'!$D$33*F492*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*F491+0.4357405005*F491+0.0330936548*F492+0.0328406739))+F500*('Segments'!$D$34*F492*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*F491+0.4357405005*F491+0.0330936548*F492+0.0328406739))</f>
+        <f>F493*('Segments'!$D$27*F492*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*F492+0.4357405005*F492+0.0330936548*F492+0.0328406739))+F494*('Segments'!$D$28*F492*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*F492+0.4357405005*F492+0.0330936548*F492+0.0328406739))+F495*('Segments'!$D$29*F492*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*F492+0.4357405005*F492+0.0330936548*F492+0.0328406739))+F496*('Segments'!$D$30*F492*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*F492+0.4357405005*F492+0.0330936548*F492+0.0328406739))+F497*('Segments'!$D$31*F492*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*F492+0.4357405005*F492+0.0330936548*F492+0.0328406739))+F498*('Segments'!$D$32*F492*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*F492+0.4357405005*F492+0.0330936548*F492+0.0328406739))+F499*('Segments'!$D$33*F492*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*F492+0.4357405005*F492+0.0330936548*F492+0.0328406739))+F500*('Segments'!$D$34*F492*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*F492+0.4357405005*F492+0.0330936548*F492+0.0328406739))</f>
         <v/>
       </c>
       <c r="G503" s="18">
-        <f>G493*('Segments'!$D$27*G492*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*G491+0.4357405005*G491+0.0330936548*G492+0.0328406739))+G494*('Segments'!$D$28*G492*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*G491+0.4357405005*G491+0.0330936548*G492+0.0328406739))+G495*('Segments'!$D$29*G492*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*G491+0.4357405005*G491+0.0330936548*G492+0.0328406739))+G496*('Segments'!$D$30*G492*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*G491+0.4357405005*G491+0.0330936548*G492+0.0328406739))+G497*('Segments'!$D$31*G492*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*G491+0.4357405005*G491+0.0330936548*G492+0.0328406739))+G498*('Segments'!$D$32*G492*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*G491+0.4357405005*G491+0.0330936548*G492+0.0328406739))+G499*('Segments'!$D$33*G492*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*G491+0.4357405005*G491+0.0330936548*G492+0.0328406739))+G500*('Segments'!$D$34*G492*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*G491+0.4357405005*G491+0.0330936548*G492+0.0328406739))</f>
+        <f>G493*('Segments'!$D$27*G492*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*G492+0.4357405005*G492+0.0330936548*G492+0.0328406739))+G494*('Segments'!$D$28*G492*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*G492+0.4357405005*G492+0.0330936548*G492+0.0328406739))+G495*('Segments'!$D$29*G492*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*G492+0.4357405005*G492+0.0330936548*G492+0.0328406739))+G496*('Segments'!$D$30*G492*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*G492+0.4357405005*G492+0.0330936548*G492+0.0328406739))+G497*('Segments'!$D$31*G492*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*G492+0.4357405005*G492+0.0330936548*G492+0.0328406739))+G498*('Segments'!$D$32*G492*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*G492+0.4357405005*G492+0.0330936548*G492+0.0328406739))+G499*('Segments'!$D$33*G492*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*G492+0.4357405005*G492+0.0330936548*G492+0.0328406739))+G500*('Segments'!$D$34*G492*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*G492+0.4357405005*G492+0.0330936548*G492+0.0328406739))</f>
         <v/>
       </c>
     </row>
@@ -14086,23 +14086,23 @@
         </is>
       </c>
       <c r="C552" s="18">
-        <f>C542*('Segments'!$D$27*C541*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*C540+0.4357405005*C540+0.0330936548*C541+0.0328406739))+C543*('Segments'!$D$28*C541*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*C540+0.4357405005*C540+0.0330936548*C541+0.0328406739))+C544*('Segments'!$D$29*C541*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*C540+0.4357405005*C540+0.0330936548*C541+0.0328406739))+C545*('Segments'!$D$30*C541*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*C540+0.4357405005*C540+0.0330936548*C541+0.0328406739))+C546*('Segments'!$D$31*C541*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*C540+0.4357405005*C540+0.0330936548*C541+0.0328406739))+C547*('Segments'!$D$32*C541*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*C540+0.4357405005*C540+0.0330936548*C541+0.0328406739))+C548*('Segments'!$D$33*C541*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*C540+0.4357405005*C540+0.0330936548*C541+0.0328406739))+C549*('Segments'!$D$34*C541*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*C540+0.4357405005*C540+0.0330936548*C541+0.0328406739))</f>
+        <f>C542*('Segments'!$D$27*C541*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*C541+0.4357405005*C541+0.0330936548*C541+0.0328406739))+C543*('Segments'!$D$28*C541*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*C541+0.4357405005*C541+0.0330936548*C541+0.0328406739))+C544*('Segments'!$D$29*C541*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*C541+0.4357405005*C541+0.0330936548*C541+0.0328406739))+C545*('Segments'!$D$30*C541*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*C541+0.4357405005*C541+0.0330936548*C541+0.0328406739))+C546*('Segments'!$D$31*C541*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*C541+0.4357405005*C541+0.0330936548*C541+0.0328406739))+C547*('Segments'!$D$32*C541*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*C541+0.4357405005*C541+0.0330936548*C541+0.0328406739))+C548*('Segments'!$D$33*C541*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*C541+0.4357405005*C541+0.0330936548*C541+0.0328406739))+C549*('Segments'!$D$34*C541*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*C541+0.4357405005*C541+0.0330936548*C541+0.0328406739))</f>
         <v/>
       </c>
       <c r="D552" s="18">
-        <f>D542*('Segments'!$D$27*D541*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*D540+0.4357405005*D540+0.0330936548*D541+0.0328406739))+D543*('Segments'!$D$28*D541*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*D540+0.4357405005*D540+0.0330936548*D541+0.0328406739))+D544*('Segments'!$D$29*D541*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*D540+0.4357405005*D540+0.0330936548*D541+0.0328406739))+D545*('Segments'!$D$30*D541*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*D540+0.4357405005*D540+0.0330936548*D541+0.0328406739))+D546*('Segments'!$D$31*D541*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*D540+0.4357405005*D540+0.0330936548*D541+0.0328406739))+D547*('Segments'!$D$32*D541*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*D540+0.4357405005*D540+0.0330936548*D541+0.0328406739))+D548*('Segments'!$D$33*D541*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*D540+0.4357405005*D540+0.0330936548*D541+0.0328406739))+D549*('Segments'!$D$34*D541*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*D540+0.4357405005*D540+0.0330936548*D541+0.0328406739))</f>
+        <f>D542*('Segments'!$D$27*D541*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*D541+0.4357405005*D541+0.0330936548*D541+0.0328406739))+D543*('Segments'!$D$28*D541*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*D541+0.4357405005*D541+0.0330936548*D541+0.0328406739))+D544*('Segments'!$D$29*D541*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*D541+0.4357405005*D541+0.0330936548*D541+0.0328406739))+D545*('Segments'!$D$30*D541*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*D541+0.4357405005*D541+0.0330936548*D541+0.0328406739))+D546*('Segments'!$D$31*D541*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*D541+0.4357405005*D541+0.0330936548*D541+0.0328406739))+D547*('Segments'!$D$32*D541*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*D541+0.4357405005*D541+0.0330936548*D541+0.0328406739))+D548*('Segments'!$D$33*D541*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*D541+0.4357405005*D541+0.0330936548*D541+0.0328406739))+D549*('Segments'!$D$34*D541*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*D541+0.4357405005*D541+0.0330936548*D541+0.0328406739))</f>
         <v/>
       </c>
       <c r="E552" s="18">
-        <f>E542*('Segments'!$D$27*E541*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*E540+0.4357405005*E540+0.0330936548*E541+0.0328406739))+E543*('Segments'!$D$28*E541*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*E540+0.4357405005*E540+0.0330936548*E541+0.0328406739))+E544*('Segments'!$D$29*E541*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*E540+0.4357405005*E540+0.0330936548*E541+0.0328406739))+E545*('Segments'!$D$30*E541*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*E540+0.4357405005*E540+0.0330936548*E541+0.0328406739))+E546*('Segments'!$D$31*E541*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*E540+0.4357405005*E540+0.0330936548*E541+0.0328406739))+E547*('Segments'!$D$32*E541*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*E540+0.4357405005*E540+0.0330936548*E541+0.0328406739))+E548*('Segments'!$D$33*E541*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*E540+0.4357405005*E540+0.0330936548*E541+0.0328406739))+E549*('Segments'!$D$34*E541*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*E540+0.4357405005*E540+0.0330936548*E541+0.0328406739))</f>
+        <f>E542*('Segments'!$D$27*E541*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*E541+0.4357405005*E541+0.0330936548*E541+0.0328406739))+E543*('Segments'!$D$28*E541*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*E541+0.4357405005*E541+0.0330936548*E541+0.0328406739))+E544*('Segments'!$D$29*E541*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*E541+0.4357405005*E541+0.0330936548*E541+0.0328406739))+E545*('Segments'!$D$30*E541*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*E541+0.4357405005*E541+0.0330936548*E541+0.0328406739))+E546*('Segments'!$D$31*E541*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*E541+0.4357405005*E541+0.0330936548*E541+0.0328406739))+E547*('Segments'!$D$32*E541*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*E541+0.4357405005*E541+0.0330936548*E541+0.0328406739))+E548*('Segments'!$D$33*E541*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*E541+0.4357405005*E541+0.0330936548*E541+0.0328406739))+E549*('Segments'!$D$34*E541*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*E541+0.4357405005*E541+0.0330936548*E541+0.0328406739))</f>
         <v/>
       </c>
       <c r="F552" s="18">
-        <f>F542*('Segments'!$D$27*F541*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*F540+0.4357405005*F540+0.0330936548*F541+0.0328406739))+F543*('Segments'!$D$28*F541*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*F540+0.4357405005*F540+0.0330936548*F541+0.0328406739))+F544*('Segments'!$D$29*F541*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*F540+0.4357405005*F540+0.0330936548*F541+0.0328406739))+F545*('Segments'!$D$30*F541*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*F540+0.4357405005*F540+0.0330936548*F541+0.0328406739))+F546*('Segments'!$D$31*F541*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*F540+0.4357405005*F540+0.0330936548*F541+0.0328406739))+F547*('Segments'!$D$32*F541*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*F540+0.4357405005*F540+0.0330936548*F541+0.0328406739))+F548*('Segments'!$D$33*F541*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*F540+0.4357405005*F540+0.0330936548*F541+0.0328406739))+F549*('Segments'!$D$34*F541*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*F540+0.4357405005*F540+0.0330936548*F541+0.0328406739))</f>
+        <f>F542*('Segments'!$D$27*F541*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*F541+0.4357405005*F541+0.0330936548*F541+0.0328406739))+F543*('Segments'!$D$28*F541*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*F541+0.4357405005*F541+0.0330936548*F541+0.0328406739))+F544*('Segments'!$D$29*F541*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*F541+0.4357405005*F541+0.0330936548*F541+0.0328406739))+F545*('Segments'!$D$30*F541*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*F541+0.4357405005*F541+0.0330936548*F541+0.0328406739))+F546*('Segments'!$D$31*F541*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*F541+0.4357405005*F541+0.0330936548*F541+0.0328406739))+F547*('Segments'!$D$32*F541*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*F541+0.4357405005*F541+0.0330936548*F541+0.0328406739))+F548*('Segments'!$D$33*F541*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*F541+0.4357405005*F541+0.0330936548*F541+0.0328406739))+F549*('Segments'!$D$34*F541*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*F541+0.4357405005*F541+0.0330936548*F541+0.0328406739))</f>
         <v/>
       </c>
       <c r="G552" s="18">
-        <f>G542*('Segments'!$D$27*G541*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*G540+0.4357405005*G540+0.0330936548*G541+0.0328406739))+G543*('Segments'!$D$28*G541*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*G540+0.4357405005*G540+0.0330936548*G541+0.0328406739))+G544*('Segments'!$D$29*G541*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*G540+0.4357405005*G540+0.0330936548*G541+0.0328406739))+G545*('Segments'!$D$30*G541*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*G540+0.4357405005*G540+0.0330936548*G541+0.0328406739))+G546*('Segments'!$D$31*G541*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*G540+0.4357405005*G540+0.0330936548*G541+0.0328406739))+G547*('Segments'!$D$32*G541*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*G540+0.4357405005*G540+0.0330936548*G541+0.0328406739))+G548*('Segments'!$D$33*G541*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*G540+0.4357405005*G540+0.0330936548*G541+0.0328406739))+G549*('Segments'!$D$34*G541*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*G540+0.4357405005*G540+0.0330936548*G541+0.0328406739))</f>
+        <f>G542*('Segments'!$D$27*G541*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*G541+0.4357405005*G541+0.0330936548*G541+0.0328406739))+G543*('Segments'!$D$28*G541*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*G541+0.4357405005*G541+0.0330936548*G541+0.0328406739))+G544*('Segments'!$D$29*G541*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*G541+0.4357405005*G541+0.0330936548*G541+0.0328406739))+G545*('Segments'!$D$30*G541*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*G541+0.4357405005*G541+0.0330936548*G541+0.0328406739))+G546*('Segments'!$D$31*G541*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*G541+0.4357405005*G541+0.0330936548*G541+0.0328406739))+G547*('Segments'!$D$32*G541*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*G541+0.4357405005*G541+0.0330936548*G541+0.0328406739))+G548*('Segments'!$D$33*G541*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*G541+0.4357405005*G541+0.0330936548*G541+0.0328406739))+G549*('Segments'!$D$34*G541*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*G541+0.4357405005*G541+0.0330936548*G541+0.0328406739))</f>
         <v/>
       </c>
     </row>
@@ -15156,23 +15156,23 @@
         </is>
       </c>
       <c r="C601" s="18">
-        <f>C591*('Segments'!$D$27*C590*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*C589+0.4357405005*C589+0.0330936548*C590+0.0328406739))+C592*('Segments'!$D$28*C590*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*C589+0.4357405005*C589+0.0330936548*C590+0.0328406739))+C593*('Segments'!$D$29*C590*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*C589+0.4357405005*C589+0.0330936548*C590+0.0328406739))+C594*('Segments'!$D$30*C590*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*C589+0.4357405005*C589+0.0330936548*C590+0.0328406739))+C595*('Segments'!$D$31*C590*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*C589+0.4357405005*C589+0.0330936548*C590+0.0328406739))+C596*('Segments'!$D$32*C590*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*C589+0.4357405005*C589+0.0330936548*C590+0.0328406739))+C597*('Segments'!$D$33*C590*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*C589+0.4357405005*C589+0.0330936548*C590+0.0328406739))+C598*('Segments'!$D$34*C590*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*C589+0.4357405005*C589+0.0330936548*C590+0.0328406739))</f>
+        <f>C591*('Segments'!$D$27*C590*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*C590+0.4357405005*C590+0.0330936548*C590+0.0328406739))+C592*('Segments'!$D$28*C590*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*C590+0.4357405005*C590+0.0330936548*C590+0.0328406739))+C593*('Segments'!$D$29*C590*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*C590+0.4357405005*C590+0.0330936548*C590+0.0328406739))+C594*('Segments'!$D$30*C590*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*C590+0.4357405005*C590+0.0330936548*C590+0.0328406739))+C595*('Segments'!$D$31*C590*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*C590+0.4357405005*C590+0.0330936548*C590+0.0328406739))+C596*('Segments'!$D$32*C590*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*C590+0.4357405005*C590+0.0330936548*C590+0.0328406739))+C597*('Segments'!$D$33*C590*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*C590+0.4357405005*C590+0.0330936548*C590+0.0328406739))+C598*('Segments'!$D$34*C590*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*C590+0.4357405005*C590+0.0330936548*C590+0.0328406739))</f>
         <v/>
       </c>
       <c r="D601" s="18">
-        <f>D591*('Segments'!$D$27*D590*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*D589+0.4357405005*D589+0.0330936548*D590+0.0328406739))+D592*('Segments'!$D$28*D590*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*D589+0.4357405005*D589+0.0330936548*D590+0.0328406739))+D593*('Segments'!$D$29*D590*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*D589+0.4357405005*D589+0.0330936548*D590+0.0328406739))+D594*('Segments'!$D$30*D590*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*D589+0.4357405005*D589+0.0330936548*D590+0.0328406739))+D595*('Segments'!$D$31*D590*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*D589+0.4357405005*D589+0.0330936548*D590+0.0328406739))+D596*('Segments'!$D$32*D590*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*D589+0.4357405005*D589+0.0330936548*D590+0.0328406739))+D597*('Segments'!$D$33*D590*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*D589+0.4357405005*D589+0.0330936548*D590+0.0328406739))+D598*('Segments'!$D$34*D590*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*D589+0.4357405005*D589+0.0330936548*D590+0.0328406739))</f>
+        <f>D591*('Segments'!$D$27*D590*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*D590+0.4357405005*D590+0.0330936548*D590+0.0328406739))+D592*('Segments'!$D$28*D590*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*D590+0.4357405005*D590+0.0330936548*D590+0.0328406739))+D593*('Segments'!$D$29*D590*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*D590+0.4357405005*D590+0.0330936548*D590+0.0328406739))+D594*('Segments'!$D$30*D590*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*D590+0.4357405005*D590+0.0330936548*D590+0.0328406739))+D595*('Segments'!$D$31*D590*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*D590+0.4357405005*D590+0.0330936548*D590+0.0328406739))+D596*('Segments'!$D$32*D590*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*D590+0.4357405005*D590+0.0330936548*D590+0.0328406739))+D597*('Segments'!$D$33*D590*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*D590+0.4357405005*D590+0.0330936548*D590+0.0328406739))+D598*('Segments'!$D$34*D590*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*D590+0.4357405005*D590+0.0330936548*D590+0.0328406739))</f>
         <v/>
       </c>
       <c r="E601" s="18">
-        <f>E591*('Segments'!$D$27*E590*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*E589+0.4357405005*E589+0.0330936548*E590+0.0328406739))+E592*('Segments'!$D$28*E590*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*E589+0.4357405005*E589+0.0330936548*E590+0.0328406739))+E593*('Segments'!$D$29*E590*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*E589+0.4357405005*E589+0.0330936548*E590+0.0328406739))+E594*('Segments'!$D$30*E590*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*E589+0.4357405005*E589+0.0330936548*E590+0.0328406739))+E595*('Segments'!$D$31*E590*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*E589+0.4357405005*E589+0.0330936548*E590+0.0328406739))+E596*('Segments'!$D$32*E590*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*E589+0.4357405005*E589+0.0330936548*E590+0.0328406739))+E597*('Segments'!$D$33*E590*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*E589+0.4357405005*E589+0.0330936548*E590+0.0328406739))+E598*('Segments'!$D$34*E590*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*E589+0.4357405005*E589+0.0330936548*E590+0.0328406739))</f>
+        <f>E591*('Segments'!$D$27*E590*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*E590+0.4357405005*E590+0.0330936548*E590+0.0328406739))+E592*('Segments'!$D$28*E590*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*E590+0.4357405005*E590+0.0330936548*E590+0.0328406739))+E593*('Segments'!$D$29*E590*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*E590+0.4357405005*E590+0.0330936548*E590+0.0328406739))+E594*('Segments'!$D$30*E590*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*E590+0.4357405005*E590+0.0330936548*E590+0.0328406739))+E595*('Segments'!$D$31*E590*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*E590+0.4357405005*E590+0.0330936548*E590+0.0328406739))+E596*('Segments'!$D$32*E590*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*E590+0.4357405005*E590+0.0330936548*E590+0.0328406739))+E597*('Segments'!$D$33*E590*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*E590+0.4357405005*E590+0.0330936548*E590+0.0328406739))+E598*('Segments'!$D$34*E590*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*E590+0.4357405005*E590+0.0330936548*E590+0.0328406739))</f>
         <v/>
       </c>
       <c r="F601" s="18">
-        <f>F591*('Segments'!$D$27*F590*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*F589+0.4357405005*F589+0.0330936548*F590+0.0328406739))+F592*('Segments'!$D$28*F590*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*F589+0.4357405005*F589+0.0330936548*F590+0.0328406739))+F593*('Segments'!$D$29*F590*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*F589+0.4357405005*F589+0.0330936548*F590+0.0328406739))+F594*('Segments'!$D$30*F590*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*F589+0.4357405005*F589+0.0330936548*F590+0.0328406739))+F595*('Segments'!$D$31*F590*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*F589+0.4357405005*F589+0.0330936548*F590+0.0328406739))+F596*('Segments'!$D$32*F590*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*F589+0.4357405005*F589+0.0330936548*F590+0.0328406739))+F597*('Segments'!$D$33*F590*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*F589+0.4357405005*F589+0.0330936548*F590+0.0328406739))+F598*('Segments'!$D$34*F590*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*F589+0.4357405005*F589+0.0330936548*F590+0.0328406739))</f>
+        <f>F591*('Segments'!$D$27*F590*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*F590+0.4357405005*F590+0.0330936548*F590+0.0328406739))+F592*('Segments'!$D$28*F590*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*F590+0.4357405005*F590+0.0330936548*F590+0.0328406739))+F593*('Segments'!$D$29*F590*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*F590+0.4357405005*F590+0.0330936548*F590+0.0328406739))+F594*('Segments'!$D$30*F590*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*F590+0.4357405005*F590+0.0330936548*F590+0.0328406739))+F595*('Segments'!$D$31*F590*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*F590+0.4357405005*F590+0.0330936548*F590+0.0328406739))+F596*('Segments'!$D$32*F590*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*F590+0.4357405005*F590+0.0330936548*F590+0.0328406739))+F597*('Segments'!$D$33*F590*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*F590+0.4357405005*F590+0.0330936548*F590+0.0328406739))+F598*('Segments'!$D$34*F590*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*F590+0.4357405005*F590+0.0330936548*F590+0.0328406739))</f>
         <v/>
       </c>
       <c r="G601" s="18">
-        <f>G591*('Segments'!$D$27*G590*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*G589+0.4357405005*G589+0.0330936548*G590+0.0328406739))+G592*('Segments'!$D$28*G590*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*G589+0.4357405005*G589+0.0330936548*G590+0.0328406739))+G593*('Segments'!$D$29*G590*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*G589+0.4357405005*G589+0.0330936548*G590+0.0328406739))+G594*('Segments'!$D$30*G590*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*G589+0.4357405005*G589+0.0330936548*G590+0.0328406739))+G595*('Segments'!$D$31*G590*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*G589+0.4357405005*G589+0.0330936548*G590+0.0328406739))+G596*('Segments'!$D$32*G590*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*G589+0.4357405005*G589+0.0330936548*G590+0.0328406739))+G597*('Segments'!$D$33*G590*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*G589+0.4357405005*G589+0.0330936548*G590+0.0328406739))+G598*('Segments'!$D$34*G590*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*G589+0.4357405005*G589+0.0330936548*G590+0.0328406739))</f>
+        <f>G591*('Segments'!$D$27*G590*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*G590+0.4357405005*G590+0.0330936548*G590+0.0328406739))+G592*('Segments'!$D$28*G590*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*G590+0.4357405005*G590+0.0330936548*G590+0.0328406739))+G593*('Segments'!$D$29*G590*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*G590+0.4357405005*G590+0.0330936548*G590+0.0328406739))+G594*('Segments'!$D$30*G590*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*G590+0.4357405005*G590+0.0330936548*G590+0.0328406739))+G595*('Segments'!$D$31*G590*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*G590+0.4357405005*G590+0.0330936548*G590+0.0328406739))+G596*('Segments'!$D$32*G590*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*G590+0.4357405005*G590+0.0330936548*G590+0.0328406739))+G597*('Segments'!$D$33*G590*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*G590+0.4357405005*G590+0.0330936548*G590+0.0328406739))+G598*('Segments'!$D$34*G590*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*G590+0.4357405005*G590+0.0330936548*G590+0.0328406739))</f>
         <v/>
       </c>
     </row>
@@ -16226,23 +16226,23 @@
         </is>
       </c>
       <c r="C650" s="18">
-        <f>C640*('Segments'!$D$27*C639*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*C638+0.4357405005*C638+0.0330936548*C639+0.0328406739))+C641*('Segments'!$D$28*C639*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*C638+0.4357405005*C638+0.0330936548*C639+0.0328406739))+C642*('Segments'!$D$29*C639*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*C638+0.4357405005*C638+0.0330936548*C639+0.0328406739))+C643*('Segments'!$D$30*C639*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*C638+0.4357405005*C638+0.0330936548*C639+0.0328406739))+C644*('Segments'!$D$31*C639*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*C638+0.4357405005*C638+0.0330936548*C639+0.0328406739))+C645*('Segments'!$D$32*C639*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*C638+0.4357405005*C638+0.0330936548*C639+0.0328406739))+C646*('Segments'!$D$33*C639*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*C638+0.4357405005*C638+0.0330936548*C639+0.0328406739))+C647*('Segments'!$D$34*C639*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*C638+0.4357405005*C638+0.0330936548*C639+0.0328406739))</f>
+        <f>C640*('Segments'!$D$27*C639*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*C639+0.4357405005*C639+0.0330936548*C639+0.0328406739))+C641*('Segments'!$D$28*C639*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*C639+0.4357405005*C639+0.0330936548*C639+0.0328406739))+C642*('Segments'!$D$29*C639*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*C639+0.4357405005*C639+0.0330936548*C639+0.0328406739))+C643*('Segments'!$D$30*C639*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*C639+0.4357405005*C639+0.0330936548*C639+0.0328406739))+C644*('Segments'!$D$31*C639*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*C639+0.4357405005*C639+0.0330936548*C639+0.0328406739))+C645*('Segments'!$D$32*C639*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*C639+0.4357405005*C639+0.0330936548*C639+0.0328406739))+C646*('Segments'!$D$33*C639*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*C639+0.4357405005*C639+0.0330936548*C639+0.0328406739))+C647*('Segments'!$D$34*C639*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*C639+0.4357405005*C639+0.0330936548*C639+0.0328406739))</f>
         <v/>
       </c>
       <c r="D650" s="18">
-        <f>D640*('Segments'!$D$27*D639*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*D638+0.4357405005*D638+0.0330936548*D639+0.0328406739))+D641*('Segments'!$D$28*D639*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*D638+0.4357405005*D638+0.0330936548*D639+0.0328406739))+D642*('Segments'!$D$29*D639*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*D638+0.4357405005*D638+0.0330936548*D639+0.0328406739))+D643*('Segments'!$D$30*D639*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*D638+0.4357405005*D638+0.0330936548*D639+0.0328406739))+D644*('Segments'!$D$31*D639*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*D638+0.4357405005*D638+0.0330936548*D639+0.0328406739))+D645*('Segments'!$D$32*D639*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*D638+0.4357405005*D638+0.0330936548*D639+0.0328406739))+D646*('Segments'!$D$33*D639*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*D638+0.4357405005*D638+0.0330936548*D639+0.0328406739))+D647*('Segments'!$D$34*D639*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*D638+0.4357405005*D638+0.0330936548*D639+0.0328406739))</f>
+        <f>D640*('Segments'!$D$27*D639*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*D639+0.4357405005*D639+0.0330936548*D639+0.0328406739))+D641*('Segments'!$D$28*D639*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*D639+0.4357405005*D639+0.0330936548*D639+0.0328406739))+D642*('Segments'!$D$29*D639*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*D639+0.4357405005*D639+0.0330936548*D639+0.0328406739))+D643*('Segments'!$D$30*D639*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*D639+0.4357405005*D639+0.0330936548*D639+0.0328406739))+D644*('Segments'!$D$31*D639*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*D639+0.4357405005*D639+0.0330936548*D639+0.0328406739))+D645*('Segments'!$D$32*D639*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*D639+0.4357405005*D639+0.0330936548*D639+0.0328406739))+D646*('Segments'!$D$33*D639*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*D639+0.4357405005*D639+0.0330936548*D639+0.0328406739))+D647*('Segments'!$D$34*D639*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*D639+0.4357405005*D639+0.0330936548*D639+0.0328406739))</f>
         <v/>
       </c>
       <c r="E650" s="18">
-        <f>E640*('Segments'!$D$27*E639*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*E638+0.4357405005*E638+0.0330936548*E639+0.0328406739))+E641*('Segments'!$D$28*E639*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*E638+0.4357405005*E638+0.0330936548*E639+0.0328406739))+E642*('Segments'!$D$29*E639*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*E638+0.4357405005*E638+0.0330936548*E639+0.0328406739))+E643*('Segments'!$D$30*E639*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*E638+0.4357405005*E638+0.0330936548*E639+0.0328406739))+E644*('Segments'!$D$31*E639*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*E638+0.4357405005*E638+0.0330936548*E639+0.0328406739))+E645*('Segments'!$D$32*E639*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*E638+0.4357405005*E638+0.0330936548*E639+0.0328406739))+E646*('Segments'!$D$33*E639*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*E638+0.4357405005*E638+0.0330936548*E639+0.0328406739))+E647*('Segments'!$D$34*E639*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*E638+0.4357405005*E638+0.0330936548*E639+0.0328406739))</f>
+        <f>E640*('Segments'!$D$27*E639*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*E639+0.4357405005*E639+0.0330936548*E639+0.0328406739))+E641*('Segments'!$D$28*E639*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*E639+0.4357405005*E639+0.0330936548*E639+0.0328406739))+E642*('Segments'!$D$29*E639*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*E639+0.4357405005*E639+0.0330936548*E639+0.0328406739))+E643*('Segments'!$D$30*E639*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*E639+0.4357405005*E639+0.0330936548*E639+0.0328406739))+E644*('Segments'!$D$31*E639*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*E639+0.4357405005*E639+0.0330936548*E639+0.0328406739))+E645*('Segments'!$D$32*E639*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*E639+0.4357405005*E639+0.0330936548*E639+0.0328406739))+E646*('Segments'!$D$33*E639*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*E639+0.4357405005*E639+0.0330936548*E639+0.0328406739))+E647*('Segments'!$D$34*E639*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*E639+0.4357405005*E639+0.0330936548*E639+0.0328406739))</f>
         <v/>
       </c>
       <c r="F650" s="18">
-        <f>F640*('Segments'!$D$27*F639*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*F638+0.4357405005*F638+0.0330936548*F639+0.0328406739))+F641*('Segments'!$D$28*F639*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*F638+0.4357405005*F638+0.0330936548*F639+0.0328406739))+F642*('Segments'!$D$29*F639*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*F638+0.4357405005*F638+0.0330936548*F639+0.0328406739))+F643*('Segments'!$D$30*F639*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*F638+0.4357405005*F638+0.0330936548*F639+0.0328406739))+F644*('Segments'!$D$31*F639*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*F638+0.4357405005*F638+0.0330936548*F639+0.0328406739))+F645*('Segments'!$D$32*F639*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*F638+0.4357405005*F638+0.0330936548*F639+0.0328406739))+F646*('Segments'!$D$33*F639*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*F638+0.4357405005*F638+0.0330936548*F639+0.0328406739))+F647*('Segments'!$D$34*F639*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*F638+0.4357405005*F638+0.0330936548*F639+0.0328406739))</f>
+        <f>F640*('Segments'!$D$27*F639*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*F639+0.4357405005*F639+0.0330936548*F639+0.0328406739))+F641*('Segments'!$D$28*F639*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*F639+0.4357405005*F639+0.0330936548*F639+0.0328406739))+F642*('Segments'!$D$29*F639*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*F639+0.4357405005*F639+0.0330936548*F639+0.0328406739))+F643*('Segments'!$D$30*F639*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*F639+0.4357405005*F639+0.0330936548*F639+0.0328406739))+F644*('Segments'!$D$31*F639*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*F639+0.4357405005*F639+0.0330936548*F639+0.0328406739))+F645*('Segments'!$D$32*F639*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*F639+0.4357405005*F639+0.0330936548*F639+0.0328406739))+F646*('Segments'!$D$33*F639*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*F639+0.4357405005*F639+0.0330936548*F639+0.0328406739))+F647*('Segments'!$D$34*F639*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*F639+0.4357405005*F639+0.0330936548*F639+0.0328406739))</f>
         <v/>
       </c>
       <c r="G650" s="18">
-        <f>G640*('Segments'!$D$27*G639*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*G638+0.4357405005*G638+0.0330936548*G639+0.0328406739))+G641*('Segments'!$D$28*G639*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*G638+0.4357405005*G638+0.0330936548*G639+0.0328406739))+G642*('Segments'!$D$29*G639*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*G638+0.4357405005*G638+0.0330936548*G639+0.0328406739))+G643*('Segments'!$D$30*G639*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*G638+0.4357405005*G638+0.0330936548*G639+0.0328406739))+G644*('Segments'!$D$31*G639*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*G638+0.4357405005*G638+0.0330936548*G639+0.0328406739))+G645*('Segments'!$D$32*G639*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*G638+0.4357405005*G638+0.0330936548*G639+0.0328406739))+G646*('Segments'!$D$33*G639*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*G638+0.4357405005*G638+0.0330936548*G639+0.0328406739))+G647*('Segments'!$D$34*G639*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*G638+0.4357405005*G638+0.0330936548*G639+0.0328406739))</f>
+        <f>G640*('Segments'!$D$27*G639*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*G639+0.4357405005*G639+0.0330936548*G639+0.0328406739))+G641*('Segments'!$D$28*G639*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*G639+0.4357405005*G639+0.0330936548*G639+0.0328406739))+G642*('Segments'!$D$29*G639*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*G639+0.4357405005*G639+0.0330936548*G639+0.0328406739))+G643*('Segments'!$D$30*G639*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*G639+0.4357405005*G639+0.0330936548*G639+0.0328406739))+G644*('Segments'!$D$31*G639*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*G639+0.4357405005*G639+0.0330936548*G639+0.0328406739))+G645*('Segments'!$D$32*G639*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*G639+0.4357405005*G639+0.0330936548*G639+0.0328406739))+G646*('Segments'!$D$33*G639*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*G639+0.4357405005*G639+0.0330936548*G639+0.0328406739))+G647*('Segments'!$D$34*G639*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*G639+0.4357405005*G639+0.0330936548*G639+0.0328406739))</f>
         <v/>
       </c>
     </row>
@@ -17296,23 +17296,23 @@
         </is>
       </c>
       <c r="C699" s="18">
-        <f>C689*('Segments'!$D$27*C688*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*C687+0.4357405005*C687+0.0330936548*C688+0.0328406739))+C690*('Segments'!$D$28*C688*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*C687+0.4357405005*C687+0.0330936548*C688+0.0328406739))+C691*('Segments'!$D$29*C688*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*C687+0.4357405005*C687+0.0330936548*C688+0.0328406739))+C692*('Segments'!$D$30*C688*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*C687+0.4357405005*C687+0.0330936548*C688+0.0328406739))+C693*('Segments'!$D$31*C688*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*C687+0.4357405005*C687+0.0330936548*C688+0.0328406739))+C694*('Segments'!$D$32*C688*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*C687+0.4357405005*C687+0.0330936548*C688+0.0328406739))+C695*('Segments'!$D$33*C688*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*C687+0.4357405005*C687+0.0330936548*C688+0.0328406739))+C696*('Segments'!$D$34*C688*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*C687+0.4357405005*C687+0.0330936548*C688+0.0328406739))</f>
+        <f>C689*('Segments'!$D$27*C688*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*C688+0.4357405005*C688+0.0330936548*C688+0.0328406739))+C690*('Segments'!$D$28*C688*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*C688+0.4357405005*C688+0.0330936548*C688+0.0328406739))+C691*('Segments'!$D$29*C688*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*C688+0.4357405005*C688+0.0330936548*C688+0.0328406739))+C692*('Segments'!$D$30*C688*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*C688+0.4357405005*C688+0.0330936548*C688+0.0328406739))+C693*('Segments'!$D$31*C688*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*C688+0.4357405005*C688+0.0330936548*C688+0.0328406739))+C694*('Segments'!$D$32*C688*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*C688+0.4357405005*C688+0.0330936548*C688+0.0328406739))+C695*('Segments'!$D$33*C688*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*C688+0.4357405005*C688+0.0330936548*C688+0.0328406739))+C696*('Segments'!$D$34*C688*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*C688+0.4357405005*C688+0.0330936548*C688+0.0328406739))</f>
         <v/>
       </c>
       <c r="D699" s="18">
-        <f>D689*('Segments'!$D$27*D688*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*D687+0.4357405005*D687+0.0330936548*D688+0.0328406739))+D690*('Segments'!$D$28*D688*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*D687+0.4357405005*D687+0.0330936548*D688+0.0328406739))+D691*('Segments'!$D$29*D688*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*D687+0.4357405005*D687+0.0330936548*D688+0.0328406739))+D692*('Segments'!$D$30*D688*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*D687+0.4357405005*D687+0.0330936548*D688+0.0328406739))+D693*('Segments'!$D$31*D688*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*D687+0.4357405005*D687+0.0330936548*D688+0.0328406739))+D694*('Segments'!$D$32*D688*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*D687+0.4357405005*D687+0.0330936548*D688+0.0328406739))+D695*('Segments'!$D$33*D688*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*D687+0.4357405005*D687+0.0330936548*D688+0.0328406739))+D696*('Segments'!$D$34*D688*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*D687+0.4357405005*D687+0.0330936548*D688+0.0328406739))</f>
+        <f>D689*('Segments'!$D$27*D688*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*D688+0.4357405005*D688+0.0330936548*D688+0.0328406739))+D690*('Segments'!$D$28*D688*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*D688+0.4357405005*D688+0.0330936548*D688+0.0328406739))+D691*('Segments'!$D$29*D688*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*D688+0.4357405005*D688+0.0330936548*D688+0.0328406739))+D692*('Segments'!$D$30*D688*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*D688+0.4357405005*D688+0.0330936548*D688+0.0328406739))+D693*('Segments'!$D$31*D688*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*D688+0.4357405005*D688+0.0330936548*D688+0.0328406739))+D694*('Segments'!$D$32*D688*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*D688+0.4357405005*D688+0.0330936548*D688+0.0328406739))+D695*('Segments'!$D$33*D688*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*D688+0.4357405005*D688+0.0330936548*D688+0.0328406739))+D696*('Segments'!$D$34*D688*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*D688+0.4357405005*D688+0.0330936548*D688+0.0328406739))</f>
         <v/>
       </c>
       <c r="E699" s="18">
-        <f>E689*('Segments'!$D$27*E688*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*E687+0.4357405005*E687+0.0330936548*E688+0.0328406739))+E690*('Segments'!$D$28*E688*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*E687+0.4357405005*E687+0.0330936548*E688+0.0328406739))+E691*('Segments'!$D$29*E688*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*E687+0.4357405005*E687+0.0330936548*E688+0.0328406739))+E692*('Segments'!$D$30*E688*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*E687+0.4357405005*E687+0.0330936548*E688+0.0328406739))+E693*('Segments'!$D$31*E688*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*E687+0.4357405005*E687+0.0330936548*E688+0.0328406739))+E694*('Segments'!$D$32*E688*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*E687+0.4357405005*E687+0.0330936548*E688+0.0328406739))+E695*('Segments'!$D$33*E688*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*E687+0.4357405005*E687+0.0330936548*E688+0.0328406739))+E696*('Segments'!$D$34*E688*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*E687+0.4357405005*E687+0.0330936548*E688+0.0328406739))</f>
+        <f>E689*('Segments'!$D$27*E688*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*E688+0.4357405005*E688+0.0330936548*E688+0.0328406739))+E690*('Segments'!$D$28*E688*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*E688+0.4357405005*E688+0.0330936548*E688+0.0328406739))+E691*('Segments'!$D$29*E688*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*E688+0.4357405005*E688+0.0330936548*E688+0.0328406739))+E692*('Segments'!$D$30*E688*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*E688+0.4357405005*E688+0.0330936548*E688+0.0328406739))+E693*('Segments'!$D$31*E688*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*E688+0.4357405005*E688+0.0330936548*E688+0.0328406739))+E694*('Segments'!$D$32*E688*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*E688+0.4357405005*E688+0.0330936548*E688+0.0328406739))+E695*('Segments'!$D$33*E688*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*E688+0.4357405005*E688+0.0330936548*E688+0.0328406739))+E696*('Segments'!$D$34*E688*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*E688+0.4357405005*E688+0.0330936548*E688+0.0328406739))</f>
         <v/>
       </c>
       <c r="F699" s="18">
-        <f>F689*('Segments'!$D$27*F688*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*F687+0.4357405005*F687+0.0330936548*F688+0.0328406739))+F690*('Segments'!$D$28*F688*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*F687+0.4357405005*F687+0.0330936548*F688+0.0328406739))+F691*('Segments'!$D$29*F688*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*F687+0.4357405005*F687+0.0330936548*F688+0.0328406739))+F692*('Segments'!$D$30*F688*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*F687+0.4357405005*F687+0.0330936548*F688+0.0328406739))+F693*('Segments'!$D$31*F688*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*F687+0.4357405005*F687+0.0330936548*F688+0.0328406739))+F694*('Segments'!$D$32*F688*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*F687+0.4357405005*F687+0.0330936548*F688+0.0328406739))+F695*('Segments'!$D$33*F688*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*F687+0.4357405005*F687+0.0330936548*F688+0.0328406739))+F696*('Segments'!$D$34*F688*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*F687+0.4357405005*F687+0.0330936548*F688+0.0328406739))</f>
+        <f>F689*('Segments'!$D$27*F688*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*F688+0.4357405005*F688+0.0330936548*F688+0.0328406739))+F690*('Segments'!$D$28*F688*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*F688+0.4357405005*F688+0.0330936548*F688+0.0328406739))+F691*('Segments'!$D$29*F688*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*F688+0.4357405005*F688+0.0330936548*F688+0.0328406739))+F692*('Segments'!$D$30*F688*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*F688+0.4357405005*F688+0.0330936548*F688+0.0328406739))+F693*('Segments'!$D$31*F688*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*F688+0.4357405005*F688+0.0330936548*F688+0.0328406739))+F694*('Segments'!$D$32*F688*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*F688+0.4357405005*F688+0.0330936548*F688+0.0328406739))+F695*('Segments'!$D$33*F688*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*F688+0.4357405005*F688+0.0330936548*F688+0.0328406739))+F696*('Segments'!$D$34*F688*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*F688+0.4357405005*F688+0.0330936548*F688+0.0328406739))</f>
         <v/>
       </c>
       <c r="G699" s="18">
-        <f>G689*('Segments'!$D$27*G688*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*G687+0.4357405005*G687+0.0330936548*G688+0.0328406739))+G690*('Segments'!$D$28*G688*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*G687+0.4357405005*G687+0.0330936548*G688+0.0328406739))+G691*('Segments'!$D$29*G688*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*G687+0.4357405005*G687+0.0330936548*G688+0.0328406739))+G692*('Segments'!$D$30*G688*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*G687+0.4357405005*G687+0.0330936548*G688+0.0328406739))+G693*('Segments'!$D$31*G688*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*G687+0.4357405005*G687+0.0330936548*G688+0.0328406739))+G694*('Segments'!$D$32*G688*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*G687+0.4357405005*G687+0.0330936548*G688+0.0328406739))+G695*('Segments'!$D$33*G688*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*G687+0.4357405005*G687+0.0330936548*G688+0.0328406739))+G696*('Segments'!$D$34*G688*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*G687+0.4357405005*G687+0.0330936548*G688+0.0328406739))</f>
+        <f>G689*('Segments'!$D$27*G688*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*G688+0.4357405005*G688+0.0330936548*G688+0.0328406739))+G690*('Segments'!$D$28*G688*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*G688+0.4357405005*G688+0.0330936548*G688+0.0328406739))+G691*('Segments'!$D$29*G688*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*G688+0.4357405005*G688+0.0330936548*G688+0.0328406739))+G692*('Segments'!$D$30*G688*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*G688+0.4357405005*G688+0.0330936548*G688+0.0328406739))+G693*('Segments'!$D$31*G688*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*G688+0.4357405005*G688+0.0330936548*G688+0.0328406739))+G694*('Segments'!$D$32*G688*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*G688+0.4357405005*G688+0.0330936548*G688+0.0328406739))+G695*('Segments'!$D$33*G688*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*G688+0.4357405005*G688+0.0330936548*G688+0.0328406739))+G696*('Segments'!$D$34*G688*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*G688+0.4357405005*G688+0.0330936548*G688+0.0328406739))</f>
         <v/>
       </c>
     </row>
@@ -18366,23 +18366,23 @@
         </is>
       </c>
       <c r="C748" s="18">
-        <f>C738*('Segments'!$D$27*C737*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*C736+0.4357405005*C736+0.0330936548*C737+0.0328406739))+C739*('Segments'!$D$28*C737*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*C736+0.4357405005*C736+0.0330936548*C737+0.0328406739))+C740*('Segments'!$D$29*C737*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*C736+0.4357405005*C736+0.0330936548*C737+0.0328406739))+C741*('Segments'!$D$30*C737*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*C736+0.4357405005*C736+0.0330936548*C737+0.0328406739))+C742*('Segments'!$D$31*C737*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*C736+0.4357405005*C736+0.0330936548*C737+0.0328406739))+C743*('Segments'!$D$32*C737*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*C736+0.4357405005*C736+0.0330936548*C737+0.0328406739))+C744*('Segments'!$D$33*C737*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*C736+0.4357405005*C736+0.0330936548*C737+0.0328406739))+C745*('Segments'!$D$34*C737*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*C736+0.4357405005*C736+0.0330936548*C737+0.0328406739))</f>
+        <f>C738*('Segments'!$D$27*C737*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*C737+0.4357405005*C737+0.0330936548*C737+0.0328406739))+C739*('Segments'!$D$28*C737*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*C737+0.4357405005*C737+0.0330936548*C737+0.0328406739))+C740*('Segments'!$D$29*C737*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*C737+0.4357405005*C737+0.0330936548*C737+0.0328406739))+C741*('Segments'!$D$30*C737*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*C737+0.4357405005*C737+0.0330936548*C737+0.0328406739))+C742*('Segments'!$D$31*C737*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*C737+0.4357405005*C737+0.0330936548*C737+0.0328406739))+C743*('Segments'!$D$32*C737*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*C737+0.4357405005*C737+0.0330936548*C737+0.0328406739))+C744*('Segments'!$D$33*C737*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*C737+0.4357405005*C737+0.0330936548*C737+0.0328406739))+C745*('Segments'!$D$34*C737*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*C737+0.4357405005*C737+0.0330936548*C737+0.0328406739))</f>
         <v/>
       </c>
       <c r="D748" s="18">
-        <f>D738*('Segments'!$D$27*D737*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*D736+0.4357405005*D736+0.0330936548*D737+0.0328406739))+D739*('Segments'!$D$28*D737*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*D736+0.4357405005*D736+0.0330936548*D737+0.0328406739))+D740*('Segments'!$D$29*D737*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*D736+0.4357405005*D736+0.0330936548*D737+0.0328406739))+D741*('Segments'!$D$30*D737*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*D736+0.4357405005*D736+0.0330936548*D737+0.0328406739))+D742*('Segments'!$D$31*D737*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*D736+0.4357405005*D736+0.0330936548*D737+0.0328406739))+D743*('Segments'!$D$32*D737*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*D736+0.4357405005*D736+0.0330936548*D737+0.0328406739))+D744*('Segments'!$D$33*D737*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*D736+0.4357405005*D736+0.0330936548*D737+0.0328406739))+D745*('Segments'!$D$34*D737*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*D736+0.4357405005*D736+0.0330936548*D737+0.0328406739))</f>
+        <f>D738*('Segments'!$D$27*D737*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*D737+0.4357405005*D737+0.0330936548*D737+0.0328406739))+D739*('Segments'!$D$28*D737*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*D737+0.4357405005*D737+0.0330936548*D737+0.0328406739))+D740*('Segments'!$D$29*D737*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*D737+0.4357405005*D737+0.0330936548*D737+0.0328406739))+D741*('Segments'!$D$30*D737*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*D737+0.4357405005*D737+0.0330936548*D737+0.0328406739))+D742*('Segments'!$D$31*D737*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*D737+0.4357405005*D737+0.0330936548*D737+0.0328406739))+D743*('Segments'!$D$32*D737*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*D737+0.4357405005*D737+0.0330936548*D737+0.0328406739))+D744*('Segments'!$D$33*D737*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*D737+0.4357405005*D737+0.0330936548*D737+0.0328406739))+D745*('Segments'!$D$34*D737*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*D737+0.4357405005*D737+0.0330936548*D737+0.0328406739))</f>
         <v/>
       </c>
       <c r="E748" s="18">
-        <f>E738*('Segments'!$D$27*E737*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*E736+0.4357405005*E736+0.0330936548*E737+0.0328406739))+E739*('Segments'!$D$28*E737*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*E736+0.4357405005*E736+0.0330936548*E737+0.0328406739))+E740*('Segments'!$D$29*E737*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*E736+0.4357405005*E736+0.0330936548*E737+0.0328406739))+E741*('Segments'!$D$30*E737*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*E736+0.4357405005*E736+0.0330936548*E737+0.0328406739))+E742*('Segments'!$D$31*E737*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*E736+0.4357405005*E736+0.0330936548*E737+0.0328406739))+E743*('Segments'!$D$32*E737*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*E736+0.4357405005*E736+0.0330936548*E737+0.0328406739))+E744*('Segments'!$D$33*E737*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*E736+0.4357405005*E736+0.0330936548*E737+0.0328406739))+E745*('Segments'!$D$34*E737*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*E736+0.4357405005*E736+0.0330936548*E737+0.0328406739))</f>
+        <f>E738*('Segments'!$D$27*E737*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*E737+0.4357405005*E737+0.0330936548*E737+0.0328406739))+E739*('Segments'!$D$28*E737*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*E737+0.4357405005*E737+0.0330936548*E737+0.0328406739))+E740*('Segments'!$D$29*E737*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*E737+0.4357405005*E737+0.0330936548*E737+0.0328406739))+E741*('Segments'!$D$30*E737*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*E737+0.4357405005*E737+0.0330936548*E737+0.0328406739))+E742*('Segments'!$D$31*E737*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*E737+0.4357405005*E737+0.0330936548*E737+0.0328406739))+E743*('Segments'!$D$32*E737*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*E737+0.4357405005*E737+0.0330936548*E737+0.0328406739))+E744*('Segments'!$D$33*E737*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*E737+0.4357405005*E737+0.0330936548*E737+0.0328406739))+E745*('Segments'!$D$34*E737*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*E737+0.4357405005*E737+0.0330936548*E737+0.0328406739))</f>
         <v/>
       </c>
       <c r="F748" s="18">
-        <f>F738*('Segments'!$D$27*F737*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*F736+0.4357405005*F736+0.0330936548*F737+0.0328406739))+F739*('Segments'!$D$28*F737*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*F736+0.4357405005*F736+0.0330936548*F737+0.0328406739))+F740*('Segments'!$D$29*F737*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*F736+0.4357405005*F736+0.0330936548*F737+0.0328406739))+F741*('Segments'!$D$30*F737*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*F736+0.4357405005*F736+0.0330936548*F737+0.0328406739))+F742*('Segments'!$D$31*F737*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*F736+0.4357405005*F736+0.0330936548*F737+0.0328406739))+F743*('Segments'!$D$32*F737*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*F736+0.4357405005*F736+0.0330936548*F737+0.0328406739))+F744*('Segments'!$D$33*F737*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*F736+0.4357405005*F736+0.0330936548*F737+0.0328406739))+F745*('Segments'!$D$34*F737*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*F736+0.4357405005*F736+0.0330936548*F737+0.0328406739))</f>
+        <f>F738*('Segments'!$D$27*F737*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*F737+0.4357405005*F737+0.0330936548*F737+0.0328406739))+F739*('Segments'!$D$28*F737*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*F737+0.4357405005*F737+0.0330936548*F737+0.0328406739))+F740*('Segments'!$D$29*F737*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*F737+0.4357405005*F737+0.0330936548*F737+0.0328406739))+F741*('Segments'!$D$30*F737*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*F737+0.4357405005*F737+0.0330936548*F737+0.0328406739))+F742*('Segments'!$D$31*F737*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*F737+0.4357405005*F737+0.0330936548*F737+0.0328406739))+F743*('Segments'!$D$32*F737*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*F737+0.4357405005*F737+0.0330936548*F737+0.0328406739))+F744*('Segments'!$D$33*F737*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*F737+0.4357405005*F737+0.0330936548*F737+0.0328406739))+F745*('Segments'!$D$34*F737*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*F737+0.4357405005*F737+0.0330936548*F737+0.0328406739))</f>
         <v/>
       </c>
       <c r="G748" s="18">
-        <f>G738*('Segments'!$D$27*G737*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*G736+0.4357405005*G736+0.0330936548*G737+0.0328406739))+G739*('Segments'!$D$28*G737*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*G736+0.4357405005*G736+0.0330936548*G737+0.0328406739))+G740*('Segments'!$D$29*G737*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*G736+0.4357405005*G736+0.0330936548*G737+0.0328406739))+G741*('Segments'!$D$30*G737*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*G736+0.4357405005*G736+0.0330936548*G737+0.0328406739))+G742*('Segments'!$D$31*G737*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*G736+0.4357405005*G736+0.0330936548*G737+0.0328406739))+G743*('Segments'!$D$32*G737*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*G736+0.4357405005*G736+0.0330936548*G737+0.0328406739))+G744*('Segments'!$D$33*G737*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*G736+0.4357405005*G736+0.0330936548*G737+0.0328406739))+G745*('Segments'!$D$34*G737*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*G736+0.4357405005*G736+0.0330936548*G737+0.0328406739))</f>
+        <f>G738*('Segments'!$D$27*G737*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*G737+0.4357405005*G737+0.0330936548*G737+0.0328406739))+G739*('Segments'!$D$28*G737*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*G737+0.4357405005*G737+0.0330936548*G737+0.0328406739))+G740*('Segments'!$D$29*G737*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*G737+0.4357405005*G737+0.0330936548*G737+0.0328406739))+G741*('Segments'!$D$30*G737*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*G737+0.4357405005*G737+0.0330936548*G737+0.0328406739))+G742*('Segments'!$D$31*G737*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*G737+0.4357405005*G737+0.0330936548*G737+0.0328406739))+G743*('Segments'!$D$32*G737*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*G737+0.4357405005*G737+0.0330936548*G737+0.0328406739))+G744*('Segments'!$D$33*G737*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*G737+0.4357405005*G737+0.0330936548*G737+0.0328406739))+G745*('Segments'!$D$34*G737*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*G737+0.4357405005*G737+0.0330936548*G737+0.0328406739))</f>
         <v/>
       </c>
     </row>
@@ -19436,23 +19436,23 @@
         </is>
       </c>
       <c r="C797" s="18">
-        <f>C787*('Segments'!$D$27*C786*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*C785+0.4357405005*C785+0.0330936548*C786+0.0328406739))+C788*('Segments'!$D$28*C786*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*C785+0.4357405005*C785+0.0330936548*C786+0.0328406739))+C789*('Segments'!$D$29*C786*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*C785+0.4357405005*C785+0.0330936548*C786+0.0328406739))+C790*('Segments'!$D$30*C786*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*C785+0.4357405005*C785+0.0330936548*C786+0.0328406739))+C791*('Segments'!$D$31*C786*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*C785+0.4357405005*C785+0.0330936548*C786+0.0328406739))+C792*('Segments'!$D$32*C786*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*C785+0.4357405005*C785+0.0330936548*C786+0.0328406739))+C793*('Segments'!$D$33*C786*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*C785+0.4357405005*C785+0.0330936548*C786+0.0328406739))+C794*('Segments'!$D$34*C786*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*C785+0.4357405005*C785+0.0330936548*C786+0.0328406739))</f>
+        <f>C787*('Segments'!$D$27*C786*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*C786+0.4357405005*C786+0.0330936548*C786+0.0328406739))+C788*('Segments'!$D$28*C786*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*C786+0.4357405005*C786+0.0330936548*C786+0.0328406739))+C789*('Segments'!$D$29*C786*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*C786+0.4357405005*C786+0.0330936548*C786+0.0328406739))+C790*('Segments'!$D$30*C786*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*C786+0.4357405005*C786+0.0330936548*C786+0.0328406739))+C791*('Segments'!$D$31*C786*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*C786+0.4357405005*C786+0.0330936548*C786+0.0328406739))+C792*('Segments'!$D$32*C786*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*C786+0.4357405005*C786+0.0330936548*C786+0.0328406739))+C793*('Segments'!$D$33*C786*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*C786+0.4357405005*C786+0.0330936548*C786+0.0328406739))+C794*('Segments'!$D$34*C786*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*C786+0.4357405005*C786+0.0330936548*C786+0.0328406739))</f>
         <v/>
       </c>
       <c r="D797" s="18">
-        <f>D787*('Segments'!$D$27*D786*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*D785+0.4357405005*D785+0.0330936548*D786+0.0328406739))+D788*('Segments'!$D$28*D786*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*D785+0.4357405005*D785+0.0330936548*D786+0.0328406739))+D789*('Segments'!$D$29*D786*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*D785+0.4357405005*D785+0.0330936548*D786+0.0328406739))+D790*('Segments'!$D$30*D786*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*D785+0.4357405005*D785+0.0330936548*D786+0.0328406739))+D791*('Segments'!$D$31*D786*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*D785+0.4357405005*D785+0.0330936548*D786+0.0328406739))+D792*('Segments'!$D$32*D786*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*D785+0.4357405005*D785+0.0330936548*D786+0.0328406739))+D793*('Segments'!$D$33*D786*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*D785+0.4357405005*D785+0.0330936548*D786+0.0328406739))+D794*('Segments'!$D$34*D786*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*D785+0.4357405005*D785+0.0330936548*D786+0.0328406739))</f>
+        <f>D787*('Segments'!$D$27*D786*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*D786+0.4357405005*D786+0.0330936548*D786+0.0328406739))+D788*('Segments'!$D$28*D786*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*D786+0.4357405005*D786+0.0330936548*D786+0.0328406739))+D789*('Segments'!$D$29*D786*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*D786+0.4357405005*D786+0.0330936548*D786+0.0328406739))+D790*('Segments'!$D$30*D786*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*D786+0.4357405005*D786+0.0330936548*D786+0.0328406739))+D791*('Segments'!$D$31*D786*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*D786+0.4357405005*D786+0.0330936548*D786+0.0328406739))+D792*('Segments'!$D$32*D786*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*D786+0.4357405005*D786+0.0330936548*D786+0.0328406739))+D793*('Segments'!$D$33*D786*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*D786+0.4357405005*D786+0.0330936548*D786+0.0328406739))+D794*('Segments'!$D$34*D786*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*D786+0.4357405005*D786+0.0330936548*D786+0.0328406739))</f>
         <v/>
       </c>
       <c r="E797" s="18">
-        <f>E787*('Segments'!$D$27*E786*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*E785+0.4357405005*E785+0.0330936548*E786+0.0328406739))+E788*('Segments'!$D$28*E786*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*E785+0.4357405005*E785+0.0330936548*E786+0.0328406739))+E789*('Segments'!$D$29*E786*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*E785+0.4357405005*E785+0.0330936548*E786+0.0328406739))+E790*('Segments'!$D$30*E786*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*E785+0.4357405005*E785+0.0330936548*E786+0.0328406739))+E791*('Segments'!$D$31*E786*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*E785+0.4357405005*E785+0.0330936548*E786+0.0328406739))+E792*('Segments'!$D$32*E786*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*E785+0.4357405005*E785+0.0330936548*E786+0.0328406739))+E793*('Segments'!$D$33*E786*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*E785+0.4357405005*E785+0.0330936548*E786+0.0328406739))+E794*('Segments'!$D$34*E786*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*E785+0.4357405005*E785+0.0330936548*E786+0.0328406739))</f>
+        <f>E787*('Segments'!$D$27*E786*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*E786+0.4357405005*E786+0.0330936548*E786+0.0328406739))+E788*('Segments'!$D$28*E786*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*E786+0.4357405005*E786+0.0330936548*E786+0.0328406739))+E789*('Segments'!$D$29*E786*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*E786+0.4357405005*E786+0.0330936548*E786+0.0328406739))+E790*('Segments'!$D$30*E786*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*E786+0.4357405005*E786+0.0330936548*E786+0.0328406739))+E791*('Segments'!$D$31*E786*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*E786+0.4357405005*E786+0.0330936548*E786+0.0328406739))+E792*('Segments'!$D$32*E786*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*E786+0.4357405005*E786+0.0330936548*E786+0.0328406739))+E793*('Segments'!$D$33*E786*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*E786+0.4357405005*E786+0.0330936548*E786+0.0328406739))+E794*('Segments'!$D$34*E786*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*E786+0.4357405005*E786+0.0330936548*E786+0.0328406739))</f>
         <v/>
       </c>
       <c r="F797" s="18">
-        <f>F787*('Segments'!$D$27*F786*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*F785+0.4357405005*F785+0.0330936548*F786+0.0328406739))+F788*('Segments'!$D$28*F786*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*F785+0.4357405005*F785+0.0330936548*F786+0.0328406739))+F789*('Segments'!$D$29*F786*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*F785+0.4357405005*F785+0.0330936548*F786+0.0328406739))+F790*('Segments'!$D$30*F786*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*F785+0.4357405005*F785+0.0330936548*F786+0.0328406739))+F791*('Segments'!$D$31*F786*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*F785+0.4357405005*F785+0.0330936548*F786+0.0328406739))+F792*('Segments'!$D$32*F786*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*F785+0.4357405005*F785+0.0330936548*F786+0.0328406739))+F793*('Segments'!$D$33*F786*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*F785+0.4357405005*F785+0.0330936548*F786+0.0328406739))+F794*('Segments'!$D$34*F786*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*F785+0.4357405005*F785+0.0330936548*F786+0.0328406739))</f>
+        <f>F787*('Segments'!$D$27*F786*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*F786+0.4357405005*F786+0.0330936548*F786+0.0328406739))+F788*('Segments'!$D$28*F786*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*F786+0.4357405005*F786+0.0330936548*F786+0.0328406739))+F789*('Segments'!$D$29*F786*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*F786+0.4357405005*F786+0.0330936548*F786+0.0328406739))+F790*('Segments'!$D$30*F786*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*F786+0.4357405005*F786+0.0330936548*F786+0.0328406739))+F791*('Segments'!$D$31*F786*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*F786+0.4357405005*F786+0.0330936548*F786+0.0328406739))+F792*('Segments'!$D$32*F786*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*F786+0.4357405005*F786+0.0330936548*F786+0.0328406739))+F793*('Segments'!$D$33*F786*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*F786+0.4357405005*F786+0.0330936548*F786+0.0328406739))+F794*('Segments'!$D$34*F786*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*F786+0.4357405005*F786+0.0330936548*F786+0.0328406739))</f>
         <v/>
       </c>
       <c r="G797" s="18">
-        <f>G787*('Segments'!$D$27*G786*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*G785+0.4357405005*G785+0.0330936548*G786+0.0328406739))+G788*('Segments'!$D$28*G786*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*G785+0.4357405005*G785+0.0330936548*G786+0.0328406739))+G789*('Segments'!$D$29*G786*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*G785+0.4357405005*G785+0.0330936548*G786+0.0328406739))+G790*('Segments'!$D$30*G786*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*G785+0.4357405005*G785+0.0330936548*G786+0.0328406739))+G791*('Segments'!$D$31*G786*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*G785+0.4357405005*G785+0.0330936548*G786+0.0328406739))+G792*('Segments'!$D$32*G786*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*G785+0.4357405005*G785+0.0330936548*G786+0.0328406739))+G793*('Segments'!$D$33*G786*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*G785+0.4357405005*G785+0.0330936548*G786+0.0328406739))+G794*('Segments'!$D$34*G786*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*G785+0.4357405005*G785+0.0330936548*G786+0.0328406739))</f>
+        <f>G787*('Segments'!$D$27*G786*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*G786+0.4357405005*G786+0.0330936548*G786+0.0328406739))+G788*('Segments'!$D$28*G786*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*G786+0.4357405005*G786+0.0330936548*G786+0.0328406739))+G789*('Segments'!$D$29*G786*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*G786+0.4357405005*G786+0.0330936548*G786+0.0328406739))+G790*('Segments'!$D$30*G786*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*G786+0.4357405005*G786+0.0330936548*G786+0.0328406739))+G791*('Segments'!$D$31*G786*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*G786+0.4357405005*G786+0.0330936548*G786+0.0328406739))+G792*('Segments'!$D$32*G786*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*G786+0.4357405005*G786+0.0330936548*G786+0.0328406739))+G793*('Segments'!$D$33*G786*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*G786+0.4357405005*G786+0.0330936548*G786+0.0328406739))+G794*('Segments'!$D$34*G786*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*G786+0.4357405005*G786+0.0330936548*G786+0.0328406739))</f>
         <v/>
       </c>
     </row>
@@ -20506,23 +20506,23 @@
         </is>
       </c>
       <c r="C846" s="18">
-        <f>C836*('Segments'!$D$27*C835*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*C834+0.4357405005*C834+0.0330936548*C835+0.0328406739))+C837*('Segments'!$D$28*C835*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*C834+0.4357405005*C834+0.0330936548*C835+0.0328406739))+C838*('Segments'!$D$29*C835*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*C834+0.4357405005*C834+0.0330936548*C835+0.0328406739))+C839*('Segments'!$D$30*C835*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*C834+0.4357405005*C834+0.0330936548*C835+0.0328406739))+C840*('Segments'!$D$31*C835*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*C834+0.4357405005*C834+0.0330936548*C835+0.0328406739))+C841*('Segments'!$D$32*C835*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*C834+0.4357405005*C834+0.0330936548*C835+0.0328406739))+C842*('Segments'!$D$33*C835*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*C834+0.4357405005*C834+0.0330936548*C835+0.0328406739))+C843*('Segments'!$D$34*C835*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*C834+0.4357405005*C834+0.0330936548*C835+0.0328406739))</f>
+        <f>C836*('Segments'!$D$27*C835*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*C835+0.4357405005*C835+0.0330936548*C835+0.0328406739))+C837*('Segments'!$D$28*C835*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*C835+0.4357405005*C835+0.0330936548*C835+0.0328406739))+C838*('Segments'!$D$29*C835*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*C835+0.4357405005*C835+0.0330936548*C835+0.0328406739))+C839*('Segments'!$D$30*C835*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*C835+0.4357405005*C835+0.0330936548*C835+0.0328406739))+C840*('Segments'!$D$31*C835*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*C835+0.4357405005*C835+0.0330936548*C835+0.0328406739))+C841*('Segments'!$D$32*C835*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*C835+0.4357405005*C835+0.0330936548*C835+0.0328406739))+C842*('Segments'!$D$33*C835*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*C835+0.4357405005*C835+0.0330936548*C835+0.0328406739))+C843*('Segments'!$D$34*C835*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*C835+0.4357405005*C835+0.0330936548*C835+0.0328406739))</f>
         <v/>
       </c>
       <c r="D846" s="18">
-        <f>D836*('Segments'!$D$27*D835*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*D834+0.4357405005*D834+0.0330936548*D835+0.0328406739))+D837*('Segments'!$D$28*D835*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*D834+0.4357405005*D834+0.0330936548*D835+0.0328406739))+D838*('Segments'!$D$29*D835*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*D834+0.4357405005*D834+0.0330936548*D835+0.0328406739))+D839*('Segments'!$D$30*D835*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*D834+0.4357405005*D834+0.0330936548*D835+0.0328406739))+D840*('Segments'!$D$31*D835*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*D834+0.4357405005*D834+0.0330936548*D835+0.0328406739))+D841*('Segments'!$D$32*D835*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*D834+0.4357405005*D834+0.0330936548*D835+0.0328406739))+D842*('Segments'!$D$33*D835*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*D834+0.4357405005*D834+0.0330936548*D835+0.0328406739))+D843*('Segments'!$D$34*D835*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*D834+0.4357405005*D834+0.0330936548*D835+0.0328406739))</f>
+        <f>D836*('Segments'!$D$27*D835*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*D835+0.4357405005*D835+0.0330936548*D835+0.0328406739))+D837*('Segments'!$D$28*D835*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*D835+0.4357405005*D835+0.0330936548*D835+0.0328406739))+D838*('Segments'!$D$29*D835*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*D835+0.4357405005*D835+0.0330936548*D835+0.0328406739))+D839*('Segments'!$D$30*D835*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*D835+0.4357405005*D835+0.0330936548*D835+0.0328406739))+D840*('Segments'!$D$31*D835*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*D835+0.4357405005*D835+0.0330936548*D835+0.0328406739))+D841*('Segments'!$D$32*D835*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*D835+0.4357405005*D835+0.0330936548*D835+0.0328406739))+D842*('Segments'!$D$33*D835*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*D835+0.4357405005*D835+0.0330936548*D835+0.0328406739))+D843*('Segments'!$D$34*D835*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*D835+0.4357405005*D835+0.0330936548*D835+0.0328406739))</f>
         <v/>
       </c>
       <c r="E846" s="18">
-        <f>E836*('Segments'!$D$27*E835*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*E834+0.4357405005*E834+0.0330936548*E835+0.0328406739))+E837*('Segments'!$D$28*E835*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*E834+0.4357405005*E834+0.0330936548*E835+0.0328406739))+E838*('Segments'!$D$29*E835*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*E834+0.4357405005*E834+0.0330936548*E835+0.0328406739))+E839*('Segments'!$D$30*E835*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*E834+0.4357405005*E834+0.0330936548*E835+0.0328406739))+E840*('Segments'!$D$31*E835*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*E834+0.4357405005*E834+0.0330936548*E835+0.0328406739))+E841*('Segments'!$D$32*E835*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*E834+0.4357405005*E834+0.0330936548*E835+0.0328406739))+E842*('Segments'!$D$33*E835*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*E834+0.4357405005*E834+0.0330936548*E835+0.0328406739))+E843*('Segments'!$D$34*E835*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*E834+0.4357405005*E834+0.0330936548*E835+0.0328406739))</f>
+        <f>E836*('Segments'!$D$27*E835*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*E835+0.4357405005*E835+0.0330936548*E835+0.0328406739))+E837*('Segments'!$D$28*E835*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*E835+0.4357405005*E835+0.0330936548*E835+0.0328406739))+E838*('Segments'!$D$29*E835*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*E835+0.4357405005*E835+0.0330936548*E835+0.0328406739))+E839*('Segments'!$D$30*E835*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*E835+0.4357405005*E835+0.0330936548*E835+0.0328406739))+E840*('Segments'!$D$31*E835*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*E835+0.4357405005*E835+0.0330936548*E835+0.0328406739))+E841*('Segments'!$D$32*E835*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*E835+0.4357405005*E835+0.0330936548*E835+0.0328406739))+E842*('Segments'!$D$33*E835*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*E835+0.4357405005*E835+0.0330936548*E835+0.0328406739))+E843*('Segments'!$D$34*E835*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*E835+0.4357405005*E835+0.0330936548*E835+0.0328406739))</f>
         <v/>
       </c>
       <c r="F846" s="18">
-        <f>F836*('Segments'!$D$27*F835*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*F834+0.4357405005*F834+0.0330936548*F835+0.0328406739))+F837*('Segments'!$D$28*F835*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*F834+0.4357405005*F834+0.0330936548*F835+0.0328406739))+F838*('Segments'!$D$29*F835*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*F834+0.4357405005*F834+0.0330936548*F835+0.0328406739))+F839*('Segments'!$D$30*F835*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*F834+0.4357405005*F834+0.0330936548*F835+0.0328406739))+F840*('Segments'!$D$31*F835*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*F834+0.4357405005*F834+0.0330936548*F835+0.0328406739))+F841*('Segments'!$D$32*F835*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*F834+0.4357405005*F834+0.0330936548*F835+0.0328406739))+F842*('Segments'!$D$33*F835*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*F834+0.4357405005*F834+0.0330936548*F835+0.0328406739))+F843*('Segments'!$D$34*F835*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*F834+0.4357405005*F834+0.0330936548*F835+0.0328406739))</f>
+        <f>F836*('Segments'!$D$27*F835*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*F835+0.4357405005*F835+0.0330936548*F835+0.0328406739))+F837*('Segments'!$D$28*F835*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*F835+0.4357405005*F835+0.0330936548*F835+0.0328406739))+F838*('Segments'!$D$29*F835*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*F835+0.4357405005*F835+0.0330936548*F835+0.0328406739))+F839*('Segments'!$D$30*F835*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*F835+0.4357405005*F835+0.0330936548*F835+0.0328406739))+F840*('Segments'!$D$31*F835*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*F835+0.4357405005*F835+0.0330936548*F835+0.0328406739))+F841*('Segments'!$D$32*F835*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*F835+0.4357405005*F835+0.0330936548*F835+0.0328406739))+F842*('Segments'!$D$33*F835*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*F835+0.4357405005*F835+0.0330936548*F835+0.0328406739))+F843*('Segments'!$D$34*F835*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*F835+0.4357405005*F835+0.0330936548*F835+0.0328406739))</f>
         <v/>
       </c>
       <c r="G846" s="18">
-        <f>G836*('Segments'!$D$27*G835*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*G834+0.4357405005*G834+0.0330936548*G835+0.0328406739))+G837*('Segments'!$D$28*G835*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*G834+0.4357405005*G834+0.0330936548*G835+0.0328406739))+G838*('Segments'!$D$29*G835*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*G834+0.4357405005*G834+0.0330936548*G835+0.0328406739))+G839*('Segments'!$D$30*G835*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*G834+0.4357405005*G834+0.0330936548*G835+0.0328406739))+G840*('Segments'!$D$31*G835*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*G834+0.4357405005*G834+0.0330936548*G835+0.0328406739))+G841*('Segments'!$D$32*G835*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*G834+0.4357405005*G834+0.0330936548*G835+0.0328406739))+G842*('Segments'!$D$33*G835*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*G834+0.4357405005*G834+0.0330936548*G835+0.0328406739))+G843*('Segments'!$D$34*G835*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*G834+0.4357405005*G834+0.0330936548*G835+0.0328406739))</f>
+        <f>G836*('Segments'!$D$27*G835*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*G835+0.4357405005*G835+0.0330936548*G835+0.0328406739))+G837*('Segments'!$D$28*G835*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*G835+0.4357405005*G835+0.0330936548*G835+0.0328406739))+G838*('Segments'!$D$29*G835*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*G835+0.4357405005*G835+0.0330936548*G835+0.0328406739))+G839*('Segments'!$D$30*G835*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*G835+0.4357405005*G835+0.0330936548*G835+0.0328406739))+G840*('Segments'!$D$31*G835*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*G835+0.4357405005*G835+0.0330936548*G835+0.0328406739))+G841*('Segments'!$D$32*G835*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*G835+0.4357405005*G835+0.0330936548*G835+0.0328406739))+G842*('Segments'!$D$33*G835*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*G835+0.4357405005*G835+0.0330936548*G835+0.0328406739))+G843*('Segments'!$D$34*G835*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*G835+0.4357405005*G835+0.0330936548*G835+0.0328406739))</f>
         <v/>
       </c>
     </row>
@@ -21576,23 +21576,23 @@
         </is>
       </c>
       <c r="C895" s="18">
-        <f>C885*('Segments'!$D$27*C884*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*C883+0.4357405005*C883+0.0330936548*C884+0.0328406739))+C886*('Segments'!$D$28*C884*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*C883+0.4357405005*C883+0.0330936548*C884+0.0328406739))+C887*('Segments'!$D$29*C884*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*C883+0.4357405005*C883+0.0330936548*C884+0.0328406739))+C888*('Segments'!$D$30*C884*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*C883+0.4357405005*C883+0.0330936548*C884+0.0328406739))+C889*('Segments'!$D$31*C884*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*C883+0.4357405005*C883+0.0330936548*C884+0.0328406739))+C890*('Segments'!$D$32*C884*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*C883+0.4357405005*C883+0.0330936548*C884+0.0328406739))+C891*('Segments'!$D$33*C884*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*C883+0.4357405005*C883+0.0330936548*C884+0.0328406739))+C892*('Segments'!$D$34*C884*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*C883+0.4357405005*C883+0.0330936548*C884+0.0328406739))</f>
+        <f>C885*('Segments'!$D$27*C884*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*C884+0.4357405005*C884+0.0330936548*C884+0.0328406739))+C886*('Segments'!$D$28*C884*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*C884+0.4357405005*C884+0.0330936548*C884+0.0328406739))+C887*('Segments'!$D$29*C884*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*C884+0.4357405005*C884+0.0330936548*C884+0.0328406739))+C888*('Segments'!$D$30*C884*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*C884+0.4357405005*C884+0.0330936548*C884+0.0328406739))+C889*('Segments'!$D$31*C884*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*C884+0.4357405005*C884+0.0330936548*C884+0.0328406739))+C890*('Segments'!$D$32*C884*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*C884+0.4357405005*C884+0.0330936548*C884+0.0328406739))+C891*('Segments'!$D$33*C884*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*C884+0.4357405005*C884+0.0330936548*C884+0.0328406739))+C892*('Segments'!$D$34*C884*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*C884+0.4357405005*C884+0.0330936548*C884+0.0328406739))</f>
         <v/>
       </c>
       <c r="D895" s="18">
-        <f>D885*('Segments'!$D$27*D884*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*D883+0.4357405005*D883+0.0330936548*D884+0.0328406739))+D886*('Segments'!$D$28*D884*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*D883+0.4357405005*D883+0.0330936548*D884+0.0328406739))+D887*('Segments'!$D$29*D884*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*D883+0.4357405005*D883+0.0330936548*D884+0.0328406739))+D888*('Segments'!$D$30*D884*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*D883+0.4357405005*D883+0.0330936548*D884+0.0328406739))+D889*('Segments'!$D$31*D884*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*D883+0.4357405005*D883+0.0330936548*D884+0.0328406739))+D890*('Segments'!$D$32*D884*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*D883+0.4357405005*D883+0.0330936548*D884+0.0328406739))+D891*('Segments'!$D$33*D884*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*D883+0.4357405005*D883+0.0330936548*D884+0.0328406739))+D892*('Segments'!$D$34*D884*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*D883+0.4357405005*D883+0.0330936548*D884+0.0328406739))</f>
+        <f>D885*('Segments'!$D$27*D884*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*D884+0.4357405005*D884+0.0330936548*D884+0.0328406739))+D886*('Segments'!$D$28*D884*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*D884+0.4357405005*D884+0.0330936548*D884+0.0328406739))+D887*('Segments'!$D$29*D884*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*D884+0.4357405005*D884+0.0330936548*D884+0.0328406739))+D888*('Segments'!$D$30*D884*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*D884+0.4357405005*D884+0.0330936548*D884+0.0328406739))+D889*('Segments'!$D$31*D884*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*D884+0.4357405005*D884+0.0330936548*D884+0.0328406739))+D890*('Segments'!$D$32*D884*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*D884+0.4357405005*D884+0.0330936548*D884+0.0328406739))+D891*('Segments'!$D$33*D884*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*D884+0.4357405005*D884+0.0330936548*D884+0.0328406739))+D892*('Segments'!$D$34*D884*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*D884+0.4357405005*D884+0.0330936548*D884+0.0328406739))</f>
         <v/>
       </c>
       <c r="E895" s="18">
-        <f>E885*('Segments'!$D$27*E884*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*E883+0.4357405005*E883+0.0330936548*E884+0.0328406739))+E886*('Segments'!$D$28*E884*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*E883+0.4357405005*E883+0.0330936548*E884+0.0328406739))+E887*('Segments'!$D$29*E884*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*E883+0.4357405005*E883+0.0330936548*E884+0.0328406739))+E888*('Segments'!$D$30*E884*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*E883+0.4357405005*E883+0.0330936548*E884+0.0328406739))+E889*('Segments'!$D$31*E884*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*E883+0.4357405005*E883+0.0330936548*E884+0.0328406739))+E890*('Segments'!$D$32*E884*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*E883+0.4357405005*E883+0.0330936548*E884+0.0328406739))+E891*('Segments'!$D$33*E884*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*E883+0.4357405005*E883+0.0330936548*E884+0.0328406739))+E892*('Segments'!$D$34*E884*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*E883+0.4357405005*E883+0.0330936548*E884+0.0328406739))</f>
+        <f>E885*('Segments'!$D$27*E884*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*E884+0.4357405005*E884+0.0330936548*E884+0.0328406739))+E886*('Segments'!$D$28*E884*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*E884+0.4357405005*E884+0.0330936548*E884+0.0328406739))+E887*('Segments'!$D$29*E884*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*E884+0.4357405005*E884+0.0330936548*E884+0.0328406739))+E888*('Segments'!$D$30*E884*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*E884+0.4357405005*E884+0.0330936548*E884+0.0328406739))+E889*('Segments'!$D$31*E884*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*E884+0.4357405005*E884+0.0330936548*E884+0.0328406739))+E890*('Segments'!$D$32*E884*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*E884+0.4357405005*E884+0.0330936548*E884+0.0328406739))+E891*('Segments'!$D$33*E884*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*E884+0.4357405005*E884+0.0330936548*E884+0.0328406739))+E892*('Segments'!$D$34*E884*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*E884+0.4357405005*E884+0.0330936548*E884+0.0328406739))</f>
         <v/>
       </c>
       <c r="F895" s="18">
-        <f>F885*('Segments'!$D$27*F884*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*F883+0.4357405005*F883+0.0330936548*F884+0.0328406739))+F886*('Segments'!$D$28*F884*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*F883+0.4357405005*F883+0.0330936548*F884+0.0328406739))+F887*('Segments'!$D$29*F884*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*F883+0.4357405005*F883+0.0330936548*F884+0.0328406739))+F888*('Segments'!$D$30*F884*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*F883+0.4357405005*F883+0.0330936548*F884+0.0328406739))+F889*('Segments'!$D$31*F884*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*F883+0.4357405005*F883+0.0330936548*F884+0.0328406739))+F890*('Segments'!$D$32*F884*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*F883+0.4357405005*F883+0.0330936548*F884+0.0328406739))+F891*('Segments'!$D$33*F884*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*F883+0.4357405005*F883+0.0330936548*F884+0.0328406739))+F892*('Segments'!$D$34*F884*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*F883+0.4357405005*F883+0.0330936548*F884+0.0328406739))</f>
+        <f>F885*('Segments'!$D$27*F884*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*F884+0.4357405005*F884+0.0330936548*F884+0.0328406739))+F886*('Segments'!$D$28*F884*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*F884+0.4357405005*F884+0.0330936548*F884+0.0328406739))+F887*('Segments'!$D$29*F884*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*F884+0.4357405005*F884+0.0330936548*F884+0.0328406739))+F888*('Segments'!$D$30*F884*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*F884+0.4357405005*F884+0.0330936548*F884+0.0328406739))+F889*('Segments'!$D$31*F884*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*F884+0.4357405005*F884+0.0330936548*F884+0.0328406739))+F890*('Segments'!$D$32*F884*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*F884+0.4357405005*F884+0.0330936548*F884+0.0328406739))+F891*('Segments'!$D$33*F884*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*F884+0.4357405005*F884+0.0330936548*F884+0.0328406739))+F892*('Segments'!$D$34*F884*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*F884+0.4357405005*F884+0.0330936548*F884+0.0328406739))</f>
         <v/>
       </c>
       <c r="G895" s="18">
-        <f>G885*('Segments'!$D$27*G884*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*G883+0.4357405005*G883+0.0330936548*G884+0.0328406739))+G886*('Segments'!$D$28*G884*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*G883+0.4357405005*G883+0.0330936548*G884+0.0328406739))+G887*('Segments'!$D$29*G884*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*G883+0.4357405005*G883+0.0330936548*G884+0.0328406739))+G888*('Segments'!$D$30*G884*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*G883+0.4357405005*G883+0.0330936548*G884+0.0328406739))+G889*('Segments'!$D$31*G884*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*G883+0.4357405005*G883+0.0330936548*G884+0.0328406739))+G890*('Segments'!$D$32*G884*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*G883+0.4357405005*G883+0.0330936548*G884+0.0328406739))+G891*('Segments'!$D$33*G884*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*G883+0.4357405005*G883+0.0330936548*G884+0.0328406739))+G892*('Segments'!$D$34*G884*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*G883+0.4357405005*G883+0.0330936548*G884+0.0328406739))</f>
+        <f>G885*('Segments'!$D$27*G884*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*G884+0.4357405005*G884+0.0330936548*G884+0.0328406739))+G886*('Segments'!$D$28*G884*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*G884+0.4357405005*G884+0.0330936548*G884+0.0328406739))+G887*('Segments'!$D$29*G884*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*G884+0.4357405005*G884+0.0330936548*G884+0.0328406739))+G888*('Segments'!$D$30*G884*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*G884+0.4357405005*G884+0.0330936548*G884+0.0328406739))+G889*('Segments'!$D$31*G884*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*G884+0.4357405005*G884+0.0330936548*G884+0.0328406739))+G890*('Segments'!$D$32*G884*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*G884+0.4357405005*G884+0.0330936548*G884+0.0328406739))+G891*('Segments'!$D$33*G884*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*G884+0.4357405005*G884+0.0330936548*G884+0.0328406739))+G892*('Segments'!$D$34*G884*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*G884+0.4357405005*G884+0.0330936548*G884+0.0328406739))</f>
         <v/>
       </c>
     </row>
@@ -22646,23 +22646,23 @@
         </is>
       </c>
       <c r="C944" s="18">
-        <f>C934*('Segments'!$D$27*C933*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*C932+0.4357405005*C932+0.0330936548*C933+0.0328406739))+C935*('Segments'!$D$28*C933*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*C932+0.4357405005*C932+0.0330936548*C933+0.0328406739))+C936*('Segments'!$D$29*C933*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*C932+0.4357405005*C932+0.0330936548*C933+0.0328406739))+C937*('Segments'!$D$30*C933*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*C932+0.4357405005*C932+0.0330936548*C933+0.0328406739))+C938*('Segments'!$D$31*C933*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*C932+0.4357405005*C932+0.0330936548*C933+0.0328406739))+C939*('Segments'!$D$32*C933*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*C932+0.4357405005*C932+0.0330936548*C933+0.0328406739))+C940*('Segments'!$D$33*C933*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*C932+0.4357405005*C932+0.0330936548*C933+0.0328406739))+C941*('Segments'!$D$34*C933*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*C932+0.4357405005*C932+0.0330936548*C933+0.0328406739))</f>
+        <f>C934*('Segments'!$D$27*C933*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*C933+0.4357405005*C933+0.0330936548*C933+0.0328406739))+C935*('Segments'!$D$28*C933*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*C933+0.4357405005*C933+0.0330936548*C933+0.0328406739))+C936*('Segments'!$D$29*C933*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*C933+0.4357405005*C933+0.0330936548*C933+0.0328406739))+C937*('Segments'!$D$30*C933*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*C933+0.4357405005*C933+0.0330936548*C933+0.0328406739))+C938*('Segments'!$D$31*C933*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*C933+0.4357405005*C933+0.0330936548*C933+0.0328406739))+C939*('Segments'!$D$32*C933*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*C933+0.4357405005*C933+0.0330936548*C933+0.0328406739))+C940*('Segments'!$D$33*C933*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*C933+0.4357405005*C933+0.0330936548*C933+0.0328406739))+C941*('Segments'!$D$34*C933*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*C933+0.4357405005*C933+0.0330936548*C933+0.0328406739))</f>
         <v/>
       </c>
       <c r="D944" s="18">
-        <f>D934*('Segments'!$D$27*D933*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*D932+0.4357405005*D932+0.0330936548*D933+0.0328406739))+D935*('Segments'!$D$28*D933*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*D932+0.4357405005*D932+0.0330936548*D933+0.0328406739))+D936*('Segments'!$D$29*D933*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*D932+0.4357405005*D932+0.0330936548*D933+0.0328406739))+D937*('Segments'!$D$30*D933*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*D932+0.4357405005*D932+0.0330936548*D933+0.0328406739))+D938*('Segments'!$D$31*D933*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*D932+0.4357405005*D932+0.0330936548*D933+0.0328406739))+D939*('Segments'!$D$32*D933*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*D932+0.4357405005*D932+0.0330936548*D933+0.0328406739))+D940*('Segments'!$D$33*D933*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*D932+0.4357405005*D932+0.0330936548*D933+0.0328406739))+D941*('Segments'!$D$34*D933*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*D932+0.4357405005*D932+0.0330936548*D933+0.0328406739))</f>
+        <f>D934*('Segments'!$D$27*D933*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*D933+0.4357405005*D933+0.0330936548*D933+0.0328406739))+D935*('Segments'!$D$28*D933*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*D933+0.4357405005*D933+0.0330936548*D933+0.0328406739))+D936*('Segments'!$D$29*D933*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*D933+0.4357405005*D933+0.0330936548*D933+0.0328406739))+D937*('Segments'!$D$30*D933*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*D933+0.4357405005*D933+0.0330936548*D933+0.0328406739))+D938*('Segments'!$D$31*D933*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*D933+0.4357405005*D933+0.0330936548*D933+0.0328406739))+D939*('Segments'!$D$32*D933*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*D933+0.4357405005*D933+0.0330936548*D933+0.0328406739))+D940*('Segments'!$D$33*D933*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*D933+0.4357405005*D933+0.0330936548*D933+0.0328406739))+D941*('Segments'!$D$34*D933*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*D933+0.4357405005*D933+0.0330936548*D933+0.0328406739))</f>
         <v/>
       </c>
       <c r="E944" s="18">
-        <f>E934*('Segments'!$D$27*E933*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*E932+0.4357405005*E932+0.0330936548*E933+0.0328406739))+E935*('Segments'!$D$28*E933*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*E932+0.4357405005*E932+0.0330936548*E933+0.0328406739))+E936*('Segments'!$D$29*E933*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*E932+0.4357405005*E932+0.0330936548*E933+0.0328406739))+E937*('Segments'!$D$30*E933*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*E932+0.4357405005*E932+0.0330936548*E933+0.0328406739))+E938*('Segments'!$D$31*E933*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*E932+0.4357405005*E932+0.0330936548*E933+0.0328406739))+E939*('Segments'!$D$32*E933*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*E932+0.4357405005*E932+0.0330936548*E933+0.0328406739))+E940*('Segments'!$D$33*E933*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*E932+0.4357405005*E932+0.0330936548*E933+0.0328406739))+E941*('Segments'!$D$34*E933*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*E932+0.4357405005*E932+0.0330936548*E933+0.0328406739))</f>
+        <f>E934*('Segments'!$D$27*E933*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*E933+0.4357405005*E933+0.0330936548*E933+0.0328406739))+E935*('Segments'!$D$28*E933*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*E933+0.4357405005*E933+0.0330936548*E933+0.0328406739))+E936*('Segments'!$D$29*E933*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*E933+0.4357405005*E933+0.0330936548*E933+0.0328406739))+E937*('Segments'!$D$30*E933*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*E933+0.4357405005*E933+0.0330936548*E933+0.0328406739))+E938*('Segments'!$D$31*E933*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*E933+0.4357405005*E933+0.0330936548*E933+0.0328406739))+E939*('Segments'!$D$32*E933*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*E933+0.4357405005*E933+0.0330936548*E933+0.0328406739))+E940*('Segments'!$D$33*E933*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*E933+0.4357405005*E933+0.0330936548*E933+0.0328406739))+E941*('Segments'!$D$34*E933*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*E933+0.4357405005*E933+0.0330936548*E933+0.0328406739))</f>
         <v/>
       </c>
       <c r="F944" s="18">
-        <f>F934*('Segments'!$D$27*F933*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*F932+0.4357405005*F932+0.0330936548*F933+0.0328406739))+F935*('Segments'!$D$28*F933*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*F932+0.4357405005*F932+0.0330936548*F933+0.0328406739))+F936*('Segments'!$D$29*F933*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*F932+0.4357405005*F932+0.0330936548*F933+0.0328406739))+F937*('Segments'!$D$30*F933*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*F932+0.4357405005*F932+0.0330936548*F933+0.0328406739))+F938*('Segments'!$D$31*F933*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*F932+0.4357405005*F932+0.0330936548*F933+0.0328406739))+F939*('Segments'!$D$32*F933*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*F932+0.4357405005*F932+0.0330936548*F933+0.0328406739))+F940*('Segments'!$D$33*F933*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*F932+0.4357405005*F932+0.0330936548*F933+0.0328406739))+F941*('Segments'!$D$34*F933*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*F932+0.4357405005*F932+0.0330936548*F933+0.0328406739))</f>
+        <f>F934*('Segments'!$D$27*F933*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*F933+0.4357405005*F933+0.0330936548*F933+0.0328406739))+F935*('Segments'!$D$28*F933*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*F933+0.4357405005*F933+0.0330936548*F933+0.0328406739))+F936*('Segments'!$D$29*F933*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*F933+0.4357405005*F933+0.0330936548*F933+0.0328406739))+F937*('Segments'!$D$30*F933*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*F933+0.4357405005*F933+0.0330936548*F933+0.0328406739))+F938*('Segments'!$D$31*F933*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*F933+0.4357405005*F933+0.0330936548*F933+0.0328406739))+F939*('Segments'!$D$32*F933*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*F933+0.4357405005*F933+0.0330936548*F933+0.0328406739))+F940*('Segments'!$D$33*F933*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*F933+0.4357405005*F933+0.0330936548*F933+0.0328406739))+F941*('Segments'!$D$34*F933*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*F933+0.4357405005*F933+0.0330936548*F933+0.0328406739))</f>
         <v/>
       </c>
       <c r="G944" s="18">
-        <f>G934*('Segments'!$D$27*G933*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*G932+0.4357405005*G932+0.0330936548*G933+0.0328406739))+G935*('Segments'!$D$28*G933*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*G932+0.4357405005*G932+0.0330936548*G933+0.0328406739))+G936*('Segments'!$D$29*G933*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*G932+0.4357405005*G932+0.0330936548*G933+0.0328406739))+G937*('Segments'!$D$30*G933*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*G932+0.4357405005*G932+0.0330936548*G933+0.0328406739))+G938*('Segments'!$D$31*G933*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*G932+0.4357405005*G932+0.0330936548*G933+0.0328406739))+G939*('Segments'!$D$32*G933*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*G932+0.4357405005*G932+0.0330936548*G933+0.0328406739))+G940*('Segments'!$D$33*G933*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*G932+0.4357405005*G932+0.0330936548*G933+0.0328406739))+G941*('Segments'!$D$34*G933*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*G932+0.4357405005*G932+0.0330936548*G933+0.0328406739))</f>
+        <f>G934*('Segments'!$D$27*G933*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*G933+0.4357405005*G933+0.0330936548*G933+0.0328406739))+G935*('Segments'!$D$28*G933*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*G933+0.4357405005*G933+0.0330936548*G933+0.0328406739))+G936*('Segments'!$D$29*G933*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*G933+0.4357405005*G933+0.0330936548*G933+0.0328406739))+G937*('Segments'!$D$30*G933*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*G933+0.4357405005*G933+0.0330936548*G933+0.0328406739))+G938*('Segments'!$D$31*G933*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*G933+0.4357405005*G933+0.0330936548*G933+0.0328406739))+G939*('Segments'!$D$32*G933*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*G933+0.4357405005*G933+0.0330936548*G933+0.0328406739))+G940*('Segments'!$D$33*G933*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*G933+0.4357405005*G933+0.0330936548*G933+0.0328406739))+G941*('Segments'!$D$34*G933*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*G933+0.4357405005*G933+0.0330936548*G933+0.0328406739))</f>
         <v/>
       </c>
     </row>
@@ -23716,23 +23716,23 @@
         </is>
       </c>
       <c r="C993" s="18">
-        <f>C983*('Segments'!$D$27*C982*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*C981+0.4357405005*C981+0.0330936548*C982+0.0328406739))+C984*('Segments'!$D$28*C982*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*C981+0.4357405005*C981+0.0330936548*C982+0.0328406739))+C985*('Segments'!$D$29*C982*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*C981+0.4357405005*C981+0.0330936548*C982+0.0328406739))+C986*('Segments'!$D$30*C982*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*C981+0.4357405005*C981+0.0330936548*C982+0.0328406739))+C987*('Segments'!$D$31*C982*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*C981+0.4357405005*C981+0.0330936548*C982+0.0328406739))+C988*('Segments'!$D$32*C982*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*C981+0.4357405005*C981+0.0330936548*C982+0.0328406739))+C989*('Segments'!$D$33*C982*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*C981+0.4357405005*C981+0.0330936548*C982+0.0328406739))+C990*('Segments'!$D$34*C982*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*C981+0.4357405005*C981+0.0330936548*C982+0.0328406739))</f>
+        <f>C983*('Segments'!$D$27*C982*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*C982+0.4357405005*C982+0.0330936548*C982+0.0328406739))+C984*('Segments'!$D$28*C982*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*C982+0.4357405005*C982+0.0330936548*C982+0.0328406739))+C985*('Segments'!$D$29*C982*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*C982+0.4357405005*C982+0.0330936548*C982+0.0328406739))+C986*('Segments'!$D$30*C982*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*C982+0.4357405005*C982+0.0330936548*C982+0.0328406739))+C987*('Segments'!$D$31*C982*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*C982+0.4357405005*C982+0.0330936548*C982+0.0328406739))+C988*('Segments'!$D$32*C982*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*C982+0.4357405005*C982+0.0330936548*C982+0.0328406739))+C989*('Segments'!$D$33*C982*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*C982+0.4357405005*C982+0.0330936548*C982+0.0328406739))+C990*('Segments'!$D$34*C982*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*C982+0.4357405005*C982+0.0330936548*C982+0.0328406739))</f>
         <v/>
       </c>
       <c r="D993" s="18">
-        <f>D983*('Segments'!$D$27*D982*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*D981+0.4357405005*D981+0.0330936548*D982+0.0328406739))+D984*('Segments'!$D$28*D982*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*D981+0.4357405005*D981+0.0330936548*D982+0.0328406739))+D985*('Segments'!$D$29*D982*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*D981+0.4357405005*D981+0.0330936548*D982+0.0328406739))+D986*('Segments'!$D$30*D982*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*D981+0.4357405005*D981+0.0330936548*D982+0.0328406739))+D987*('Segments'!$D$31*D982*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*D981+0.4357405005*D981+0.0330936548*D982+0.0328406739))+D988*('Segments'!$D$32*D982*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*D981+0.4357405005*D981+0.0330936548*D982+0.0328406739))+D989*('Segments'!$D$33*D982*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*D981+0.4357405005*D981+0.0330936548*D982+0.0328406739))+D990*('Segments'!$D$34*D982*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*D981+0.4357405005*D981+0.0330936548*D982+0.0328406739))</f>
+        <f>D983*('Segments'!$D$27*D982*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*D982+0.4357405005*D982+0.0330936548*D982+0.0328406739))+D984*('Segments'!$D$28*D982*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*D982+0.4357405005*D982+0.0330936548*D982+0.0328406739))+D985*('Segments'!$D$29*D982*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*D982+0.4357405005*D982+0.0330936548*D982+0.0328406739))+D986*('Segments'!$D$30*D982*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*D982+0.4357405005*D982+0.0330936548*D982+0.0328406739))+D987*('Segments'!$D$31*D982*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*D982+0.4357405005*D982+0.0330936548*D982+0.0328406739))+D988*('Segments'!$D$32*D982*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*D982+0.4357405005*D982+0.0330936548*D982+0.0328406739))+D989*('Segments'!$D$33*D982*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*D982+0.4357405005*D982+0.0330936548*D982+0.0328406739))+D990*('Segments'!$D$34*D982*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*D982+0.4357405005*D982+0.0330936548*D982+0.0328406739))</f>
         <v/>
       </c>
       <c r="E993" s="18">
-        <f>E983*('Segments'!$D$27*E982*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*E981+0.4357405005*E981+0.0330936548*E982+0.0328406739))+E984*('Segments'!$D$28*E982*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*E981+0.4357405005*E981+0.0330936548*E982+0.0328406739))+E985*('Segments'!$D$29*E982*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*E981+0.4357405005*E981+0.0330936548*E982+0.0328406739))+E986*('Segments'!$D$30*E982*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*E981+0.4357405005*E981+0.0330936548*E982+0.0328406739))+E987*('Segments'!$D$31*E982*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*E981+0.4357405005*E981+0.0330936548*E982+0.0328406739))+E988*('Segments'!$D$32*E982*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*E981+0.4357405005*E981+0.0330936548*E982+0.0328406739))+E989*('Segments'!$D$33*E982*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*E981+0.4357405005*E981+0.0330936548*E982+0.0328406739))+E990*('Segments'!$D$34*E982*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*E981+0.4357405005*E981+0.0330936548*E982+0.0328406739))</f>
+        <f>E983*('Segments'!$D$27*E982*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*E982+0.4357405005*E982+0.0330936548*E982+0.0328406739))+E984*('Segments'!$D$28*E982*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*E982+0.4357405005*E982+0.0330936548*E982+0.0328406739))+E985*('Segments'!$D$29*E982*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*E982+0.4357405005*E982+0.0330936548*E982+0.0328406739))+E986*('Segments'!$D$30*E982*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*E982+0.4357405005*E982+0.0330936548*E982+0.0328406739))+E987*('Segments'!$D$31*E982*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*E982+0.4357405005*E982+0.0330936548*E982+0.0328406739))+E988*('Segments'!$D$32*E982*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*E982+0.4357405005*E982+0.0330936548*E982+0.0328406739))+E989*('Segments'!$D$33*E982*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*E982+0.4357405005*E982+0.0330936548*E982+0.0328406739))+E990*('Segments'!$D$34*E982*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*E982+0.4357405005*E982+0.0330936548*E982+0.0328406739))</f>
         <v/>
       </c>
       <c r="F993" s="18">
-        <f>F983*('Segments'!$D$27*F982*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*F981+0.4357405005*F981+0.0330936548*F982+0.0328406739))+F984*('Segments'!$D$28*F982*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*F981+0.4357405005*F981+0.0330936548*F982+0.0328406739))+F985*('Segments'!$D$29*F982*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*F981+0.4357405005*F981+0.0330936548*F982+0.0328406739))+F986*('Segments'!$D$30*F982*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*F981+0.4357405005*F981+0.0330936548*F982+0.0328406739))+F987*('Segments'!$D$31*F982*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*F981+0.4357405005*F981+0.0330936548*F982+0.0328406739))+F988*('Segments'!$D$32*F982*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*F981+0.4357405005*F981+0.0330936548*F982+0.0328406739))+F989*('Segments'!$D$33*F982*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*F981+0.4357405005*F981+0.0330936548*F982+0.0328406739))+F990*('Segments'!$D$34*F982*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*F981+0.4357405005*F981+0.0330936548*F982+0.0328406739))</f>
+        <f>F983*('Segments'!$D$27*F982*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*F982+0.4357405005*F982+0.0330936548*F982+0.0328406739))+F984*('Segments'!$D$28*F982*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*F982+0.4357405005*F982+0.0330936548*F982+0.0328406739))+F985*('Segments'!$D$29*F982*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*F982+0.4357405005*F982+0.0330936548*F982+0.0328406739))+F986*('Segments'!$D$30*F982*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*F982+0.4357405005*F982+0.0330936548*F982+0.0328406739))+F987*('Segments'!$D$31*F982*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*F982+0.4357405005*F982+0.0330936548*F982+0.0328406739))+F988*('Segments'!$D$32*F982*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*F982+0.4357405005*F982+0.0330936548*F982+0.0328406739))+F989*('Segments'!$D$33*F982*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*F982+0.4357405005*F982+0.0330936548*F982+0.0328406739))+F990*('Segments'!$D$34*F982*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*F982+0.4357405005*F982+0.0330936548*F982+0.0328406739))</f>
         <v/>
       </c>
       <c r="G993" s="18">
-        <f>G983*('Segments'!$D$27*G982*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*G981+0.4357405005*G981+0.0330936548*G982+0.0328406739))+G984*('Segments'!$D$28*G982*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*G981+0.4357405005*G981+0.0330936548*G982+0.0328406739))+G985*('Segments'!$D$29*G982*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*G981+0.4357405005*G981+0.0330936548*G982+0.0328406739))+G986*('Segments'!$D$30*G982*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*G981+0.4357405005*G981+0.0330936548*G982+0.0328406739))+G987*('Segments'!$D$31*G982*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*G981+0.4357405005*G981+0.0330936548*G982+0.0328406739))+G988*('Segments'!$D$32*G982*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*G981+0.4357405005*G981+0.0330936548*G982+0.0328406739))+G989*('Segments'!$D$33*G982*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*G981+0.4357405005*G981+0.0330936548*G982+0.0328406739))+G990*('Segments'!$D$34*G982*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*G981+0.4357405005*G981+0.0330936548*G982+0.0328406739))</f>
+        <f>G983*('Segments'!$D$27*G982*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*G982+0.4357405005*G982+0.0330936548*G982+0.0328406739))+G984*('Segments'!$D$28*G982*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*G982+0.4357405005*G982+0.0330936548*G982+0.0328406739))+G985*('Segments'!$D$29*G982*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*G982+0.4357405005*G982+0.0330936548*G982+0.0328406739))+G986*('Segments'!$D$30*G982*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*G982+0.4357405005*G982+0.0330936548*G982+0.0328406739))+G987*('Segments'!$D$31*G982*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*G982+0.4357405005*G982+0.0330936548*G982+0.0328406739))+G988*('Segments'!$D$32*G982*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*G982+0.4357405005*G982+0.0330936548*G982+0.0328406739))+G989*('Segments'!$D$33*G982*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*G982+0.4357405005*G982+0.0330936548*G982+0.0328406739))+G990*('Segments'!$D$34*G982*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*G982+0.4357405005*G982+0.0330936548*G982+0.0328406739))</f>
         <v/>
       </c>
     </row>
@@ -24786,23 +24786,23 @@
         </is>
       </c>
       <c r="C1042" s="18">
-        <f>C1032*('Segments'!$D$27*C1031*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*C1030+0.4357405005*C1030+0.0330936548*C1031+0.0328406739))+C1033*('Segments'!$D$28*C1031*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*C1030+0.4357405005*C1030+0.0330936548*C1031+0.0328406739))+C1034*('Segments'!$D$29*C1031*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*C1030+0.4357405005*C1030+0.0330936548*C1031+0.0328406739))+C1035*('Segments'!$D$30*C1031*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*C1030+0.4357405005*C1030+0.0330936548*C1031+0.0328406739))+C1036*('Segments'!$D$31*C1031*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*C1030+0.4357405005*C1030+0.0330936548*C1031+0.0328406739))+C1037*('Segments'!$D$32*C1031*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*C1030+0.4357405005*C1030+0.0330936548*C1031+0.0328406739))+C1038*('Segments'!$D$33*C1031*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*C1030+0.4357405005*C1030+0.0330936548*C1031+0.0328406739))+C1039*('Segments'!$D$34*C1031*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*C1030+0.4357405005*C1030+0.0330936548*C1031+0.0328406739))</f>
+        <f>C1032*('Segments'!$D$27*C1031*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*C1031+0.4357405005*C1031+0.0330936548*C1031+0.0328406739))+C1033*('Segments'!$D$28*C1031*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*C1031+0.4357405005*C1031+0.0330936548*C1031+0.0328406739))+C1034*('Segments'!$D$29*C1031*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*C1031+0.4357405005*C1031+0.0330936548*C1031+0.0328406739))+C1035*('Segments'!$D$30*C1031*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*C1031+0.4357405005*C1031+0.0330936548*C1031+0.0328406739))+C1036*('Segments'!$D$31*C1031*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*C1031+0.4357405005*C1031+0.0330936548*C1031+0.0328406739))+C1037*('Segments'!$D$32*C1031*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*C1031+0.4357405005*C1031+0.0330936548*C1031+0.0328406739))+C1038*('Segments'!$D$33*C1031*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*C1031+0.4357405005*C1031+0.0330936548*C1031+0.0328406739))+C1039*('Segments'!$D$34*C1031*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*C1031+0.4357405005*C1031+0.0330936548*C1031+0.0328406739))</f>
         <v/>
       </c>
       <c r="D1042" s="18">
-        <f>D1032*('Segments'!$D$27*D1031*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*D1030+0.4357405005*D1030+0.0330936548*D1031+0.0328406739))+D1033*('Segments'!$D$28*D1031*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*D1030+0.4357405005*D1030+0.0330936548*D1031+0.0328406739))+D1034*('Segments'!$D$29*D1031*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*D1030+0.4357405005*D1030+0.0330936548*D1031+0.0328406739))+D1035*('Segments'!$D$30*D1031*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*D1030+0.4357405005*D1030+0.0330936548*D1031+0.0328406739))+D1036*('Segments'!$D$31*D1031*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*D1030+0.4357405005*D1030+0.0330936548*D1031+0.0328406739))+D1037*('Segments'!$D$32*D1031*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*D1030+0.4357405005*D1030+0.0330936548*D1031+0.0328406739))+D1038*('Segments'!$D$33*D1031*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*D1030+0.4357405005*D1030+0.0330936548*D1031+0.0328406739))+D1039*('Segments'!$D$34*D1031*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*D1030+0.4357405005*D1030+0.0330936548*D1031+0.0328406739))</f>
+        <f>D1032*('Segments'!$D$27*D1031*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*D1031+0.4357405005*D1031+0.0330936548*D1031+0.0328406739))+D1033*('Segments'!$D$28*D1031*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*D1031+0.4357405005*D1031+0.0330936548*D1031+0.0328406739))+D1034*('Segments'!$D$29*D1031*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*D1031+0.4357405005*D1031+0.0330936548*D1031+0.0328406739))+D1035*('Segments'!$D$30*D1031*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*D1031+0.4357405005*D1031+0.0330936548*D1031+0.0328406739))+D1036*('Segments'!$D$31*D1031*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*D1031+0.4357405005*D1031+0.0330936548*D1031+0.0328406739))+D1037*('Segments'!$D$32*D1031*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*D1031+0.4357405005*D1031+0.0330936548*D1031+0.0328406739))+D1038*('Segments'!$D$33*D1031*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*D1031+0.4357405005*D1031+0.0330936548*D1031+0.0328406739))+D1039*('Segments'!$D$34*D1031*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*D1031+0.4357405005*D1031+0.0330936548*D1031+0.0328406739))</f>
         <v/>
       </c>
       <c r="E1042" s="18">
-        <f>E1032*('Segments'!$D$27*E1031*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*E1030+0.4357405005*E1030+0.0330936548*E1031+0.0328406739))+E1033*('Segments'!$D$28*E1031*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*E1030+0.4357405005*E1030+0.0330936548*E1031+0.0328406739))+E1034*('Segments'!$D$29*E1031*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*E1030+0.4357405005*E1030+0.0330936548*E1031+0.0328406739))+E1035*('Segments'!$D$30*E1031*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*E1030+0.4357405005*E1030+0.0330936548*E1031+0.0328406739))+E1036*('Segments'!$D$31*E1031*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*E1030+0.4357405005*E1030+0.0330936548*E1031+0.0328406739))+E1037*('Segments'!$D$32*E1031*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*E1030+0.4357405005*E1030+0.0330936548*E1031+0.0328406739))+E1038*('Segments'!$D$33*E1031*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*E1030+0.4357405005*E1030+0.0330936548*E1031+0.0328406739))+E1039*('Segments'!$D$34*E1031*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*E1030+0.4357405005*E1030+0.0330936548*E1031+0.0328406739))</f>
+        <f>E1032*('Segments'!$D$27*E1031*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*E1031+0.4357405005*E1031+0.0330936548*E1031+0.0328406739))+E1033*('Segments'!$D$28*E1031*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*E1031+0.4357405005*E1031+0.0330936548*E1031+0.0328406739))+E1034*('Segments'!$D$29*E1031*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*E1031+0.4357405005*E1031+0.0330936548*E1031+0.0328406739))+E1035*('Segments'!$D$30*E1031*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*E1031+0.4357405005*E1031+0.0330936548*E1031+0.0328406739))+E1036*('Segments'!$D$31*E1031*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*E1031+0.4357405005*E1031+0.0330936548*E1031+0.0328406739))+E1037*('Segments'!$D$32*E1031*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*E1031+0.4357405005*E1031+0.0330936548*E1031+0.0328406739))+E1038*('Segments'!$D$33*E1031*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*E1031+0.4357405005*E1031+0.0330936548*E1031+0.0328406739))+E1039*('Segments'!$D$34*E1031*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*E1031+0.4357405005*E1031+0.0330936548*E1031+0.0328406739))</f>
         <v/>
       </c>
       <c r="F1042" s="18">
-        <f>F1032*('Segments'!$D$27*F1031*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*F1030+0.4357405005*F1030+0.0330936548*F1031+0.0328406739))+F1033*('Segments'!$D$28*F1031*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*F1030+0.4357405005*F1030+0.0330936548*F1031+0.0328406739))+F1034*('Segments'!$D$29*F1031*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*F1030+0.4357405005*F1030+0.0330936548*F1031+0.0328406739))+F1035*('Segments'!$D$30*F1031*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*F1030+0.4357405005*F1030+0.0330936548*F1031+0.0328406739))+F1036*('Segments'!$D$31*F1031*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*F1030+0.4357405005*F1030+0.0330936548*F1031+0.0328406739))+F1037*('Segments'!$D$32*F1031*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*F1030+0.4357405005*F1030+0.0330936548*F1031+0.0328406739))+F1038*('Segments'!$D$33*F1031*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*F1030+0.4357405005*F1030+0.0330936548*F1031+0.0328406739))+F1039*('Segments'!$D$34*F1031*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*F1030+0.4357405005*F1030+0.0330936548*F1031+0.0328406739))</f>
+        <f>F1032*('Segments'!$D$27*F1031*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*F1031+0.4357405005*F1031+0.0330936548*F1031+0.0328406739))+F1033*('Segments'!$D$28*F1031*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*F1031+0.4357405005*F1031+0.0330936548*F1031+0.0328406739))+F1034*('Segments'!$D$29*F1031*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*F1031+0.4357405005*F1031+0.0330936548*F1031+0.0328406739))+F1035*('Segments'!$D$30*F1031*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*F1031+0.4357405005*F1031+0.0330936548*F1031+0.0328406739))+F1036*('Segments'!$D$31*F1031*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*F1031+0.4357405005*F1031+0.0330936548*F1031+0.0328406739))+F1037*('Segments'!$D$32*F1031*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*F1031+0.4357405005*F1031+0.0330936548*F1031+0.0328406739))+F1038*('Segments'!$D$33*F1031*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*F1031+0.4357405005*F1031+0.0330936548*F1031+0.0328406739))+F1039*('Segments'!$D$34*F1031*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*F1031+0.4357405005*F1031+0.0330936548*F1031+0.0328406739))</f>
         <v/>
       </c>
       <c r="G1042" s="18">
-        <f>G1032*('Segments'!$D$27*G1031*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*G1030+0.4357405005*G1030+0.0330936548*G1031+0.0328406739))+G1033*('Segments'!$D$28*G1031*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*G1030+0.4357405005*G1030+0.0330936548*G1031+0.0328406739))+G1034*('Segments'!$D$29*G1031*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*G1030+0.4357405005*G1030+0.0330936548*G1031+0.0328406739))+G1035*('Segments'!$D$30*G1031*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*G1030+0.4357405005*G1030+0.0330936548*G1031+0.0328406739))+G1036*('Segments'!$D$31*G1031*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*G1030+0.4357405005*G1030+0.0330936548*G1031+0.0328406739))+G1037*('Segments'!$D$32*G1031*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*G1030+0.4357405005*G1030+0.0330936548*G1031+0.0328406739))+G1038*('Segments'!$D$33*G1031*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*G1030+0.4357405005*G1030+0.0330936548*G1031+0.0328406739))+G1039*('Segments'!$D$34*G1031*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*G1030+0.4357405005*G1030+0.0330936548*G1031+0.0328406739))</f>
+        <f>G1032*('Segments'!$D$27*G1031*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*G1031+0.4357405005*G1031+0.0330936548*G1031+0.0328406739))+G1033*('Segments'!$D$28*G1031*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*G1031+0.4357405005*G1031+0.0330936548*G1031+0.0328406739))+G1034*('Segments'!$D$29*G1031*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*G1031+0.4357405005*G1031+0.0330936548*G1031+0.0328406739))+G1035*('Segments'!$D$30*G1031*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*G1031+0.4357405005*G1031+0.0330936548*G1031+0.0328406739))+G1036*('Segments'!$D$31*G1031*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*G1031+0.4357405005*G1031+0.0330936548*G1031+0.0328406739))+G1037*('Segments'!$D$32*G1031*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*G1031+0.4357405005*G1031+0.0330936548*G1031+0.0328406739))+G1038*('Segments'!$D$33*G1031*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*G1031+0.4357405005*G1031+0.0330936548*G1031+0.0328406739))+G1039*('Segments'!$D$34*G1031*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*G1031+0.4357405005*G1031+0.0330936548*G1031+0.0328406739))</f>
         <v/>
       </c>
     </row>
@@ -25856,23 +25856,23 @@
         </is>
       </c>
       <c r="C1091" s="18">
-        <f>C1081*('Segments'!$D$27*C1080*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*C1079+0.4357405005*C1079+0.0330936548*C1080+0.0328406739))+C1082*('Segments'!$D$28*C1080*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*C1079+0.4357405005*C1079+0.0330936548*C1080+0.0328406739))+C1083*('Segments'!$D$29*C1080*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*C1079+0.4357405005*C1079+0.0330936548*C1080+0.0328406739))+C1084*('Segments'!$D$30*C1080*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*C1079+0.4357405005*C1079+0.0330936548*C1080+0.0328406739))+C1085*('Segments'!$D$31*C1080*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*C1079+0.4357405005*C1079+0.0330936548*C1080+0.0328406739))+C1086*('Segments'!$D$32*C1080*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*C1079+0.4357405005*C1079+0.0330936548*C1080+0.0328406739))+C1087*('Segments'!$D$33*C1080*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*C1079+0.4357405005*C1079+0.0330936548*C1080+0.0328406739))+C1088*('Segments'!$D$34*C1080*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*C1079+0.4357405005*C1079+0.0330936548*C1080+0.0328406739))</f>
+        <f>C1081*('Segments'!$D$27*C1080*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*C1080+0.4357405005*C1080+0.0330936548*C1080+0.0328406739))+C1082*('Segments'!$D$28*C1080*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*C1080+0.4357405005*C1080+0.0330936548*C1080+0.0328406739))+C1083*('Segments'!$D$29*C1080*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*C1080+0.4357405005*C1080+0.0330936548*C1080+0.0328406739))+C1084*('Segments'!$D$30*C1080*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*C1080+0.4357405005*C1080+0.0330936548*C1080+0.0328406739))+C1085*('Segments'!$D$31*C1080*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*C1080+0.4357405005*C1080+0.0330936548*C1080+0.0328406739))+C1086*('Segments'!$D$32*C1080*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*C1080+0.4357405005*C1080+0.0330936548*C1080+0.0328406739))+C1087*('Segments'!$D$33*C1080*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*C1080+0.4357405005*C1080+0.0330936548*C1080+0.0328406739))+C1088*('Segments'!$D$34*C1080*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*C1080+0.4357405005*C1080+0.0330936548*C1080+0.0328406739))</f>
         <v/>
       </c>
       <c r="D1091" s="18">
-        <f>D1081*('Segments'!$D$27*D1080*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*D1079+0.4357405005*D1079+0.0330936548*D1080+0.0328406739))+D1082*('Segments'!$D$28*D1080*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*D1079+0.4357405005*D1079+0.0330936548*D1080+0.0328406739))+D1083*('Segments'!$D$29*D1080*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*D1079+0.4357405005*D1079+0.0330936548*D1080+0.0328406739))+D1084*('Segments'!$D$30*D1080*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*D1079+0.4357405005*D1079+0.0330936548*D1080+0.0328406739))+D1085*('Segments'!$D$31*D1080*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*D1079+0.4357405005*D1079+0.0330936548*D1080+0.0328406739))+D1086*('Segments'!$D$32*D1080*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*D1079+0.4357405005*D1079+0.0330936548*D1080+0.0328406739))+D1087*('Segments'!$D$33*D1080*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*D1079+0.4357405005*D1079+0.0330936548*D1080+0.0328406739))+D1088*('Segments'!$D$34*D1080*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*D1079+0.4357405005*D1079+0.0330936548*D1080+0.0328406739))</f>
+        <f>D1081*('Segments'!$D$27*D1080*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*D1080+0.4357405005*D1080+0.0330936548*D1080+0.0328406739))+D1082*('Segments'!$D$28*D1080*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*D1080+0.4357405005*D1080+0.0330936548*D1080+0.0328406739))+D1083*('Segments'!$D$29*D1080*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*D1080+0.4357405005*D1080+0.0330936548*D1080+0.0328406739))+D1084*('Segments'!$D$30*D1080*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*D1080+0.4357405005*D1080+0.0330936548*D1080+0.0328406739))+D1085*('Segments'!$D$31*D1080*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*D1080+0.4357405005*D1080+0.0330936548*D1080+0.0328406739))+D1086*('Segments'!$D$32*D1080*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*D1080+0.4357405005*D1080+0.0330936548*D1080+0.0328406739))+D1087*('Segments'!$D$33*D1080*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*D1080+0.4357405005*D1080+0.0330936548*D1080+0.0328406739))+D1088*('Segments'!$D$34*D1080*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*D1080+0.4357405005*D1080+0.0330936548*D1080+0.0328406739))</f>
         <v/>
       </c>
       <c r="E1091" s="18">
-        <f>E1081*('Segments'!$D$27*E1080*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*E1079+0.4357405005*E1079+0.0330936548*E1080+0.0328406739))+E1082*('Segments'!$D$28*E1080*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*E1079+0.4357405005*E1079+0.0330936548*E1080+0.0328406739))+E1083*('Segments'!$D$29*E1080*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*E1079+0.4357405005*E1079+0.0330936548*E1080+0.0328406739))+E1084*('Segments'!$D$30*E1080*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*E1079+0.4357405005*E1079+0.0330936548*E1080+0.0328406739))+E1085*('Segments'!$D$31*E1080*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*E1079+0.4357405005*E1079+0.0330936548*E1080+0.0328406739))+E1086*('Segments'!$D$32*E1080*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*E1079+0.4357405005*E1079+0.0330936548*E1080+0.0328406739))+E1087*('Segments'!$D$33*E1080*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*E1079+0.4357405005*E1079+0.0330936548*E1080+0.0328406739))+E1088*('Segments'!$D$34*E1080*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*E1079+0.4357405005*E1079+0.0330936548*E1080+0.0328406739))</f>
+        <f>E1081*('Segments'!$D$27*E1080*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*E1080+0.4357405005*E1080+0.0330936548*E1080+0.0328406739))+E1082*('Segments'!$D$28*E1080*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*E1080+0.4357405005*E1080+0.0330936548*E1080+0.0328406739))+E1083*('Segments'!$D$29*E1080*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*E1080+0.4357405005*E1080+0.0330936548*E1080+0.0328406739))+E1084*('Segments'!$D$30*E1080*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*E1080+0.4357405005*E1080+0.0330936548*E1080+0.0328406739))+E1085*('Segments'!$D$31*E1080*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*E1080+0.4357405005*E1080+0.0330936548*E1080+0.0328406739))+E1086*('Segments'!$D$32*E1080*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*E1080+0.4357405005*E1080+0.0330936548*E1080+0.0328406739))+E1087*('Segments'!$D$33*E1080*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*E1080+0.4357405005*E1080+0.0330936548*E1080+0.0328406739))+E1088*('Segments'!$D$34*E1080*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*E1080+0.4357405005*E1080+0.0330936548*E1080+0.0328406739))</f>
         <v/>
       </c>
       <c r="F1091" s="18">
-        <f>F1081*('Segments'!$D$27*F1080*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*F1079+0.4357405005*F1079+0.0330936548*F1080+0.0328406739))+F1082*('Segments'!$D$28*F1080*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*F1079+0.4357405005*F1079+0.0330936548*F1080+0.0328406739))+F1083*('Segments'!$D$29*F1080*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*F1079+0.4357405005*F1079+0.0330936548*F1080+0.0328406739))+F1084*('Segments'!$D$30*F1080*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*F1079+0.4357405005*F1079+0.0330936548*F1080+0.0328406739))+F1085*('Segments'!$D$31*F1080*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*F1079+0.4357405005*F1079+0.0330936548*F1080+0.0328406739))+F1086*('Segments'!$D$32*F1080*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*F1079+0.4357405005*F1079+0.0330936548*F1080+0.0328406739))+F1087*('Segments'!$D$33*F1080*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*F1079+0.4357405005*F1079+0.0330936548*F1080+0.0328406739))+F1088*('Segments'!$D$34*F1080*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*F1079+0.4357405005*F1079+0.0330936548*F1080+0.0328406739))</f>
+        <f>F1081*('Segments'!$D$27*F1080*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*F1080+0.4357405005*F1080+0.0330936548*F1080+0.0328406739))+F1082*('Segments'!$D$28*F1080*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*F1080+0.4357405005*F1080+0.0330936548*F1080+0.0328406739))+F1083*('Segments'!$D$29*F1080*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*F1080+0.4357405005*F1080+0.0330936548*F1080+0.0328406739))+F1084*('Segments'!$D$30*F1080*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*F1080+0.4357405005*F1080+0.0330936548*F1080+0.0328406739))+F1085*('Segments'!$D$31*F1080*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*F1080+0.4357405005*F1080+0.0330936548*F1080+0.0328406739))+F1086*('Segments'!$D$32*F1080*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*F1080+0.4357405005*F1080+0.0330936548*F1080+0.0328406739))+F1087*('Segments'!$D$33*F1080*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*F1080+0.4357405005*F1080+0.0330936548*F1080+0.0328406739))+F1088*('Segments'!$D$34*F1080*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*F1080+0.4357405005*F1080+0.0330936548*F1080+0.0328406739))</f>
         <v/>
       </c>
       <c r="G1091" s="18">
-        <f>G1081*('Segments'!$D$27*G1080*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*G1079+0.4357405005*G1079+0.0330936548*G1080+0.0328406739))+G1082*('Segments'!$D$28*G1080*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*G1079+0.4357405005*G1079+0.0330936548*G1080+0.0328406739))+G1083*('Segments'!$D$29*G1080*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*G1079+0.4357405005*G1079+0.0330936548*G1080+0.0328406739))+G1084*('Segments'!$D$30*G1080*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*G1079+0.4357405005*G1079+0.0330936548*G1080+0.0328406739))+G1085*('Segments'!$D$31*G1080*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*G1079+0.4357405005*G1079+0.0330936548*G1080+0.0328406739))+G1086*('Segments'!$D$32*G1080*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*G1079+0.4357405005*G1079+0.0330936548*G1080+0.0328406739))+G1087*('Segments'!$D$33*G1080*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*G1079+0.4357405005*G1079+0.0330936548*G1080+0.0328406739))+G1088*('Segments'!$D$34*G1080*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*G1079+0.4357405005*G1079+0.0330936548*G1080+0.0328406739))</f>
+        <f>G1081*('Segments'!$D$27*G1080*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*G1080+0.4357405005*G1080+0.0330936548*G1080+0.0328406739))+G1082*('Segments'!$D$28*G1080*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*G1080+0.4357405005*G1080+0.0330936548*G1080+0.0328406739))+G1083*('Segments'!$D$29*G1080*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*G1080+0.4357405005*G1080+0.0330936548*G1080+0.0328406739))+G1084*('Segments'!$D$30*G1080*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*G1080+0.4357405005*G1080+0.0330936548*G1080+0.0328406739))+G1085*('Segments'!$D$31*G1080*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*G1080+0.4357405005*G1080+0.0330936548*G1080+0.0328406739))+G1086*('Segments'!$D$32*G1080*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*G1080+0.4357405005*G1080+0.0330936548*G1080+0.0328406739))+G1087*('Segments'!$D$33*G1080*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*G1080+0.4357405005*G1080+0.0330936548*G1080+0.0328406739))+G1088*('Segments'!$D$34*G1080*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*G1080+0.4357405005*G1080+0.0330936548*G1080+0.0328406739))</f>
         <v/>
       </c>
     </row>
@@ -26926,23 +26926,23 @@
         </is>
       </c>
       <c r="C1140" s="18">
-        <f>C1130*('Segments'!$D$27*C1129*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*C1128+0.4357405005*C1128+0.0330936548*C1129+0.0328406739))+C1131*('Segments'!$D$28*C1129*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*C1128+0.4357405005*C1128+0.0330936548*C1129+0.0328406739))+C1132*('Segments'!$D$29*C1129*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*C1128+0.4357405005*C1128+0.0330936548*C1129+0.0328406739))+C1133*('Segments'!$D$30*C1129*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*C1128+0.4357405005*C1128+0.0330936548*C1129+0.0328406739))+C1134*('Segments'!$D$31*C1129*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*C1128+0.4357405005*C1128+0.0330936548*C1129+0.0328406739))+C1135*('Segments'!$D$32*C1129*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*C1128+0.4357405005*C1128+0.0330936548*C1129+0.0328406739))+C1136*('Segments'!$D$33*C1129*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*C1128+0.4357405005*C1128+0.0330936548*C1129+0.0328406739))+C1137*('Segments'!$D$34*C1129*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*C1128+0.4357405005*C1128+0.0330936548*C1129+0.0328406739))</f>
+        <f>C1130*('Segments'!$D$27*C1129*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*C1129+0.4357405005*C1129+0.0330936548*C1129+0.0328406739))+C1131*('Segments'!$D$28*C1129*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*C1129+0.4357405005*C1129+0.0330936548*C1129+0.0328406739))+C1132*('Segments'!$D$29*C1129*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*C1129+0.4357405005*C1129+0.0330936548*C1129+0.0328406739))+C1133*('Segments'!$D$30*C1129*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*C1129+0.4357405005*C1129+0.0330936548*C1129+0.0328406739))+C1134*('Segments'!$D$31*C1129*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*C1129+0.4357405005*C1129+0.0330936548*C1129+0.0328406739))+C1135*('Segments'!$D$32*C1129*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*C1129+0.4357405005*C1129+0.0330936548*C1129+0.0328406739))+C1136*('Segments'!$D$33*C1129*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*C1129+0.4357405005*C1129+0.0330936548*C1129+0.0328406739))+C1137*('Segments'!$D$34*C1129*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*C1129+0.4357405005*C1129+0.0330936548*C1129+0.0328406739))</f>
         <v/>
       </c>
       <c r="D1140" s="18">
-        <f>D1130*('Segments'!$D$27*D1129*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*D1128+0.4357405005*D1128+0.0330936548*D1129+0.0328406739))+D1131*('Segments'!$D$28*D1129*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*D1128+0.4357405005*D1128+0.0330936548*D1129+0.0328406739))+D1132*('Segments'!$D$29*D1129*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*D1128+0.4357405005*D1128+0.0330936548*D1129+0.0328406739))+D1133*('Segments'!$D$30*D1129*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*D1128+0.4357405005*D1128+0.0330936548*D1129+0.0328406739))+D1134*('Segments'!$D$31*D1129*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*D1128+0.4357405005*D1128+0.0330936548*D1129+0.0328406739))+D1135*('Segments'!$D$32*D1129*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*D1128+0.4357405005*D1128+0.0330936548*D1129+0.0328406739))+D1136*('Segments'!$D$33*D1129*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*D1128+0.4357405005*D1128+0.0330936548*D1129+0.0328406739))+D1137*('Segments'!$D$34*D1129*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*D1128+0.4357405005*D1128+0.0330936548*D1129+0.0328406739))</f>
+        <f>D1130*('Segments'!$D$27*D1129*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*D1129+0.4357405005*D1129+0.0330936548*D1129+0.0328406739))+D1131*('Segments'!$D$28*D1129*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*D1129+0.4357405005*D1129+0.0330936548*D1129+0.0328406739))+D1132*('Segments'!$D$29*D1129*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*D1129+0.4357405005*D1129+0.0330936548*D1129+0.0328406739))+D1133*('Segments'!$D$30*D1129*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*D1129+0.4357405005*D1129+0.0330936548*D1129+0.0328406739))+D1134*('Segments'!$D$31*D1129*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*D1129+0.4357405005*D1129+0.0330936548*D1129+0.0328406739))+D1135*('Segments'!$D$32*D1129*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*D1129+0.4357405005*D1129+0.0330936548*D1129+0.0328406739))+D1136*('Segments'!$D$33*D1129*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*D1129+0.4357405005*D1129+0.0330936548*D1129+0.0328406739))+D1137*('Segments'!$D$34*D1129*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*D1129+0.4357405005*D1129+0.0330936548*D1129+0.0328406739))</f>
         <v/>
       </c>
       <c r="E1140" s="18">
-        <f>E1130*('Segments'!$D$27*E1129*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*E1128+0.4357405005*E1128+0.0330936548*E1129+0.0328406739))+E1131*('Segments'!$D$28*E1129*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*E1128+0.4357405005*E1128+0.0330936548*E1129+0.0328406739))+E1132*('Segments'!$D$29*E1129*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*E1128+0.4357405005*E1128+0.0330936548*E1129+0.0328406739))+E1133*('Segments'!$D$30*E1129*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*E1128+0.4357405005*E1128+0.0330936548*E1129+0.0328406739))+E1134*('Segments'!$D$31*E1129*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*E1128+0.4357405005*E1128+0.0330936548*E1129+0.0328406739))+E1135*('Segments'!$D$32*E1129*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*E1128+0.4357405005*E1128+0.0330936548*E1129+0.0328406739))+E1136*('Segments'!$D$33*E1129*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*E1128+0.4357405005*E1128+0.0330936548*E1129+0.0328406739))+E1137*('Segments'!$D$34*E1129*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*E1128+0.4357405005*E1128+0.0330936548*E1129+0.0328406739))</f>
+        <f>E1130*('Segments'!$D$27*E1129*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*E1129+0.4357405005*E1129+0.0330936548*E1129+0.0328406739))+E1131*('Segments'!$D$28*E1129*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*E1129+0.4357405005*E1129+0.0330936548*E1129+0.0328406739))+E1132*('Segments'!$D$29*E1129*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*E1129+0.4357405005*E1129+0.0330936548*E1129+0.0328406739))+E1133*('Segments'!$D$30*E1129*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*E1129+0.4357405005*E1129+0.0330936548*E1129+0.0328406739))+E1134*('Segments'!$D$31*E1129*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*E1129+0.4357405005*E1129+0.0330936548*E1129+0.0328406739))+E1135*('Segments'!$D$32*E1129*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*E1129+0.4357405005*E1129+0.0330936548*E1129+0.0328406739))+E1136*('Segments'!$D$33*E1129*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*E1129+0.4357405005*E1129+0.0330936548*E1129+0.0328406739))+E1137*('Segments'!$D$34*E1129*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*E1129+0.4357405005*E1129+0.0330936548*E1129+0.0328406739))</f>
         <v/>
       </c>
       <c r="F1140" s="18">
-        <f>F1130*('Segments'!$D$27*F1129*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*F1128+0.4357405005*F1128+0.0330936548*F1129+0.0328406739))+F1131*('Segments'!$D$28*F1129*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*F1128+0.4357405005*F1128+0.0330936548*F1129+0.0328406739))+F1132*('Segments'!$D$29*F1129*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*F1128+0.4357405005*F1128+0.0330936548*F1129+0.0328406739))+F1133*('Segments'!$D$30*F1129*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*F1128+0.4357405005*F1128+0.0330936548*F1129+0.0328406739))+F1134*('Segments'!$D$31*F1129*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*F1128+0.4357405005*F1128+0.0330936548*F1129+0.0328406739))+F1135*('Segments'!$D$32*F1129*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*F1128+0.4357405005*F1128+0.0330936548*F1129+0.0328406739))+F1136*('Segments'!$D$33*F1129*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*F1128+0.4357405005*F1128+0.0330936548*F1129+0.0328406739))+F1137*('Segments'!$D$34*F1129*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*F1128+0.4357405005*F1128+0.0330936548*F1129+0.0328406739))</f>
+        <f>F1130*('Segments'!$D$27*F1129*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*F1129+0.4357405005*F1129+0.0330936548*F1129+0.0328406739))+F1131*('Segments'!$D$28*F1129*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*F1129+0.4357405005*F1129+0.0330936548*F1129+0.0328406739))+F1132*('Segments'!$D$29*F1129*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*F1129+0.4357405005*F1129+0.0330936548*F1129+0.0328406739))+F1133*('Segments'!$D$30*F1129*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*F1129+0.4357405005*F1129+0.0330936548*F1129+0.0328406739))+F1134*('Segments'!$D$31*F1129*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*F1129+0.4357405005*F1129+0.0330936548*F1129+0.0328406739))+F1135*('Segments'!$D$32*F1129*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*F1129+0.4357405005*F1129+0.0330936548*F1129+0.0328406739))+F1136*('Segments'!$D$33*F1129*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*F1129+0.4357405005*F1129+0.0330936548*F1129+0.0328406739))+F1137*('Segments'!$D$34*F1129*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*F1129+0.4357405005*F1129+0.0330936548*F1129+0.0328406739))</f>
         <v/>
       </c>
       <c r="G1140" s="18">
-        <f>G1130*('Segments'!$D$27*G1129*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*G1128+0.4357405005*G1128+0.0330936548*G1129+0.0328406739))+G1131*('Segments'!$D$28*G1129*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*G1128+0.4357405005*G1128+0.0330936548*G1129+0.0328406739))+G1132*('Segments'!$D$29*G1129*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*G1128+0.4357405005*G1128+0.0330936548*G1129+0.0328406739))+G1133*('Segments'!$D$30*G1129*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*G1128+0.4357405005*G1128+0.0330936548*G1129+0.0328406739))+G1134*('Segments'!$D$31*G1129*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*G1128+0.4357405005*G1128+0.0330936548*G1129+0.0328406739))+G1135*('Segments'!$D$32*G1129*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*G1128+0.4357405005*G1128+0.0330936548*G1129+0.0328406739))+G1136*('Segments'!$D$33*G1129*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*G1128+0.4357405005*G1128+0.0330936548*G1129+0.0328406739))+G1137*('Segments'!$D$34*G1129*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*G1128+0.4357405005*G1128+0.0330936548*G1129+0.0328406739))</f>
+        <f>G1130*('Segments'!$D$27*G1129*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*G1129+0.4357405005*G1129+0.0330936548*G1129+0.0328406739))+G1131*('Segments'!$D$28*G1129*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*G1129+0.4357405005*G1129+0.0330936548*G1129+0.0328406739))+G1132*('Segments'!$D$29*G1129*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*G1129+0.4357405005*G1129+0.0330936548*G1129+0.0328406739))+G1133*('Segments'!$D$30*G1129*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*G1129+0.4357405005*G1129+0.0330936548*G1129+0.0328406739))+G1134*('Segments'!$D$31*G1129*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*G1129+0.4357405005*G1129+0.0330936548*G1129+0.0328406739))+G1135*('Segments'!$D$32*G1129*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*G1129+0.4357405005*G1129+0.0330936548*G1129+0.0328406739))+G1136*('Segments'!$D$33*G1129*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*G1129+0.4357405005*G1129+0.0330936548*G1129+0.0328406739))+G1137*('Segments'!$D$34*G1129*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*G1129+0.4357405005*G1129+0.0330936548*G1129+0.0328406739))</f>
         <v/>
       </c>
     </row>
@@ -27996,23 +27996,23 @@
         </is>
       </c>
       <c r="C1189" s="18">
-        <f>C1179*('Segments'!$D$27*C1178*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*C1177+0.4357405005*C1177+0.0330936548*C1178+0.0328406739))+C1180*('Segments'!$D$28*C1178*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*C1177+0.4357405005*C1177+0.0330936548*C1178+0.0328406739))+C1181*('Segments'!$D$29*C1178*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*C1177+0.4357405005*C1177+0.0330936548*C1178+0.0328406739))+C1182*('Segments'!$D$30*C1178*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*C1177+0.4357405005*C1177+0.0330936548*C1178+0.0328406739))+C1183*('Segments'!$D$31*C1178*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*C1177+0.4357405005*C1177+0.0330936548*C1178+0.0328406739))+C1184*('Segments'!$D$32*C1178*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*C1177+0.4357405005*C1177+0.0330936548*C1178+0.0328406739))+C1185*('Segments'!$D$33*C1178*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*C1177+0.4357405005*C1177+0.0330936548*C1178+0.0328406739))+C1186*('Segments'!$D$34*C1178*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*C1177+0.4357405005*C1177+0.0330936548*C1178+0.0328406739))</f>
+        <f>C1179*('Segments'!$D$27*C1178*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*C1178+0.4357405005*C1178+0.0330936548*C1178+0.0328406739))+C1180*('Segments'!$D$28*C1178*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*C1178+0.4357405005*C1178+0.0330936548*C1178+0.0328406739))+C1181*('Segments'!$D$29*C1178*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*C1178+0.4357405005*C1178+0.0330936548*C1178+0.0328406739))+C1182*('Segments'!$D$30*C1178*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*C1178+0.4357405005*C1178+0.0330936548*C1178+0.0328406739))+C1183*('Segments'!$D$31*C1178*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*C1178+0.4357405005*C1178+0.0330936548*C1178+0.0328406739))+C1184*('Segments'!$D$32*C1178*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*C1178+0.4357405005*C1178+0.0330936548*C1178+0.0328406739))+C1185*('Segments'!$D$33*C1178*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*C1178+0.4357405005*C1178+0.0330936548*C1178+0.0328406739))+C1186*('Segments'!$D$34*C1178*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*C1178+0.4357405005*C1178+0.0330936548*C1178+0.0328406739))</f>
         <v/>
       </c>
       <c r="D1189" s="18">
-        <f>D1179*('Segments'!$D$27*D1178*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*D1177+0.4357405005*D1177+0.0330936548*D1178+0.0328406739))+D1180*('Segments'!$D$28*D1178*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*D1177+0.4357405005*D1177+0.0330936548*D1178+0.0328406739))+D1181*('Segments'!$D$29*D1178*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*D1177+0.4357405005*D1177+0.0330936548*D1178+0.0328406739))+D1182*('Segments'!$D$30*D1178*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*D1177+0.4357405005*D1177+0.0330936548*D1178+0.0328406739))+D1183*('Segments'!$D$31*D1178*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*D1177+0.4357405005*D1177+0.0330936548*D1178+0.0328406739))+D1184*('Segments'!$D$32*D1178*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*D1177+0.4357405005*D1177+0.0330936548*D1178+0.0328406739))+D1185*('Segments'!$D$33*D1178*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*D1177+0.4357405005*D1177+0.0330936548*D1178+0.0328406739))+D1186*('Segments'!$D$34*D1178*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*D1177+0.4357405005*D1177+0.0330936548*D1178+0.0328406739))</f>
+        <f>D1179*('Segments'!$D$27*D1178*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*D1178+0.4357405005*D1178+0.0330936548*D1178+0.0328406739))+D1180*('Segments'!$D$28*D1178*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*D1178+0.4357405005*D1178+0.0330936548*D1178+0.0328406739))+D1181*('Segments'!$D$29*D1178*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*D1178+0.4357405005*D1178+0.0330936548*D1178+0.0328406739))+D1182*('Segments'!$D$30*D1178*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*D1178+0.4357405005*D1178+0.0330936548*D1178+0.0328406739))+D1183*('Segments'!$D$31*D1178*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*D1178+0.4357405005*D1178+0.0330936548*D1178+0.0328406739))+D1184*('Segments'!$D$32*D1178*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*D1178+0.4357405005*D1178+0.0330936548*D1178+0.0328406739))+D1185*('Segments'!$D$33*D1178*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*D1178+0.4357405005*D1178+0.0330936548*D1178+0.0328406739))+D1186*('Segments'!$D$34*D1178*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*D1178+0.4357405005*D1178+0.0330936548*D1178+0.0328406739))</f>
         <v/>
       </c>
       <c r="E1189" s="18">
-        <f>E1179*('Segments'!$D$27*E1178*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*E1177+0.4357405005*E1177+0.0330936548*E1178+0.0328406739))+E1180*('Segments'!$D$28*E1178*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*E1177+0.4357405005*E1177+0.0330936548*E1178+0.0328406739))+E1181*('Segments'!$D$29*E1178*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*E1177+0.4357405005*E1177+0.0330936548*E1178+0.0328406739))+E1182*('Segments'!$D$30*E1178*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*E1177+0.4357405005*E1177+0.0330936548*E1178+0.0328406739))+E1183*('Segments'!$D$31*E1178*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*E1177+0.4357405005*E1177+0.0330936548*E1178+0.0328406739))+E1184*('Segments'!$D$32*E1178*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*E1177+0.4357405005*E1177+0.0330936548*E1178+0.0328406739))+E1185*('Segments'!$D$33*E1178*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*E1177+0.4357405005*E1177+0.0330936548*E1178+0.0328406739))+E1186*('Segments'!$D$34*E1178*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*E1177+0.4357405005*E1177+0.0330936548*E1178+0.0328406739))</f>
+        <f>E1179*('Segments'!$D$27*E1178*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*E1178+0.4357405005*E1178+0.0330936548*E1178+0.0328406739))+E1180*('Segments'!$D$28*E1178*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*E1178+0.4357405005*E1178+0.0330936548*E1178+0.0328406739))+E1181*('Segments'!$D$29*E1178*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*E1178+0.4357405005*E1178+0.0330936548*E1178+0.0328406739))+E1182*('Segments'!$D$30*E1178*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*E1178+0.4357405005*E1178+0.0330936548*E1178+0.0328406739))+E1183*('Segments'!$D$31*E1178*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*E1178+0.4357405005*E1178+0.0330936548*E1178+0.0328406739))+E1184*('Segments'!$D$32*E1178*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*E1178+0.4357405005*E1178+0.0330936548*E1178+0.0328406739))+E1185*('Segments'!$D$33*E1178*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*E1178+0.4357405005*E1178+0.0330936548*E1178+0.0328406739))+E1186*('Segments'!$D$34*E1178*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*E1178+0.4357405005*E1178+0.0330936548*E1178+0.0328406739))</f>
         <v/>
       </c>
       <c r="F1189" s="18">
-        <f>F1179*('Segments'!$D$27*F1178*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*F1177+0.4357405005*F1177+0.0330936548*F1178+0.0328406739))+F1180*('Segments'!$D$28*F1178*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*F1177+0.4357405005*F1177+0.0330936548*F1178+0.0328406739))+F1181*('Segments'!$D$29*F1178*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*F1177+0.4357405005*F1177+0.0330936548*F1178+0.0328406739))+F1182*('Segments'!$D$30*F1178*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*F1177+0.4357405005*F1177+0.0330936548*F1178+0.0328406739))+F1183*('Segments'!$D$31*F1178*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*F1177+0.4357405005*F1177+0.0330936548*F1178+0.0328406739))+F1184*('Segments'!$D$32*F1178*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*F1177+0.4357405005*F1177+0.0330936548*F1178+0.0328406739))+F1185*('Segments'!$D$33*F1178*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*F1177+0.4357405005*F1177+0.0330936548*F1178+0.0328406739))+F1186*('Segments'!$D$34*F1178*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*F1177+0.4357405005*F1177+0.0330936548*F1178+0.0328406739))</f>
+        <f>F1179*('Segments'!$D$27*F1178*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*F1178+0.4357405005*F1178+0.0330936548*F1178+0.0328406739))+F1180*('Segments'!$D$28*F1178*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*F1178+0.4357405005*F1178+0.0330936548*F1178+0.0328406739))+F1181*('Segments'!$D$29*F1178*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*F1178+0.4357405005*F1178+0.0330936548*F1178+0.0328406739))+F1182*('Segments'!$D$30*F1178*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*F1178+0.4357405005*F1178+0.0330936548*F1178+0.0328406739))+F1183*('Segments'!$D$31*F1178*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*F1178+0.4357405005*F1178+0.0330936548*F1178+0.0328406739))+F1184*('Segments'!$D$32*F1178*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*F1178+0.4357405005*F1178+0.0330936548*F1178+0.0328406739))+F1185*('Segments'!$D$33*F1178*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*F1178+0.4357405005*F1178+0.0330936548*F1178+0.0328406739))+F1186*('Segments'!$D$34*F1178*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*F1178+0.4357405005*F1178+0.0330936548*F1178+0.0328406739))</f>
         <v/>
       </c>
       <c r="G1189" s="18">
-        <f>G1179*('Segments'!$D$27*G1178*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*G1177+0.4357405005*G1177+0.0330936548*G1178+0.0328406739))+G1180*('Segments'!$D$28*G1178*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*G1177+0.4357405005*G1177+0.0330936548*G1178+0.0328406739))+G1181*('Segments'!$D$29*G1178*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*G1177+0.4357405005*G1177+0.0330936548*G1178+0.0328406739))+G1182*('Segments'!$D$30*G1178*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*G1177+0.4357405005*G1177+0.0330936548*G1178+0.0328406739))+G1183*('Segments'!$D$31*G1178*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*G1177+0.4357405005*G1177+0.0330936548*G1178+0.0328406739))+G1184*('Segments'!$D$32*G1178*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*G1177+0.4357405005*G1177+0.0330936548*G1178+0.0328406739))+G1185*('Segments'!$D$33*G1178*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*G1177+0.4357405005*G1177+0.0330936548*G1178+0.0328406739))+G1186*('Segments'!$D$34*G1178*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*G1177+0.4357405005*G1177+0.0330936548*G1178+0.0328406739))</f>
+        <f>G1179*('Segments'!$D$27*G1178*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*G1178+0.4357405005*G1178+0.0330936548*G1178+0.0328406739))+G1180*('Segments'!$D$28*G1178*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*G1178+0.4357405005*G1178+0.0330936548*G1178+0.0328406739))+G1181*('Segments'!$D$29*G1178*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*G1178+0.4357405005*G1178+0.0330936548*G1178+0.0328406739))+G1182*('Segments'!$D$30*G1178*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*G1178+0.4357405005*G1178+0.0330936548*G1178+0.0328406739))+G1183*('Segments'!$D$31*G1178*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*G1178+0.4357405005*G1178+0.0330936548*G1178+0.0328406739))+G1184*('Segments'!$D$32*G1178*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*G1178+0.4357405005*G1178+0.0330936548*G1178+0.0328406739))+G1185*('Segments'!$D$33*G1178*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*G1178+0.4357405005*G1178+0.0330936548*G1178+0.0328406739))+G1186*('Segments'!$D$34*G1178*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*G1178+0.4357405005*G1178+0.0330936548*G1178+0.0328406739))</f>
         <v/>
       </c>
     </row>
@@ -29066,23 +29066,23 @@
         </is>
       </c>
       <c r="C1238" s="18">
-        <f>C1228*('Segments'!$D$27*C1227*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*C1226+0.4357405005*C1226+0.0330936548*C1227+0.0328406739))+C1229*('Segments'!$D$28*C1227*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*C1226+0.4357405005*C1226+0.0330936548*C1227+0.0328406739))+C1230*('Segments'!$D$29*C1227*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*C1226+0.4357405005*C1226+0.0330936548*C1227+0.0328406739))+C1231*('Segments'!$D$30*C1227*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*C1226+0.4357405005*C1226+0.0330936548*C1227+0.0328406739))+C1232*('Segments'!$D$31*C1227*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*C1226+0.4357405005*C1226+0.0330936548*C1227+0.0328406739))+C1233*('Segments'!$D$32*C1227*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*C1226+0.4357405005*C1226+0.0330936548*C1227+0.0328406739))+C1234*('Segments'!$D$33*C1227*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*C1226+0.4357405005*C1226+0.0330936548*C1227+0.0328406739))+C1235*('Segments'!$D$34*C1227*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*C1226+0.4357405005*C1226+0.0330936548*C1227+0.0328406739))</f>
+        <f>C1228*('Segments'!$D$27*C1227*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*C1227+0.4357405005*C1227+0.0330936548*C1227+0.0328406739))+C1229*('Segments'!$D$28*C1227*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*C1227+0.4357405005*C1227+0.0330936548*C1227+0.0328406739))+C1230*('Segments'!$D$29*C1227*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*C1227+0.4357405005*C1227+0.0330936548*C1227+0.0328406739))+C1231*('Segments'!$D$30*C1227*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*C1227+0.4357405005*C1227+0.0330936548*C1227+0.0328406739))+C1232*('Segments'!$D$31*C1227*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*C1227+0.4357405005*C1227+0.0330936548*C1227+0.0328406739))+C1233*('Segments'!$D$32*C1227*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*C1227+0.4357405005*C1227+0.0330936548*C1227+0.0328406739))+C1234*('Segments'!$D$33*C1227*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*C1227+0.4357405005*C1227+0.0330936548*C1227+0.0328406739))+C1235*('Segments'!$D$34*C1227*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*C1227+0.4357405005*C1227+0.0330936548*C1227+0.0328406739))</f>
         <v/>
       </c>
       <c r="D1238" s="18">
-        <f>D1228*('Segments'!$D$27*D1227*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*D1226+0.4357405005*D1226+0.0330936548*D1227+0.0328406739))+D1229*('Segments'!$D$28*D1227*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*D1226+0.4357405005*D1226+0.0330936548*D1227+0.0328406739))+D1230*('Segments'!$D$29*D1227*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*D1226+0.4357405005*D1226+0.0330936548*D1227+0.0328406739))+D1231*('Segments'!$D$30*D1227*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*D1226+0.4357405005*D1226+0.0330936548*D1227+0.0328406739))+D1232*('Segments'!$D$31*D1227*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*D1226+0.4357405005*D1226+0.0330936548*D1227+0.0328406739))+D1233*('Segments'!$D$32*D1227*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*D1226+0.4357405005*D1226+0.0330936548*D1227+0.0328406739))+D1234*('Segments'!$D$33*D1227*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*D1226+0.4357405005*D1226+0.0330936548*D1227+0.0328406739))+D1235*('Segments'!$D$34*D1227*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*D1226+0.4357405005*D1226+0.0330936548*D1227+0.0328406739))</f>
+        <f>D1228*('Segments'!$D$27*D1227*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*D1227+0.4357405005*D1227+0.0330936548*D1227+0.0328406739))+D1229*('Segments'!$D$28*D1227*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*D1227+0.4357405005*D1227+0.0330936548*D1227+0.0328406739))+D1230*('Segments'!$D$29*D1227*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*D1227+0.4357405005*D1227+0.0330936548*D1227+0.0328406739))+D1231*('Segments'!$D$30*D1227*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*D1227+0.4357405005*D1227+0.0330936548*D1227+0.0328406739))+D1232*('Segments'!$D$31*D1227*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*D1227+0.4357405005*D1227+0.0330936548*D1227+0.0328406739))+D1233*('Segments'!$D$32*D1227*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*D1227+0.4357405005*D1227+0.0330936548*D1227+0.0328406739))+D1234*('Segments'!$D$33*D1227*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*D1227+0.4357405005*D1227+0.0330936548*D1227+0.0328406739))+D1235*('Segments'!$D$34*D1227*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*D1227+0.4357405005*D1227+0.0330936548*D1227+0.0328406739))</f>
         <v/>
       </c>
       <c r="E1238" s="18">
-        <f>E1228*('Segments'!$D$27*E1227*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*E1226+0.4357405005*E1226+0.0330936548*E1227+0.0328406739))+E1229*('Segments'!$D$28*E1227*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*E1226+0.4357405005*E1226+0.0330936548*E1227+0.0328406739))+E1230*('Segments'!$D$29*E1227*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*E1226+0.4357405005*E1226+0.0330936548*E1227+0.0328406739))+E1231*('Segments'!$D$30*E1227*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*E1226+0.4357405005*E1226+0.0330936548*E1227+0.0328406739))+E1232*('Segments'!$D$31*E1227*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*E1226+0.4357405005*E1226+0.0330936548*E1227+0.0328406739))+E1233*('Segments'!$D$32*E1227*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*E1226+0.4357405005*E1226+0.0330936548*E1227+0.0328406739))+E1234*('Segments'!$D$33*E1227*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*E1226+0.4357405005*E1226+0.0330936548*E1227+0.0328406739))+E1235*('Segments'!$D$34*E1227*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*E1226+0.4357405005*E1226+0.0330936548*E1227+0.0328406739))</f>
+        <f>E1228*('Segments'!$D$27*E1227*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*E1227+0.4357405005*E1227+0.0330936548*E1227+0.0328406739))+E1229*('Segments'!$D$28*E1227*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*E1227+0.4357405005*E1227+0.0330936548*E1227+0.0328406739))+E1230*('Segments'!$D$29*E1227*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*E1227+0.4357405005*E1227+0.0330936548*E1227+0.0328406739))+E1231*('Segments'!$D$30*E1227*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*E1227+0.4357405005*E1227+0.0330936548*E1227+0.0328406739))+E1232*('Segments'!$D$31*E1227*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*E1227+0.4357405005*E1227+0.0330936548*E1227+0.0328406739))+E1233*('Segments'!$D$32*E1227*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*E1227+0.4357405005*E1227+0.0330936548*E1227+0.0328406739))+E1234*('Segments'!$D$33*E1227*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*E1227+0.4357405005*E1227+0.0330936548*E1227+0.0328406739))+E1235*('Segments'!$D$34*E1227*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*E1227+0.4357405005*E1227+0.0330936548*E1227+0.0328406739))</f>
         <v/>
       </c>
       <c r="F1238" s="18">
-        <f>F1228*('Segments'!$D$27*F1227*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*F1226+0.4357405005*F1226+0.0330936548*F1227+0.0328406739))+F1229*('Segments'!$D$28*F1227*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*F1226+0.4357405005*F1226+0.0330936548*F1227+0.0328406739))+F1230*('Segments'!$D$29*F1227*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*F1226+0.4357405005*F1226+0.0330936548*F1227+0.0328406739))+F1231*('Segments'!$D$30*F1227*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*F1226+0.4357405005*F1226+0.0330936548*F1227+0.0328406739))+F1232*('Segments'!$D$31*F1227*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*F1226+0.4357405005*F1226+0.0330936548*F1227+0.0328406739))+F1233*('Segments'!$D$32*F1227*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*F1226+0.4357405005*F1226+0.0330936548*F1227+0.0328406739))+F1234*('Segments'!$D$33*F1227*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*F1226+0.4357405005*F1226+0.0330936548*F1227+0.0328406739))+F1235*('Segments'!$D$34*F1227*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*F1226+0.4357405005*F1226+0.0330936548*F1227+0.0328406739))</f>
+        <f>F1228*('Segments'!$D$27*F1227*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*F1227+0.4357405005*F1227+0.0330936548*F1227+0.0328406739))+F1229*('Segments'!$D$28*F1227*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*F1227+0.4357405005*F1227+0.0330936548*F1227+0.0328406739))+F1230*('Segments'!$D$29*F1227*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*F1227+0.4357405005*F1227+0.0330936548*F1227+0.0328406739))+F1231*('Segments'!$D$30*F1227*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*F1227+0.4357405005*F1227+0.0330936548*F1227+0.0328406739))+F1232*('Segments'!$D$31*F1227*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*F1227+0.4357405005*F1227+0.0330936548*F1227+0.0328406739))+F1233*('Segments'!$D$32*F1227*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*F1227+0.4357405005*F1227+0.0330936548*F1227+0.0328406739))+F1234*('Segments'!$D$33*F1227*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*F1227+0.4357405005*F1227+0.0330936548*F1227+0.0328406739))+F1235*('Segments'!$D$34*F1227*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*F1227+0.4357405005*F1227+0.0330936548*F1227+0.0328406739))</f>
         <v/>
       </c>
       <c r="G1238" s="18">
-        <f>G1228*('Segments'!$D$27*G1227*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*G1226+0.4357405005*G1226+0.0330936548*G1227+0.0328406739))+G1229*('Segments'!$D$28*G1227*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*G1226+0.4357405005*G1226+0.0330936548*G1227+0.0328406739))+G1230*('Segments'!$D$29*G1227*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*G1226+0.4357405005*G1226+0.0330936548*G1227+0.0328406739))+G1231*('Segments'!$D$30*G1227*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*G1226+0.4357405005*G1226+0.0330936548*G1227+0.0328406739))+G1232*('Segments'!$D$31*G1227*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*G1226+0.4357405005*G1226+0.0330936548*G1227+0.0328406739))+G1233*('Segments'!$D$32*G1227*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*G1226+0.4357405005*G1226+0.0330936548*G1227+0.0328406739))+G1234*('Segments'!$D$33*G1227*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*G1226+0.4357405005*G1226+0.0330936548*G1227+0.0328406739))+G1235*('Segments'!$D$34*G1227*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*G1226+0.4357405005*G1226+0.0330936548*G1227+0.0328406739))</f>
+        <f>G1228*('Segments'!$D$27*G1227*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*G1227+0.4357405005*G1227+0.0330936548*G1227+0.0328406739))+G1229*('Segments'!$D$28*G1227*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*G1227+0.4357405005*G1227+0.0330936548*G1227+0.0328406739))+G1230*('Segments'!$D$29*G1227*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*G1227+0.4357405005*G1227+0.0330936548*G1227+0.0328406739))+G1231*('Segments'!$D$30*G1227*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*G1227+0.4357405005*G1227+0.0330936548*G1227+0.0328406739))+G1232*('Segments'!$D$31*G1227*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*G1227+0.4357405005*G1227+0.0330936548*G1227+0.0328406739))+G1233*('Segments'!$D$32*G1227*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*G1227+0.4357405005*G1227+0.0330936548*G1227+0.0328406739))+G1234*('Segments'!$D$33*G1227*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*G1227+0.4357405005*G1227+0.0330936548*G1227+0.0328406739))+G1235*('Segments'!$D$34*G1227*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*G1227+0.4357405005*G1227+0.0330936548*G1227+0.0328406739))</f>
         <v/>
       </c>
     </row>
@@ -30136,23 +30136,23 @@
         </is>
       </c>
       <c r="C1287" s="18">
-        <f>C1277*('Segments'!$D$27*C1276*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*C1275+0.4357405005*C1275+0.0330936548*C1276+0.0328406739))+C1278*('Segments'!$D$28*C1276*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*C1275+0.4357405005*C1275+0.0330936548*C1276+0.0328406739))+C1279*('Segments'!$D$29*C1276*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*C1275+0.4357405005*C1275+0.0330936548*C1276+0.0328406739))+C1280*('Segments'!$D$30*C1276*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*C1275+0.4357405005*C1275+0.0330936548*C1276+0.0328406739))+C1281*('Segments'!$D$31*C1276*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*C1275+0.4357405005*C1275+0.0330936548*C1276+0.0328406739))+C1282*('Segments'!$D$32*C1276*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*C1275+0.4357405005*C1275+0.0330936548*C1276+0.0328406739))+C1283*('Segments'!$D$33*C1276*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*C1275+0.4357405005*C1275+0.0330936548*C1276+0.0328406739))+C1284*('Segments'!$D$34*C1276*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*C1275+0.4357405005*C1275+0.0330936548*C1276+0.0328406739))</f>
+        <f>C1277*('Segments'!$D$27*C1276*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*C1276+0.4357405005*C1276+0.0330936548*C1276+0.0328406739))+C1278*('Segments'!$D$28*C1276*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*C1276+0.4357405005*C1276+0.0330936548*C1276+0.0328406739))+C1279*('Segments'!$D$29*C1276*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*C1276+0.4357405005*C1276+0.0330936548*C1276+0.0328406739))+C1280*('Segments'!$D$30*C1276*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*C1276+0.4357405005*C1276+0.0330936548*C1276+0.0328406739))+C1281*('Segments'!$D$31*C1276*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*C1276+0.4357405005*C1276+0.0330936548*C1276+0.0328406739))+C1282*('Segments'!$D$32*C1276*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*C1276+0.4357405005*C1276+0.0330936548*C1276+0.0328406739))+C1283*('Segments'!$D$33*C1276*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*C1276+0.4357405005*C1276+0.0330936548*C1276+0.0328406739))+C1284*('Segments'!$D$34*C1276*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*C1276+0.4357405005*C1276+0.0330936548*C1276+0.0328406739))</f>
         <v/>
       </c>
       <c r="D1287" s="18">
-        <f>D1277*('Segments'!$D$27*D1276*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*D1275+0.4357405005*D1275+0.0330936548*D1276+0.0328406739))+D1278*('Segments'!$D$28*D1276*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*D1275+0.4357405005*D1275+0.0330936548*D1276+0.0328406739))+D1279*('Segments'!$D$29*D1276*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*D1275+0.4357405005*D1275+0.0330936548*D1276+0.0328406739))+D1280*('Segments'!$D$30*D1276*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*D1275+0.4357405005*D1275+0.0330936548*D1276+0.0328406739))+D1281*('Segments'!$D$31*D1276*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*D1275+0.4357405005*D1275+0.0330936548*D1276+0.0328406739))+D1282*('Segments'!$D$32*D1276*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*D1275+0.4357405005*D1275+0.0330936548*D1276+0.0328406739))+D1283*('Segments'!$D$33*D1276*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*D1275+0.4357405005*D1275+0.0330936548*D1276+0.0328406739))+D1284*('Segments'!$D$34*D1276*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*D1275+0.4357405005*D1275+0.0330936548*D1276+0.0328406739))</f>
+        <f>D1277*('Segments'!$D$27*D1276*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*D1276+0.4357405005*D1276+0.0330936548*D1276+0.0328406739))+D1278*('Segments'!$D$28*D1276*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*D1276+0.4357405005*D1276+0.0330936548*D1276+0.0328406739))+D1279*('Segments'!$D$29*D1276*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*D1276+0.4357405005*D1276+0.0330936548*D1276+0.0328406739))+D1280*('Segments'!$D$30*D1276*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*D1276+0.4357405005*D1276+0.0330936548*D1276+0.0328406739))+D1281*('Segments'!$D$31*D1276*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*D1276+0.4357405005*D1276+0.0330936548*D1276+0.0328406739))+D1282*('Segments'!$D$32*D1276*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*D1276+0.4357405005*D1276+0.0330936548*D1276+0.0328406739))+D1283*('Segments'!$D$33*D1276*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*D1276+0.4357405005*D1276+0.0330936548*D1276+0.0328406739))+D1284*('Segments'!$D$34*D1276*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*D1276+0.4357405005*D1276+0.0330936548*D1276+0.0328406739))</f>
         <v/>
       </c>
       <c r="E1287" s="18">
-        <f>E1277*('Segments'!$D$27*E1276*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*E1275+0.4357405005*E1275+0.0330936548*E1276+0.0328406739))+E1278*('Segments'!$D$28*E1276*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*E1275+0.4357405005*E1275+0.0330936548*E1276+0.0328406739))+E1279*('Segments'!$D$29*E1276*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*E1275+0.4357405005*E1275+0.0330936548*E1276+0.0328406739))+E1280*('Segments'!$D$30*E1276*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*E1275+0.4357405005*E1275+0.0330936548*E1276+0.0328406739))+E1281*('Segments'!$D$31*E1276*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*E1275+0.4357405005*E1275+0.0330936548*E1276+0.0328406739))+E1282*('Segments'!$D$32*E1276*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*E1275+0.4357405005*E1275+0.0330936548*E1276+0.0328406739))+E1283*('Segments'!$D$33*E1276*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*E1275+0.4357405005*E1275+0.0330936548*E1276+0.0328406739))+E1284*('Segments'!$D$34*E1276*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*E1275+0.4357405005*E1275+0.0330936548*E1276+0.0328406739))</f>
+        <f>E1277*('Segments'!$D$27*E1276*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*E1276+0.4357405005*E1276+0.0330936548*E1276+0.0328406739))+E1278*('Segments'!$D$28*E1276*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*E1276+0.4357405005*E1276+0.0330936548*E1276+0.0328406739))+E1279*('Segments'!$D$29*E1276*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*E1276+0.4357405005*E1276+0.0330936548*E1276+0.0328406739))+E1280*('Segments'!$D$30*E1276*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*E1276+0.4357405005*E1276+0.0330936548*E1276+0.0328406739))+E1281*('Segments'!$D$31*E1276*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*E1276+0.4357405005*E1276+0.0330936548*E1276+0.0328406739))+E1282*('Segments'!$D$32*E1276*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*E1276+0.4357405005*E1276+0.0330936548*E1276+0.0328406739))+E1283*('Segments'!$D$33*E1276*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*E1276+0.4357405005*E1276+0.0330936548*E1276+0.0328406739))+E1284*('Segments'!$D$34*E1276*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*E1276+0.4357405005*E1276+0.0330936548*E1276+0.0328406739))</f>
         <v/>
       </c>
       <c r="F1287" s="18">
-        <f>F1277*('Segments'!$D$27*F1276*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*F1275+0.4357405005*F1275+0.0330936548*F1276+0.0328406739))+F1278*('Segments'!$D$28*F1276*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*F1275+0.4357405005*F1275+0.0330936548*F1276+0.0328406739))+F1279*('Segments'!$D$29*F1276*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*F1275+0.4357405005*F1275+0.0330936548*F1276+0.0328406739))+F1280*('Segments'!$D$30*F1276*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*F1275+0.4357405005*F1275+0.0330936548*F1276+0.0328406739))+F1281*('Segments'!$D$31*F1276*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*F1275+0.4357405005*F1275+0.0330936548*F1276+0.0328406739))+F1282*('Segments'!$D$32*F1276*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*F1275+0.4357405005*F1275+0.0330936548*F1276+0.0328406739))+F1283*('Segments'!$D$33*F1276*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*F1275+0.4357405005*F1275+0.0330936548*F1276+0.0328406739))+F1284*('Segments'!$D$34*F1276*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*F1275+0.4357405005*F1275+0.0330936548*F1276+0.0328406739))</f>
+        <f>F1277*('Segments'!$D$27*F1276*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*F1276+0.4357405005*F1276+0.0330936548*F1276+0.0328406739))+F1278*('Segments'!$D$28*F1276*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*F1276+0.4357405005*F1276+0.0330936548*F1276+0.0328406739))+F1279*('Segments'!$D$29*F1276*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*F1276+0.4357405005*F1276+0.0330936548*F1276+0.0328406739))+F1280*('Segments'!$D$30*F1276*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*F1276+0.4357405005*F1276+0.0330936548*F1276+0.0328406739))+F1281*('Segments'!$D$31*F1276*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*F1276+0.4357405005*F1276+0.0330936548*F1276+0.0328406739))+F1282*('Segments'!$D$32*F1276*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*F1276+0.4357405005*F1276+0.0330936548*F1276+0.0328406739))+F1283*('Segments'!$D$33*F1276*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*F1276+0.4357405005*F1276+0.0330936548*F1276+0.0328406739))+F1284*('Segments'!$D$34*F1276*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*F1276+0.4357405005*F1276+0.0330936548*F1276+0.0328406739))</f>
         <v/>
       </c>
       <c r="G1287" s="18">
-        <f>G1277*('Segments'!$D$27*G1276*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*G1275+0.4357405005*G1275+0.0330936548*G1276+0.0328406739))+G1278*('Segments'!$D$28*G1276*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*G1275+0.4357405005*G1275+0.0330936548*G1276+0.0328406739))+G1279*('Segments'!$D$29*G1276*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*G1275+0.4357405005*G1275+0.0330936548*G1276+0.0328406739))+G1280*('Segments'!$D$30*G1276*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*G1275+0.4357405005*G1275+0.0330936548*G1276+0.0328406739))+G1281*('Segments'!$D$31*G1276*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*G1275+0.4357405005*G1275+0.0330936548*G1276+0.0328406739))+G1282*('Segments'!$D$32*G1276*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*G1275+0.4357405005*G1275+0.0330936548*G1276+0.0328406739))+G1283*('Segments'!$D$33*G1276*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*G1275+0.4357405005*G1275+0.0330936548*G1276+0.0328406739))+G1284*('Segments'!$D$34*G1276*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*G1275+0.4357405005*G1275+0.0330936548*G1276+0.0328406739))</f>
+        <f>G1277*('Segments'!$D$27*G1276*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*G1276+0.4357405005*G1276+0.0330936548*G1276+0.0328406739))+G1278*('Segments'!$D$28*G1276*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*G1276+0.4357405005*G1276+0.0330936548*G1276+0.0328406739))+G1279*('Segments'!$D$29*G1276*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*G1276+0.4357405005*G1276+0.0330936548*G1276+0.0328406739))+G1280*('Segments'!$D$30*G1276*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*G1276+0.4357405005*G1276+0.0330936548*G1276+0.0328406739))+G1281*('Segments'!$D$31*G1276*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*G1276+0.4357405005*G1276+0.0330936548*G1276+0.0328406739))+G1282*('Segments'!$D$32*G1276*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*G1276+0.4357405005*G1276+0.0330936548*G1276+0.0328406739))+G1283*('Segments'!$D$33*G1276*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*G1276+0.4357405005*G1276+0.0330936548*G1276+0.0328406739))+G1284*('Segments'!$D$34*G1276*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*G1276+0.4357405005*G1276+0.0330936548*G1276+0.0328406739))</f>
         <v/>
       </c>
     </row>
@@ -31206,23 +31206,23 @@
         </is>
       </c>
       <c r="C1336" s="18">
-        <f>C1326*('Segments'!$D$27*C1325*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*C1324+0.4357405005*C1324+0.0330936548*C1325+0.0328406739))+C1327*('Segments'!$D$28*C1325*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*C1324+0.4357405005*C1324+0.0330936548*C1325+0.0328406739))+C1328*('Segments'!$D$29*C1325*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*C1324+0.4357405005*C1324+0.0330936548*C1325+0.0328406739))+C1329*('Segments'!$D$30*C1325*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*C1324+0.4357405005*C1324+0.0330936548*C1325+0.0328406739))+C1330*('Segments'!$D$31*C1325*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*C1324+0.4357405005*C1324+0.0330936548*C1325+0.0328406739))+C1331*('Segments'!$D$32*C1325*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*C1324+0.4357405005*C1324+0.0330936548*C1325+0.0328406739))+C1332*('Segments'!$D$33*C1325*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*C1324+0.4357405005*C1324+0.0330936548*C1325+0.0328406739))+C1333*('Segments'!$D$34*C1325*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*C1324+0.4357405005*C1324+0.0330936548*C1325+0.0328406739))</f>
+        <f>C1326*('Segments'!$D$27*C1325*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*C1325+0.4357405005*C1325+0.0330936548*C1325+0.0328406739))+C1327*('Segments'!$D$28*C1325*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*C1325+0.4357405005*C1325+0.0330936548*C1325+0.0328406739))+C1328*('Segments'!$D$29*C1325*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*C1325+0.4357405005*C1325+0.0330936548*C1325+0.0328406739))+C1329*('Segments'!$D$30*C1325*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*C1325+0.4357405005*C1325+0.0330936548*C1325+0.0328406739))+C1330*('Segments'!$D$31*C1325*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*C1325+0.4357405005*C1325+0.0330936548*C1325+0.0328406739))+C1331*('Segments'!$D$32*C1325*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*C1325+0.4357405005*C1325+0.0330936548*C1325+0.0328406739))+C1332*('Segments'!$D$33*C1325*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*C1325+0.4357405005*C1325+0.0330936548*C1325+0.0328406739))+C1333*('Segments'!$D$34*C1325*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*C1325+0.4357405005*C1325+0.0330936548*C1325+0.0328406739))</f>
         <v/>
       </c>
       <c r="D1336" s="18">
-        <f>D1326*('Segments'!$D$27*D1325*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*D1324+0.4357405005*D1324+0.0330936548*D1325+0.0328406739))+D1327*('Segments'!$D$28*D1325*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*D1324+0.4357405005*D1324+0.0330936548*D1325+0.0328406739))+D1328*('Segments'!$D$29*D1325*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*D1324+0.4357405005*D1324+0.0330936548*D1325+0.0328406739))+D1329*('Segments'!$D$30*D1325*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*D1324+0.4357405005*D1324+0.0330936548*D1325+0.0328406739))+D1330*('Segments'!$D$31*D1325*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*D1324+0.4357405005*D1324+0.0330936548*D1325+0.0328406739))+D1331*('Segments'!$D$32*D1325*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*D1324+0.4357405005*D1324+0.0330936548*D1325+0.0328406739))+D1332*('Segments'!$D$33*D1325*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*D1324+0.4357405005*D1324+0.0330936548*D1325+0.0328406739))+D1333*('Segments'!$D$34*D1325*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*D1324+0.4357405005*D1324+0.0330936548*D1325+0.0328406739))</f>
+        <f>D1326*('Segments'!$D$27*D1325*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*D1325+0.4357405005*D1325+0.0330936548*D1325+0.0328406739))+D1327*('Segments'!$D$28*D1325*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*D1325+0.4357405005*D1325+0.0330936548*D1325+0.0328406739))+D1328*('Segments'!$D$29*D1325*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*D1325+0.4357405005*D1325+0.0330936548*D1325+0.0328406739))+D1329*('Segments'!$D$30*D1325*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*D1325+0.4357405005*D1325+0.0330936548*D1325+0.0328406739))+D1330*('Segments'!$D$31*D1325*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*D1325+0.4357405005*D1325+0.0330936548*D1325+0.0328406739))+D1331*('Segments'!$D$32*D1325*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*D1325+0.4357405005*D1325+0.0330936548*D1325+0.0328406739))+D1332*('Segments'!$D$33*D1325*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*D1325+0.4357405005*D1325+0.0330936548*D1325+0.0328406739))+D1333*('Segments'!$D$34*D1325*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*D1325+0.4357405005*D1325+0.0330936548*D1325+0.0328406739))</f>
         <v/>
       </c>
       <c r="E1336" s="18">
-        <f>E1326*('Segments'!$D$27*E1325*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*E1324+0.4357405005*E1324+0.0330936548*E1325+0.0328406739))+E1327*('Segments'!$D$28*E1325*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*E1324+0.4357405005*E1324+0.0330936548*E1325+0.0328406739))+E1328*('Segments'!$D$29*E1325*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*E1324+0.4357405005*E1324+0.0330936548*E1325+0.0328406739))+E1329*('Segments'!$D$30*E1325*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*E1324+0.4357405005*E1324+0.0330936548*E1325+0.0328406739))+E1330*('Segments'!$D$31*E1325*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*E1324+0.4357405005*E1324+0.0330936548*E1325+0.0328406739))+E1331*('Segments'!$D$32*E1325*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*E1324+0.4357405005*E1324+0.0330936548*E1325+0.0328406739))+E1332*('Segments'!$D$33*E1325*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*E1324+0.4357405005*E1324+0.0330936548*E1325+0.0328406739))+E1333*('Segments'!$D$34*E1325*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*E1324+0.4357405005*E1324+0.0330936548*E1325+0.0328406739))</f>
+        <f>E1326*('Segments'!$D$27*E1325*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*E1325+0.4357405005*E1325+0.0330936548*E1325+0.0328406739))+E1327*('Segments'!$D$28*E1325*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*E1325+0.4357405005*E1325+0.0330936548*E1325+0.0328406739))+E1328*('Segments'!$D$29*E1325*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*E1325+0.4357405005*E1325+0.0330936548*E1325+0.0328406739))+E1329*('Segments'!$D$30*E1325*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*E1325+0.4357405005*E1325+0.0330936548*E1325+0.0328406739))+E1330*('Segments'!$D$31*E1325*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*E1325+0.4357405005*E1325+0.0330936548*E1325+0.0328406739))+E1331*('Segments'!$D$32*E1325*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*E1325+0.4357405005*E1325+0.0330936548*E1325+0.0328406739))+E1332*('Segments'!$D$33*E1325*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*E1325+0.4357405005*E1325+0.0330936548*E1325+0.0328406739))+E1333*('Segments'!$D$34*E1325*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*E1325+0.4357405005*E1325+0.0330936548*E1325+0.0328406739))</f>
         <v/>
       </c>
       <c r="F1336" s="18">
-        <f>F1326*('Segments'!$D$27*F1325*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*F1324+0.4357405005*F1324+0.0330936548*F1325+0.0328406739))+F1327*('Segments'!$D$28*F1325*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*F1324+0.4357405005*F1324+0.0330936548*F1325+0.0328406739))+F1328*('Segments'!$D$29*F1325*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*F1324+0.4357405005*F1324+0.0330936548*F1325+0.0328406739))+F1329*('Segments'!$D$30*F1325*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*F1324+0.4357405005*F1324+0.0330936548*F1325+0.0328406739))+F1330*('Segments'!$D$31*F1325*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*F1324+0.4357405005*F1324+0.0330936548*F1325+0.0328406739))+F1331*('Segments'!$D$32*F1325*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*F1324+0.4357405005*F1324+0.0330936548*F1325+0.0328406739))+F1332*('Segments'!$D$33*F1325*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*F1324+0.4357405005*F1324+0.0330936548*F1325+0.0328406739))+F1333*('Segments'!$D$34*F1325*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*F1324+0.4357405005*F1324+0.0330936548*F1325+0.0328406739))</f>
+        <f>F1326*('Segments'!$D$27*F1325*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*F1325+0.4357405005*F1325+0.0330936548*F1325+0.0328406739))+F1327*('Segments'!$D$28*F1325*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*F1325+0.4357405005*F1325+0.0330936548*F1325+0.0328406739))+F1328*('Segments'!$D$29*F1325*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*F1325+0.4357405005*F1325+0.0330936548*F1325+0.0328406739))+F1329*('Segments'!$D$30*F1325*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*F1325+0.4357405005*F1325+0.0330936548*F1325+0.0328406739))+F1330*('Segments'!$D$31*F1325*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*F1325+0.4357405005*F1325+0.0330936548*F1325+0.0328406739))+F1331*('Segments'!$D$32*F1325*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*F1325+0.4357405005*F1325+0.0330936548*F1325+0.0328406739))+F1332*('Segments'!$D$33*F1325*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*F1325+0.4357405005*F1325+0.0330936548*F1325+0.0328406739))+F1333*('Segments'!$D$34*F1325*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*F1325+0.4357405005*F1325+0.0330936548*F1325+0.0328406739))</f>
         <v/>
       </c>
       <c r="G1336" s="18">
-        <f>G1326*('Segments'!$D$27*G1325*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*G1324+0.4357405005*G1324+0.0330936548*G1325+0.0328406739))+G1327*('Segments'!$D$28*G1325*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*G1324+0.4357405005*G1324+0.0330936548*G1325+0.0328406739))+G1328*('Segments'!$D$29*G1325*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*G1324+0.4357405005*G1324+0.0330936548*G1325+0.0328406739))+G1329*('Segments'!$D$30*G1325*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*G1324+0.4357405005*G1324+0.0330936548*G1325+0.0328406739))+G1330*('Segments'!$D$31*G1325*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*G1324+0.4357405005*G1324+0.0330936548*G1325+0.0328406739))+G1331*('Segments'!$D$32*G1325*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*G1324+0.4357405005*G1324+0.0330936548*G1325+0.0328406739))+G1332*('Segments'!$D$33*G1325*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*G1324+0.4357405005*G1324+0.0330936548*G1325+0.0328406739))+G1333*('Segments'!$D$34*G1325*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*G1324+0.4357405005*G1324+0.0330936548*G1325+0.0328406739))</f>
+        <f>G1326*('Segments'!$D$27*G1325*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*G1325+0.4357405005*G1325+0.0330936548*G1325+0.0328406739))+G1327*('Segments'!$D$28*G1325*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*G1325+0.4357405005*G1325+0.0330936548*G1325+0.0328406739))+G1328*('Segments'!$D$29*G1325*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*G1325+0.4357405005*G1325+0.0330936548*G1325+0.0328406739))+G1329*('Segments'!$D$30*G1325*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*G1325+0.4357405005*G1325+0.0330936548*G1325+0.0328406739))+G1330*('Segments'!$D$31*G1325*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*G1325+0.4357405005*G1325+0.0330936548*G1325+0.0328406739))+G1331*('Segments'!$D$32*G1325*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*G1325+0.4357405005*G1325+0.0330936548*G1325+0.0328406739))+G1332*('Segments'!$D$33*G1325*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*G1325+0.4357405005*G1325+0.0330936548*G1325+0.0328406739))+G1333*('Segments'!$D$34*G1325*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*G1325+0.4357405005*G1325+0.0330936548*G1325+0.0328406739))</f>
         <v/>
       </c>
     </row>
@@ -32276,23 +32276,23 @@
         </is>
       </c>
       <c r="C1385" s="18">
-        <f>C1375*('Segments'!$D$27*C1374*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*C1373+0.4357405005*C1373+0.0330936548*C1374+0.0328406739))+C1376*('Segments'!$D$28*C1374*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*C1373+0.4357405005*C1373+0.0330936548*C1374+0.0328406739))+C1377*('Segments'!$D$29*C1374*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*C1373+0.4357405005*C1373+0.0330936548*C1374+0.0328406739))+C1378*('Segments'!$D$30*C1374*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*C1373+0.4357405005*C1373+0.0330936548*C1374+0.0328406739))+C1379*('Segments'!$D$31*C1374*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*C1373+0.4357405005*C1373+0.0330936548*C1374+0.0328406739))+C1380*('Segments'!$D$32*C1374*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*C1373+0.4357405005*C1373+0.0330936548*C1374+0.0328406739))+C1381*('Segments'!$D$33*C1374*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*C1373+0.4357405005*C1373+0.0330936548*C1374+0.0328406739))+C1382*('Segments'!$D$34*C1374*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*C1373+0.4357405005*C1373+0.0330936548*C1374+0.0328406739))</f>
+        <f>C1375*('Segments'!$D$27*C1374*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*C1374+0.4357405005*C1374+0.0330936548*C1374+0.0328406739))+C1376*('Segments'!$D$28*C1374*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*C1374+0.4357405005*C1374+0.0330936548*C1374+0.0328406739))+C1377*('Segments'!$D$29*C1374*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*C1374+0.4357405005*C1374+0.0330936548*C1374+0.0328406739))+C1378*('Segments'!$D$30*C1374*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*C1374+0.4357405005*C1374+0.0330936548*C1374+0.0328406739))+C1379*('Segments'!$D$31*C1374*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*C1374+0.4357405005*C1374+0.0330936548*C1374+0.0328406739))+C1380*('Segments'!$D$32*C1374*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*C1374+0.4357405005*C1374+0.0330936548*C1374+0.0328406739))+C1381*('Segments'!$D$33*C1374*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*C1374+0.4357405005*C1374+0.0330936548*C1374+0.0328406739))+C1382*('Segments'!$D$34*C1374*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*C1374+0.4357405005*C1374+0.0330936548*C1374+0.0328406739))</f>
         <v/>
       </c>
       <c r="D1385" s="18">
-        <f>D1375*('Segments'!$D$27*D1374*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*D1373+0.4357405005*D1373+0.0330936548*D1374+0.0328406739))+D1376*('Segments'!$D$28*D1374*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*D1373+0.4357405005*D1373+0.0330936548*D1374+0.0328406739))+D1377*('Segments'!$D$29*D1374*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*D1373+0.4357405005*D1373+0.0330936548*D1374+0.0328406739))+D1378*('Segments'!$D$30*D1374*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*D1373+0.4357405005*D1373+0.0330936548*D1374+0.0328406739))+D1379*('Segments'!$D$31*D1374*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*D1373+0.4357405005*D1373+0.0330936548*D1374+0.0328406739))+D1380*('Segments'!$D$32*D1374*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*D1373+0.4357405005*D1373+0.0330936548*D1374+0.0328406739))+D1381*('Segments'!$D$33*D1374*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*D1373+0.4357405005*D1373+0.0330936548*D1374+0.0328406739))+D1382*('Segments'!$D$34*D1374*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*D1373+0.4357405005*D1373+0.0330936548*D1374+0.0328406739))</f>
+        <f>D1375*('Segments'!$D$27*D1374*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*D1374+0.4357405005*D1374+0.0330936548*D1374+0.0328406739))+D1376*('Segments'!$D$28*D1374*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*D1374+0.4357405005*D1374+0.0330936548*D1374+0.0328406739))+D1377*('Segments'!$D$29*D1374*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*D1374+0.4357405005*D1374+0.0330936548*D1374+0.0328406739))+D1378*('Segments'!$D$30*D1374*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*D1374+0.4357405005*D1374+0.0330936548*D1374+0.0328406739))+D1379*('Segments'!$D$31*D1374*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*D1374+0.4357405005*D1374+0.0330936548*D1374+0.0328406739))+D1380*('Segments'!$D$32*D1374*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*D1374+0.4357405005*D1374+0.0330936548*D1374+0.0328406739))+D1381*('Segments'!$D$33*D1374*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*D1374+0.4357405005*D1374+0.0330936548*D1374+0.0328406739))+D1382*('Segments'!$D$34*D1374*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*D1374+0.4357405005*D1374+0.0330936548*D1374+0.0328406739))</f>
         <v/>
       </c>
       <c r="E1385" s="18">
-        <f>E1375*('Segments'!$D$27*E1374*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*E1373+0.4357405005*E1373+0.0330936548*E1374+0.0328406739))+E1376*('Segments'!$D$28*E1374*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*E1373+0.4357405005*E1373+0.0330936548*E1374+0.0328406739))+E1377*('Segments'!$D$29*E1374*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*E1373+0.4357405005*E1373+0.0330936548*E1374+0.0328406739))+E1378*('Segments'!$D$30*E1374*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*E1373+0.4357405005*E1373+0.0330936548*E1374+0.0328406739))+E1379*('Segments'!$D$31*E1374*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*E1373+0.4357405005*E1373+0.0330936548*E1374+0.0328406739))+E1380*('Segments'!$D$32*E1374*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*E1373+0.4357405005*E1373+0.0330936548*E1374+0.0328406739))+E1381*('Segments'!$D$33*E1374*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*E1373+0.4357405005*E1373+0.0330936548*E1374+0.0328406739))+E1382*('Segments'!$D$34*E1374*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*E1373+0.4357405005*E1373+0.0330936548*E1374+0.0328406739))</f>
+        <f>E1375*('Segments'!$D$27*E1374*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*E1374+0.4357405005*E1374+0.0330936548*E1374+0.0328406739))+E1376*('Segments'!$D$28*E1374*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*E1374+0.4357405005*E1374+0.0330936548*E1374+0.0328406739))+E1377*('Segments'!$D$29*E1374*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*E1374+0.4357405005*E1374+0.0330936548*E1374+0.0328406739))+E1378*('Segments'!$D$30*E1374*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*E1374+0.4357405005*E1374+0.0330936548*E1374+0.0328406739))+E1379*('Segments'!$D$31*E1374*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*E1374+0.4357405005*E1374+0.0330936548*E1374+0.0328406739))+E1380*('Segments'!$D$32*E1374*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*E1374+0.4357405005*E1374+0.0330936548*E1374+0.0328406739))+E1381*('Segments'!$D$33*E1374*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*E1374+0.4357405005*E1374+0.0330936548*E1374+0.0328406739))+E1382*('Segments'!$D$34*E1374*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*E1374+0.4357405005*E1374+0.0330936548*E1374+0.0328406739))</f>
         <v/>
       </c>
       <c r="F1385" s="18">
-        <f>F1375*('Segments'!$D$27*F1374*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*F1373+0.4357405005*F1373+0.0330936548*F1374+0.0328406739))+F1376*('Segments'!$D$28*F1374*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*F1373+0.4357405005*F1373+0.0330936548*F1374+0.0328406739))+F1377*('Segments'!$D$29*F1374*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*F1373+0.4357405005*F1373+0.0330936548*F1374+0.0328406739))+F1378*('Segments'!$D$30*F1374*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*F1373+0.4357405005*F1373+0.0330936548*F1374+0.0328406739))+F1379*('Segments'!$D$31*F1374*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*F1373+0.4357405005*F1373+0.0330936548*F1374+0.0328406739))+F1380*('Segments'!$D$32*F1374*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*F1373+0.4357405005*F1373+0.0330936548*F1374+0.0328406739))+F1381*('Segments'!$D$33*F1374*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*F1373+0.4357405005*F1373+0.0330936548*F1374+0.0328406739))+F1382*('Segments'!$D$34*F1374*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*F1373+0.4357405005*F1373+0.0330936548*F1374+0.0328406739))</f>
+        <f>F1375*('Segments'!$D$27*F1374*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*F1374+0.4357405005*F1374+0.0330936548*F1374+0.0328406739))+F1376*('Segments'!$D$28*F1374*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*F1374+0.4357405005*F1374+0.0330936548*F1374+0.0328406739))+F1377*('Segments'!$D$29*F1374*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*F1374+0.4357405005*F1374+0.0330936548*F1374+0.0328406739))+F1378*('Segments'!$D$30*F1374*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*F1374+0.4357405005*F1374+0.0330936548*F1374+0.0328406739))+F1379*('Segments'!$D$31*F1374*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*F1374+0.4357405005*F1374+0.0330936548*F1374+0.0328406739))+F1380*('Segments'!$D$32*F1374*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*F1374+0.4357405005*F1374+0.0330936548*F1374+0.0328406739))+F1381*('Segments'!$D$33*F1374*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*F1374+0.4357405005*F1374+0.0330936548*F1374+0.0328406739))+F1382*('Segments'!$D$34*F1374*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*F1374+0.4357405005*F1374+0.0330936548*F1374+0.0328406739))</f>
         <v/>
       </c>
       <c r="G1385" s="18">
-        <f>G1375*('Segments'!$D$27*G1374*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*G1373+0.4357405005*G1373+0.0330936548*G1374+0.0328406739))+G1376*('Segments'!$D$28*G1374*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*G1373+0.4357405005*G1373+0.0330936548*G1374+0.0328406739))+G1377*('Segments'!$D$29*G1374*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*G1373+0.4357405005*G1373+0.0330936548*G1374+0.0328406739))+G1378*('Segments'!$D$30*G1374*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*G1373+0.4357405005*G1373+0.0330936548*G1374+0.0328406739))+G1379*('Segments'!$D$31*G1374*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*G1373+0.4357405005*G1373+0.0330936548*G1374+0.0328406739))+G1380*('Segments'!$D$32*G1374*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*G1373+0.4357405005*G1373+0.0330936548*G1374+0.0328406739))+G1381*('Segments'!$D$33*G1374*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*G1373+0.4357405005*G1373+0.0330936548*G1374+0.0328406739))+G1382*('Segments'!$D$34*G1374*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*G1373+0.4357405005*G1373+0.0330936548*G1374+0.0328406739))</f>
+        <f>G1375*('Segments'!$D$27*G1374*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*G1374+0.4357405005*G1374+0.0330936548*G1374+0.0328406739))+G1376*('Segments'!$D$28*G1374*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*G1374+0.4357405005*G1374+0.0330936548*G1374+0.0328406739))+G1377*('Segments'!$D$29*G1374*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*G1374+0.4357405005*G1374+0.0330936548*G1374+0.0328406739))+G1378*('Segments'!$D$30*G1374*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*G1374+0.4357405005*G1374+0.0330936548*G1374+0.0328406739))+G1379*('Segments'!$D$31*G1374*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*G1374+0.4357405005*G1374+0.0330936548*G1374+0.0328406739))+G1380*('Segments'!$D$32*G1374*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*G1374+0.4357405005*G1374+0.0330936548*G1374+0.0328406739))+G1381*('Segments'!$D$33*G1374*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*G1374+0.4357405005*G1374+0.0330936548*G1374+0.0328406739))+G1382*('Segments'!$D$34*G1374*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*G1374+0.4357405005*G1374+0.0330936548*G1374+0.0328406739))</f>
         <v/>
       </c>
     </row>
@@ -33346,23 +33346,23 @@
         </is>
       </c>
       <c r="C1434" s="18">
-        <f>C1424*('Segments'!$D$27*C1423*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*C1422+0.4357405005*C1422+0.0330936548*C1423+0.0328406739))+C1425*('Segments'!$D$28*C1423*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*C1422+0.4357405005*C1422+0.0330936548*C1423+0.0328406739))+C1426*('Segments'!$D$29*C1423*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*C1422+0.4357405005*C1422+0.0330936548*C1423+0.0328406739))+C1427*('Segments'!$D$30*C1423*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*C1422+0.4357405005*C1422+0.0330936548*C1423+0.0328406739))+C1428*('Segments'!$D$31*C1423*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*C1422+0.4357405005*C1422+0.0330936548*C1423+0.0328406739))+C1429*('Segments'!$D$32*C1423*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*C1422+0.4357405005*C1422+0.0330936548*C1423+0.0328406739))+C1430*('Segments'!$D$33*C1423*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*C1422+0.4357405005*C1422+0.0330936548*C1423+0.0328406739))+C1431*('Segments'!$D$34*C1423*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*C1422+0.4357405005*C1422+0.0330936548*C1423+0.0328406739))</f>
+        <f>C1424*('Segments'!$D$27*C1423*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*C1423+0.4357405005*C1423+0.0330936548*C1423+0.0328406739))+C1425*('Segments'!$D$28*C1423*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*C1423+0.4357405005*C1423+0.0330936548*C1423+0.0328406739))+C1426*('Segments'!$D$29*C1423*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*C1423+0.4357405005*C1423+0.0330936548*C1423+0.0328406739))+C1427*('Segments'!$D$30*C1423*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*C1423+0.4357405005*C1423+0.0330936548*C1423+0.0328406739))+C1428*('Segments'!$D$31*C1423*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*C1423+0.4357405005*C1423+0.0330936548*C1423+0.0328406739))+C1429*('Segments'!$D$32*C1423*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*C1423+0.4357405005*C1423+0.0330936548*C1423+0.0328406739))+C1430*('Segments'!$D$33*C1423*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*C1423+0.4357405005*C1423+0.0330936548*C1423+0.0328406739))+C1431*('Segments'!$D$34*C1423*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*C1423+0.4357405005*C1423+0.0330936548*C1423+0.0328406739))</f>
         <v/>
       </c>
       <c r="D1434" s="18">
-        <f>D1424*('Segments'!$D$27*D1423*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*D1422+0.4357405005*D1422+0.0330936548*D1423+0.0328406739))+D1425*('Segments'!$D$28*D1423*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*D1422+0.4357405005*D1422+0.0330936548*D1423+0.0328406739))+D1426*('Segments'!$D$29*D1423*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*D1422+0.4357405005*D1422+0.0330936548*D1423+0.0328406739))+D1427*('Segments'!$D$30*D1423*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*D1422+0.4357405005*D1422+0.0330936548*D1423+0.0328406739))+D1428*('Segments'!$D$31*D1423*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*D1422+0.4357405005*D1422+0.0330936548*D1423+0.0328406739))+D1429*('Segments'!$D$32*D1423*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*D1422+0.4357405005*D1422+0.0330936548*D1423+0.0328406739))+D1430*('Segments'!$D$33*D1423*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*D1422+0.4357405005*D1422+0.0330936548*D1423+0.0328406739))+D1431*('Segments'!$D$34*D1423*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*D1422+0.4357405005*D1422+0.0330936548*D1423+0.0328406739))</f>
+        <f>D1424*('Segments'!$D$27*D1423*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*D1423+0.4357405005*D1423+0.0330936548*D1423+0.0328406739))+D1425*('Segments'!$D$28*D1423*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*D1423+0.4357405005*D1423+0.0330936548*D1423+0.0328406739))+D1426*('Segments'!$D$29*D1423*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*D1423+0.4357405005*D1423+0.0330936548*D1423+0.0328406739))+D1427*('Segments'!$D$30*D1423*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*D1423+0.4357405005*D1423+0.0330936548*D1423+0.0328406739))+D1428*('Segments'!$D$31*D1423*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*D1423+0.4357405005*D1423+0.0330936548*D1423+0.0328406739))+D1429*('Segments'!$D$32*D1423*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*D1423+0.4357405005*D1423+0.0330936548*D1423+0.0328406739))+D1430*('Segments'!$D$33*D1423*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*D1423+0.4357405005*D1423+0.0330936548*D1423+0.0328406739))+D1431*('Segments'!$D$34*D1423*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*D1423+0.4357405005*D1423+0.0330936548*D1423+0.0328406739))</f>
         <v/>
       </c>
       <c r="E1434" s="18">
-        <f>E1424*('Segments'!$D$27*E1423*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*E1422+0.4357405005*E1422+0.0330936548*E1423+0.0328406739))+E1425*('Segments'!$D$28*E1423*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*E1422+0.4357405005*E1422+0.0330936548*E1423+0.0328406739))+E1426*('Segments'!$D$29*E1423*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*E1422+0.4357405005*E1422+0.0330936548*E1423+0.0328406739))+E1427*('Segments'!$D$30*E1423*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*E1422+0.4357405005*E1422+0.0330936548*E1423+0.0328406739))+E1428*('Segments'!$D$31*E1423*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*E1422+0.4357405005*E1422+0.0330936548*E1423+0.0328406739))+E1429*('Segments'!$D$32*E1423*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*E1422+0.4357405005*E1422+0.0330936548*E1423+0.0328406739))+E1430*('Segments'!$D$33*E1423*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*E1422+0.4357405005*E1422+0.0330936548*E1423+0.0328406739))+E1431*('Segments'!$D$34*E1423*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*E1422+0.4357405005*E1422+0.0330936548*E1423+0.0328406739))</f>
+        <f>E1424*('Segments'!$D$27*E1423*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*E1423+0.4357405005*E1423+0.0330936548*E1423+0.0328406739))+E1425*('Segments'!$D$28*E1423*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*E1423+0.4357405005*E1423+0.0330936548*E1423+0.0328406739))+E1426*('Segments'!$D$29*E1423*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*E1423+0.4357405005*E1423+0.0330936548*E1423+0.0328406739))+E1427*('Segments'!$D$30*E1423*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*E1423+0.4357405005*E1423+0.0330936548*E1423+0.0328406739))+E1428*('Segments'!$D$31*E1423*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*E1423+0.4357405005*E1423+0.0330936548*E1423+0.0328406739))+E1429*('Segments'!$D$32*E1423*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*E1423+0.4357405005*E1423+0.0330936548*E1423+0.0328406739))+E1430*('Segments'!$D$33*E1423*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*E1423+0.4357405005*E1423+0.0330936548*E1423+0.0328406739))+E1431*('Segments'!$D$34*E1423*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*E1423+0.4357405005*E1423+0.0330936548*E1423+0.0328406739))</f>
         <v/>
       </c>
       <c r="F1434" s="18">
-        <f>F1424*('Segments'!$D$27*F1423*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*F1422+0.4357405005*F1422+0.0330936548*F1423+0.0328406739))+F1425*('Segments'!$D$28*F1423*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*F1422+0.4357405005*F1422+0.0330936548*F1423+0.0328406739))+F1426*('Segments'!$D$29*F1423*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*F1422+0.4357405005*F1422+0.0330936548*F1423+0.0328406739))+F1427*('Segments'!$D$30*F1423*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*F1422+0.4357405005*F1422+0.0330936548*F1423+0.0328406739))+F1428*('Segments'!$D$31*F1423*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*F1422+0.4357405005*F1422+0.0330936548*F1423+0.0328406739))+F1429*('Segments'!$D$32*F1423*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*F1422+0.4357405005*F1422+0.0330936548*F1423+0.0328406739))+F1430*('Segments'!$D$33*F1423*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*F1422+0.4357405005*F1422+0.0330936548*F1423+0.0328406739))+F1431*('Segments'!$D$34*F1423*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*F1422+0.4357405005*F1422+0.0330936548*F1423+0.0328406739))</f>
+        <f>F1424*('Segments'!$D$27*F1423*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*F1423+0.4357405005*F1423+0.0330936548*F1423+0.0328406739))+F1425*('Segments'!$D$28*F1423*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*F1423+0.4357405005*F1423+0.0330936548*F1423+0.0328406739))+F1426*('Segments'!$D$29*F1423*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*F1423+0.4357405005*F1423+0.0330936548*F1423+0.0328406739))+F1427*('Segments'!$D$30*F1423*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*F1423+0.4357405005*F1423+0.0330936548*F1423+0.0328406739))+F1428*('Segments'!$D$31*F1423*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*F1423+0.4357405005*F1423+0.0330936548*F1423+0.0328406739))+F1429*('Segments'!$D$32*F1423*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*F1423+0.4357405005*F1423+0.0330936548*F1423+0.0328406739))+F1430*('Segments'!$D$33*F1423*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*F1423+0.4357405005*F1423+0.0330936548*F1423+0.0328406739))+F1431*('Segments'!$D$34*F1423*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*F1423+0.4357405005*F1423+0.0330936548*F1423+0.0328406739))</f>
         <v/>
       </c>
       <c r="G1434" s="18">
-        <f>G1424*('Segments'!$D$27*G1423*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*G1422+0.4357405005*G1422+0.0330936548*G1423+0.0328406739))+G1425*('Segments'!$D$28*G1423*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*G1422+0.4357405005*G1422+0.0330936548*G1423+0.0328406739))+G1426*('Segments'!$D$29*G1423*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*G1422+0.4357405005*G1422+0.0330936548*G1423+0.0328406739))+G1427*('Segments'!$D$30*G1423*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*G1422+0.4357405005*G1422+0.0330936548*G1423+0.0328406739))+G1428*('Segments'!$D$31*G1423*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*G1422+0.4357405005*G1422+0.0330936548*G1423+0.0328406739))+G1429*('Segments'!$D$32*G1423*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*G1422+0.4357405005*G1422+0.0330936548*G1423+0.0328406739))+G1430*('Segments'!$D$33*G1423*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*G1422+0.4357405005*G1422+0.0330936548*G1423+0.0328406739))+G1431*('Segments'!$D$34*G1423*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*G1422+0.4357405005*G1422+0.0330936548*G1423+0.0328406739))</f>
+        <f>G1424*('Segments'!$D$27*G1423*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*G1423+0.4357405005*G1423+0.0330936548*G1423+0.0328406739))+G1425*('Segments'!$D$28*G1423*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*G1423+0.4357405005*G1423+0.0330936548*G1423+0.0328406739))+G1426*('Segments'!$D$29*G1423*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*G1423+0.4357405005*G1423+0.0330936548*G1423+0.0328406739))+G1427*('Segments'!$D$30*G1423*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*G1423+0.4357405005*G1423+0.0330936548*G1423+0.0328406739))+G1428*('Segments'!$D$31*G1423*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*G1423+0.4357405005*G1423+0.0330936548*G1423+0.0328406739))+G1429*('Segments'!$D$32*G1423*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*G1423+0.4357405005*G1423+0.0330936548*G1423+0.0328406739))+G1430*('Segments'!$D$33*G1423*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*G1423+0.4357405005*G1423+0.0330936548*G1423+0.0328406739))+G1431*('Segments'!$D$34*G1423*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*G1423+0.4357405005*G1423+0.0330936548*G1423+0.0328406739))</f>
         <v/>
       </c>
     </row>
@@ -34416,23 +34416,23 @@
         </is>
       </c>
       <c r="C1483" s="18">
-        <f>C1473*('Segments'!$D$27*C1472*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*C1471+0.4357405005*C1471+0.0330936548*C1472+0.0328406739))+C1474*('Segments'!$D$28*C1472*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*C1471+0.4357405005*C1471+0.0330936548*C1472+0.0328406739))+C1475*('Segments'!$D$29*C1472*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*C1471+0.4357405005*C1471+0.0330936548*C1472+0.0328406739))+C1476*('Segments'!$D$30*C1472*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*C1471+0.4357405005*C1471+0.0330936548*C1472+0.0328406739))+C1477*('Segments'!$D$31*C1472*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*C1471+0.4357405005*C1471+0.0330936548*C1472+0.0328406739))+C1478*('Segments'!$D$32*C1472*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*C1471+0.4357405005*C1471+0.0330936548*C1472+0.0328406739))+C1479*('Segments'!$D$33*C1472*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*C1471+0.4357405005*C1471+0.0330936548*C1472+0.0328406739))+C1480*('Segments'!$D$34*C1472*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*C1471+0.4357405005*C1471+0.0330936548*C1472+0.0328406739))</f>
+        <f>C1473*('Segments'!$D$27*C1472*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*C1472+0.4357405005*C1472+0.0330936548*C1472+0.0328406739))+C1474*('Segments'!$D$28*C1472*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*C1472+0.4357405005*C1472+0.0330936548*C1472+0.0328406739))+C1475*('Segments'!$D$29*C1472*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*C1472+0.4357405005*C1472+0.0330936548*C1472+0.0328406739))+C1476*('Segments'!$D$30*C1472*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*C1472+0.4357405005*C1472+0.0330936548*C1472+0.0328406739))+C1477*('Segments'!$D$31*C1472*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*C1472+0.4357405005*C1472+0.0330936548*C1472+0.0328406739))+C1478*('Segments'!$D$32*C1472*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*C1472+0.4357405005*C1472+0.0330936548*C1472+0.0328406739))+C1479*('Segments'!$D$33*C1472*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*C1472+0.4357405005*C1472+0.0330936548*C1472+0.0328406739))+C1480*('Segments'!$D$34*C1472*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*C1472+0.4357405005*C1472+0.0330936548*C1472+0.0328406739))</f>
         <v/>
       </c>
       <c r="D1483" s="18">
-        <f>D1473*('Segments'!$D$27*D1472*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*D1471+0.4357405005*D1471+0.0330936548*D1472+0.0328406739))+D1474*('Segments'!$D$28*D1472*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*D1471+0.4357405005*D1471+0.0330936548*D1472+0.0328406739))+D1475*('Segments'!$D$29*D1472*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*D1471+0.4357405005*D1471+0.0330936548*D1472+0.0328406739))+D1476*('Segments'!$D$30*D1472*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*D1471+0.4357405005*D1471+0.0330936548*D1472+0.0328406739))+D1477*('Segments'!$D$31*D1472*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*D1471+0.4357405005*D1471+0.0330936548*D1472+0.0328406739))+D1478*('Segments'!$D$32*D1472*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*D1471+0.4357405005*D1471+0.0330936548*D1472+0.0328406739))+D1479*('Segments'!$D$33*D1472*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*D1471+0.4357405005*D1471+0.0330936548*D1472+0.0328406739))+D1480*('Segments'!$D$34*D1472*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*D1471+0.4357405005*D1471+0.0330936548*D1472+0.0328406739))</f>
+        <f>D1473*('Segments'!$D$27*D1472*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*D1472+0.4357405005*D1472+0.0330936548*D1472+0.0328406739))+D1474*('Segments'!$D$28*D1472*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*D1472+0.4357405005*D1472+0.0330936548*D1472+0.0328406739))+D1475*('Segments'!$D$29*D1472*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*D1472+0.4357405005*D1472+0.0330936548*D1472+0.0328406739))+D1476*('Segments'!$D$30*D1472*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*D1472+0.4357405005*D1472+0.0330936548*D1472+0.0328406739))+D1477*('Segments'!$D$31*D1472*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*D1472+0.4357405005*D1472+0.0330936548*D1472+0.0328406739))+D1478*('Segments'!$D$32*D1472*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*D1472+0.4357405005*D1472+0.0330936548*D1472+0.0328406739))+D1479*('Segments'!$D$33*D1472*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*D1472+0.4357405005*D1472+0.0330936548*D1472+0.0328406739))+D1480*('Segments'!$D$34*D1472*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*D1472+0.4357405005*D1472+0.0330936548*D1472+0.0328406739))</f>
         <v/>
       </c>
       <c r="E1483" s="18">
-        <f>E1473*('Segments'!$D$27*E1472*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*E1471+0.4357405005*E1471+0.0330936548*E1472+0.0328406739))+E1474*('Segments'!$D$28*E1472*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*E1471+0.4357405005*E1471+0.0330936548*E1472+0.0328406739))+E1475*('Segments'!$D$29*E1472*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*E1471+0.4357405005*E1471+0.0330936548*E1472+0.0328406739))+E1476*('Segments'!$D$30*E1472*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*E1471+0.4357405005*E1471+0.0330936548*E1472+0.0328406739))+E1477*('Segments'!$D$31*E1472*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*E1471+0.4357405005*E1471+0.0330936548*E1472+0.0328406739))+E1478*('Segments'!$D$32*E1472*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*E1471+0.4357405005*E1471+0.0330936548*E1472+0.0328406739))+E1479*('Segments'!$D$33*E1472*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*E1471+0.4357405005*E1471+0.0330936548*E1472+0.0328406739))+E1480*('Segments'!$D$34*E1472*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*E1471+0.4357405005*E1471+0.0330936548*E1472+0.0328406739))</f>
+        <f>E1473*('Segments'!$D$27*E1472*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*E1472+0.4357405005*E1472+0.0330936548*E1472+0.0328406739))+E1474*('Segments'!$D$28*E1472*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*E1472+0.4357405005*E1472+0.0330936548*E1472+0.0328406739))+E1475*('Segments'!$D$29*E1472*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*E1472+0.4357405005*E1472+0.0330936548*E1472+0.0328406739))+E1476*('Segments'!$D$30*E1472*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*E1472+0.4357405005*E1472+0.0330936548*E1472+0.0328406739))+E1477*('Segments'!$D$31*E1472*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*E1472+0.4357405005*E1472+0.0330936548*E1472+0.0328406739))+E1478*('Segments'!$D$32*E1472*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*E1472+0.4357405005*E1472+0.0330936548*E1472+0.0328406739))+E1479*('Segments'!$D$33*E1472*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*E1472+0.4357405005*E1472+0.0330936548*E1472+0.0328406739))+E1480*('Segments'!$D$34*E1472*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*E1472+0.4357405005*E1472+0.0330936548*E1472+0.0328406739))</f>
         <v/>
       </c>
       <c r="F1483" s="18">
-        <f>F1473*('Segments'!$D$27*F1472*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*F1471+0.4357405005*F1471+0.0330936548*F1472+0.0328406739))+F1474*('Segments'!$D$28*F1472*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*F1471+0.4357405005*F1471+0.0330936548*F1472+0.0328406739))+F1475*('Segments'!$D$29*F1472*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*F1471+0.4357405005*F1471+0.0330936548*F1472+0.0328406739))+F1476*('Segments'!$D$30*F1472*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*F1471+0.4357405005*F1471+0.0330936548*F1472+0.0328406739))+F1477*('Segments'!$D$31*F1472*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*F1471+0.4357405005*F1471+0.0330936548*F1472+0.0328406739))+F1478*('Segments'!$D$32*F1472*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*F1471+0.4357405005*F1471+0.0330936548*F1472+0.0328406739))+F1479*('Segments'!$D$33*F1472*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*F1471+0.4357405005*F1471+0.0330936548*F1472+0.0328406739))+F1480*('Segments'!$D$34*F1472*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*F1471+0.4357405005*F1471+0.0330936548*F1472+0.0328406739))</f>
+        <f>F1473*('Segments'!$D$27*F1472*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*F1472+0.4357405005*F1472+0.0330936548*F1472+0.0328406739))+F1474*('Segments'!$D$28*F1472*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*F1472+0.4357405005*F1472+0.0330936548*F1472+0.0328406739))+F1475*('Segments'!$D$29*F1472*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*F1472+0.4357405005*F1472+0.0330936548*F1472+0.0328406739))+F1476*('Segments'!$D$30*F1472*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*F1472+0.4357405005*F1472+0.0330936548*F1472+0.0328406739))+F1477*('Segments'!$D$31*F1472*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*F1472+0.4357405005*F1472+0.0330936548*F1472+0.0328406739))+F1478*('Segments'!$D$32*F1472*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*F1472+0.4357405005*F1472+0.0330936548*F1472+0.0328406739))+F1479*('Segments'!$D$33*F1472*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*F1472+0.4357405005*F1472+0.0330936548*F1472+0.0328406739))+F1480*('Segments'!$D$34*F1472*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*F1472+0.4357405005*F1472+0.0330936548*F1472+0.0328406739))</f>
         <v/>
       </c>
       <c r="G1483" s="18">
-        <f>G1473*('Segments'!$D$27*G1472*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*G1471+0.4357405005*G1471+0.0330936548*G1472+0.0328406739))+G1474*('Segments'!$D$28*G1472*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*G1471+0.4357405005*G1471+0.0330936548*G1472+0.0328406739))+G1475*('Segments'!$D$29*G1472*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*G1471+0.4357405005*G1471+0.0330936548*G1472+0.0328406739))+G1476*('Segments'!$D$30*G1472*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*G1471+0.4357405005*G1471+0.0330936548*G1472+0.0328406739))+G1477*('Segments'!$D$31*G1472*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*G1471+0.4357405005*G1471+0.0330936548*G1472+0.0328406739))+G1478*('Segments'!$D$32*G1472*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*G1471+0.4357405005*G1471+0.0330936548*G1472+0.0328406739))+G1479*('Segments'!$D$33*G1472*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*G1471+0.4357405005*G1471+0.0330936548*G1472+0.0328406739))+G1480*('Segments'!$D$34*G1472*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*G1471+0.4357405005*G1471+0.0330936548*G1472+0.0328406739))</f>
+        <f>G1473*('Segments'!$D$27*G1472*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*G1472+0.4357405005*G1472+0.0330936548*G1472+0.0328406739))+G1474*('Segments'!$D$28*G1472*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*G1472+0.4357405005*G1472+0.0330936548*G1472+0.0328406739))+G1475*('Segments'!$D$29*G1472*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*G1472+0.4357405005*G1472+0.0330936548*G1472+0.0328406739))+G1476*('Segments'!$D$30*G1472*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*G1472+0.4357405005*G1472+0.0330936548*G1472+0.0328406739))+G1477*('Segments'!$D$31*G1472*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*G1472+0.4357405005*G1472+0.0330936548*G1472+0.0328406739))+G1478*('Segments'!$D$32*G1472*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*G1472+0.4357405005*G1472+0.0330936548*G1472+0.0328406739))+G1479*('Segments'!$D$33*G1472*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*G1472+0.4357405005*G1472+0.0330936548*G1472+0.0328406739))+G1480*('Segments'!$D$34*G1472*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*G1472+0.4357405005*G1472+0.0330936548*G1472+0.0328406739))</f>
         <v/>
       </c>
     </row>
@@ -35772,14 +35772,14 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>4.928361540677973</v>
+        <v>1.587928101520202</v>
       </c>
       <c r="C6" s="9">
         <f>'Fundamental Valuation'!B10</f>
         <v/>
       </c>
       <c r="D6" s="8" t="n">
-        <v>16.72528396749479</v>
+        <v>24.97497139340252</v>
       </c>
       <c r="E6" s="10">
         <f>Assumptions!$B$189</f>
@@ -35793,14 +35793,14 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>6.675266886949602</v>
+        <v>9.877494674318957</v>
       </c>
       <c r="C7" s="9">
         <f>'Fundamental Valuation'!C11</f>
         <v/>
       </c>
       <c r="D7" s="8" t="n">
-        <v>9.962851231670475</v>
+        <v>15.29989754395273</v>
       </c>
       <c r="E7" s="10">
         <f>Assumptions!$B$190</f>
@@ -35814,14 +35814,14 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>6.511981053437262</v>
+        <v>7.123993899224735</v>
       </c>
       <c r="C8" s="9">
         <f>'Fundamental Valuation'!D12</f>
         <v/>
       </c>
       <c r="D8" s="8" t="n">
-        <v>10.26453842563406</v>
+        <v>11.32165152290333</v>
       </c>
       <c r="E8" s="10">
         <f>Assumptions!$B$191</f>
@@ -36293,14 +36293,14 @@
       <c r="E6" s="13" t="n"/>
       <c r="F6" s="13" t="n"/>
     </row>
-    <row r="7" ht="14" customHeight="1">
+    <row r="7" ht="20" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Spot price, EGP</t>
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>9.1</v>
+        <v>13.5</v>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
@@ -36309,12 +36309,12 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>AMOC closing price on the Egyptian Exchange, 6 August 2026</t>
+          <t>AMOC closing price on the Egyptian Exchange, 3 September 2026, from the prices supplied by the principal and committed at engine/prices/SUPPLIED_03-09-2026.json</t>
         </is>
       </c>
     </row>
@@ -42862,23 +42862,23 @@
         </is>
       </c>
       <c r="C32" s="18">
-        <f>C22*('Segments'!$D$27*C21*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*C20+0.4357405005*C20+0.0330936548*C21+0.0328406739))+C23*('Segments'!$D$28*C21*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*C20+0.4357405005*C20+0.0330936548*C21+0.0328406739))+C24*('Segments'!$D$29*C21*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*C20+0.4357405005*C20+0.0330936548*C21+0.0328406739))+C25*('Segments'!$D$30*C21*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*C20+0.4357405005*C20+0.0330936548*C21+0.0328406739))+C26*('Segments'!$D$31*C21*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*C20+0.4357405005*C20+0.0330936548*C21+0.0328406739))+C27*('Segments'!$D$32*C21*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*C20+0.4357405005*C20+0.0330936548*C21+0.0328406739))+C28*('Segments'!$D$33*C21*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*C20+0.4357405005*C20+0.0330936548*C21+0.0328406739))+C29*('Segments'!$D$34*C21*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*C20+0.4357405005*C20+0.0330936548*C21+0.0328406739))</f>
+        <f>C22*('Segments'!$D$27*C21*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*C21+0.4357405005*C21+0.0330936548*C21+0.0328406739))+C23*('Segments'!$D$28*C21*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*C21+0.4357405005*C21+0.0330936548*C21+0.0328406739))+C24*('Segments'!$D$29*C21*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*C21+0.4357405005*C21+0.0330936548*C21+0.0328406739))+C25*('Segments'!$D$30*C21*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*C21+0.4357405005*C21+0.0330936548*C21+0.0328406739))+C26*('Segments'!$D$31*C21*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*C21+0.4357405005*C21+0.0330936548*C21+0.0328406739))+C27*('Segments'!$D$32*C21*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*C21+0.4357405005*C21+0.0330936548*C21+0.0328406739))+C28*('Segments'!$D$33*C21*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*C21+0.4357405005*C21+0.0330936548*C21+0.0328406739))+C29*('Segments'!$D$34*C21*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*C21+0.4357405005*C21+0.0330936548*C21+0.0328406739))</f>
         <v/>
       </c>
       <c r="D32" s="18">
-        <f>D22*('Segments'!$D$27*D21*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*D20+0.4357405005*D20+0.0330936548*D21+0.0328406739))+D23*('Segments'!$D$28*D21*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*D20+0.4357405005*D20+0.0330936548*D21+0.0328406739))+D24*('Segments'!$D$29*D21*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*D20+0.4357405005*D20+0.0330936548*D21+0.0328406739))+D25*('Segments'!$D$30*D21*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*D20+0.4357405005*D20+0.0330936548*D21+0.0328406739))+D26*('Segments'!$D$31*D21*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*D20+0.4357405005*D20+0.0330936548*D21+0.0328406739))+D27*('Segments'!$D$32*D21*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*D20+0.4357405005*D20+0.0330936548*D21+0.0328406739))+D28*('Segments'!$D$33*D21*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*D20+0.4357405005*D20+0.0330936548*D21+0.0328406739))+D29*('Segments'!$D$34*D21*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*D20+0.4357405005*D20+0.0330936548*D21+0.0328406739))</f>
+        <f>D22*('Segments'!$D$27*D21*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*D21+0.4357405005*D21+0.0330936548*D21+0.0328406739))+D23*('Segments'!$D$28*D21*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*D21+0.4357405005*D21+0.0330936548*D21+0.0328406739))+D24*('Segments'!$D$29*D21*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*D21+0.4357405005*D21+0.0330936548*D21+0.0328406739))+D25*('Segments'!$D$30*D21*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*D21+0.4357405005*D21+0.0330936548*D21+0.0328406739))+D26*('Segments'!$D$31*D21*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*D21+0.4357405005*D21+0.0330936548*D21+0.0328406739))+D27*('Segments'!$D$32*D21*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*D21+0.4357405005*D21+0.0330936548*D21+0.0328406739))+D28*('Segments'!$D$33*D21*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*D21+0.4357405005*D21+0.0330936548*D21+0.0328406739))+D29*('Segments'!$D$34*D21*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*D21+0.4357405005*D21+0.0330936548*D21+0.0328406739))</f>
         <v/>
       </c>
       <c r="E32" s="18">
-        <f>E22*('Segments'!$D$27*E21*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*E20+0.4357405005*E20+0.0330936548*E21+0.0328406739))+E23*('Segments'!$D$28*E21*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*E20+0.4357405005*E20+0.0330936548*E21+0.0328406739))+E24*('Segments'!$D$29*E21*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*E20+0.4357405005*E20+0.0330936548*E21+0.0328406739))+E25*('Segments'!$D$30*E21*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*E20+0.4357405005*E20+0.0330936548*E21+0.0328406739))+E26*('Segments'!$D$31*E21*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*E20+0.4357405005*E20+0.0330936548*E21+0.0328406739))+E27*('Segments'!$D$32*E21*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*E20+0.4357405005*E20+0.0330936548*E21+0.0328406739))+E28*('Segments'!$D$33*E21*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*E20+0.4357405005*E20+0.0330936548*E21+0.0328406739))+E29*('Segments'!$D$34*E21*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*E20+0.4357405005*E20+0.0330936548*E21+0.0328406739))</f>
+        <f>E22*('Segments'!$D$27*E21*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*E21+0.4357405005*E21+0.0330936548*E21+0.0328406739))+E23*('Segments'!$D$28*E21*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*E21+0.4357405005*E21+0.0330936548*E21+0.0328406739))+E24*('Segments'!$D$29*E21*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*E21+0.4357405005*E21+0.0330936548*E21+0.0328406739))+E25*('Segments'!$D$30*E21*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*E21+0.4357405005*E21+0.0330936548*E21+0.0328406739))+E26*('Segments'!$D$31*E21*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*E21+0.4357405005*E21+0.0330936548*E21+0.0328406739))+E27*('Segments'!$D$32*E21*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*E21+0.4357405005*E21+0.0330936548*E21+0.0328406739))+E28*('Segments'!$D$33*E21*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*E21+0.4357405005*E21+0.0330936548*E21+0.0328406739))+E29*('Segments'!$D$34*E21*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*E21+0.4357405005*E21+0.0330936548*E21+0.0328406739))</f>
         <v/>
       </c>
       <c r="F32" s="18">
-        <f>F22*('Segments'!$D$27*F21*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*F20+0.4357405005*F20+0.0330936548*F21+0.0328406739))+F23*('Segments'!$D$28*F21*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*F20+0.4357405005*F20+0.0330936548*F21+0.0328406739))+F24*('Segments'!$D$29*F21*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*F20+0.4357405005*F20+0.0330936548*F21+0.0328406739))+F25*('Segments'!$D$30*F21*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*F20+0.4357405005*F20+0.0330936548*F21+0.0328406739))+F26*('Segments'!$D$31*F21*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*F20+0.4357405005*F20+0.0330936548*F21+0.0328406739))+F27*('Segments'!$D$32*F21*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*F20+0.4357405005*F20+0.0330936548*F21+0.0328406739))+F28*('Segments'!$D$33*F21*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*F20+0.4357405005*F20+0.0330936548*F21+0.0328406739))+F29*('Segments'!$D$34*F21*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*F20+0.4357405005*F20+0.0330936548*F21+0.0328406739))</f>
+        <f>F22*('Segments'!$D$27*F21*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*F21+0.4357405005*F21+0.0330936548*F21+0.0328406739))+F23*('Segments'!$D$28*F21*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*F21+0.4357405005*F21+0.0330936548*F21+0.0328406739))+F24*('Segments'!$D$29*F21*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*F21+0.4357405005*F21+0.0330936548*F21+0.0328406739))+F25*('Segments'!$D$30*F21*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*F21+0.4357405005*F21+0.0330936548*F21+0.0328406739))+F26*('Segments'!$D$31*F21*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*F21+0.4357405005*F21+0.0330936548*F21+0.0328406739))+F27*('Segments'!$D$32*F21*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*F21+0.4357405005*F21+0.0330936548*F21+0.0328406739))+F28*('Segments'!$D$33*F21*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*F21+0.4357405005*F21+0.0330936548*F21+0.0328406739))+F29*('Segments'!$D$34*F21*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*F21+0.4357405005*F21+0.0330936548*F21+0.0328406739))</f>
         <v/>
       </c>
       <c r="G32" s="18">
-        <f>G22*('Segments'!$D$27*G21*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*G20+0.4357405005*G20+0.0330936548*G21+0.0328406739))+G23*('Segments'!$D$28*G21*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*G20+0.4357405005*G20+0.0330936548*G21+0.0328406739))+G24*('Segments'!$D$29*G21*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*G20+0.4357405005*G20+0.0330936548*G21+0.0328406739))+G25*('Segments'!$D$30*G21*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*G20+0.4357405005*G20+0.0330936548*G21+0.0328406739))+G26*('Segments'!$D$31*G21*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*G20+0.4357405005*G20+0.0330936548*G21+0.0328406739))+G27*('Segments'!$D$32*G21*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*G20+0.4357405005*G20+0.0330936548*G21+0.0328406739))+G28*('Segments'!$D$33*G21*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*G20+0.4357405005*G20+0.0330936548*G21+0.0328406739))+G29*('Segments'!$D$34*G21*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*G20+0.4357405005*G20+0.0330936548*G21+0.0328406739))</f>
+        <f>G22*('Segments'!$D$27*G21*Assumptions!$B$109+'Segments'!$B$27*(0.4983251709*G21+0.4357405005*G21+0.0330936548*G21+0.0328406739))+G23*('Segments'!$D$28*G21*Assumptions!$B$109+'Segments'!$B$28*(0.4983251709*G21+0.4357405005*G21+0.0330936548*G21+0.0328406739))+G24*('Segments'!$D$29*G21*Assumptions!$B$109+'Segments'!$B$29*(0.4983251709*G21+0.4357405005*G21+0.0330936548*G21+0.0328406739))+G25*('Segments'!$D$30*G21*Assumptions!$B$109+'Segments'!$B$30*(0.4983251709*G21+0.4357405005*G21+0.0330936548*G21+0.0328406739))+G26*('Segments'!$D$31*G21*Assumptions!$B$109+'Segments'!$B$31*(0.4983251709*G21+0.4357405005*G21+0.0330936548*G21+0.0328406739))+G27*('Segments'!$D$32*G21*Assumptions!$B$109+'Segments'!$B$32*(0.4983251709*G21+0.4357405005*G21+0.0330936548*G21+0.0328406739))+G28*('Segments'!$D$33*G21*Assumptions!$B$109+'Segments'!$B$33*(0.4983251709*G21+0.4357405005*G21+0.0330936548*G21+0.0328406739))+G29*('Segments'!$D$34*G21*Assumptions!$B$109+'Segments'!$B$34*(0.4983251709*G21+0.4357405005*G21+0.0330936548*G21+0.0328406739))</f>
         <v/>
       </c>
     </row>

--- a/engine/amoc_study/AMOC_Valuation_Model_03092026_public.xlsx
+++ b/engine/amoc_study/AMOC_Valuation_Model_03092026_public.xlsx
@@ -36293,7 +36293,7 @@
       <c r="E6" s="13" t="n"/>
       <c r="F6" s="13" t="n"/>
     </row>
-    <row r="7" ht="20" customHeight="1">
+    <row r="7" ht="14" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Spot price, EGP</t>
@@ -36314,7 +36314,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>AMOC closing price on the Egyptian Exchange, 3 September 2026, from the prices supplied by the principal and committed at engine/prices/SUPPLIED_03-09-2026.json</t>
+          <t>AMOC closing price on the Egyptian Exchange, 3 September 2026</t>
         </is>
       </c>
     </row>

--- a/engine/amoc_study/AMOC_Valuation_Model_03092026_public.xlsx
+++ b/engine/amoc_study/AMOC_Valuation_Model_03092026_public.xlsx
@@ -35772,14 +35772,14 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>1.587928101520202</v>
+        <v>1.673203365046849</v>
       </c>
       <c r="C6" s="9">
         <f>'Fundamental Valuation'!B10</f>
         <v/>
       </c>
       <c r="D6" s="8" t="n">
-        <v>24.97497139340252</v>
+        <v>23.90485159462365</v>
       </c>
       <c r="E6" s="10">
         <f>Assumptions!$B$189</f>
@@ -35814,14 +35814,14 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>7.123993899224735</v>
+        <v>7.007467250043815</v>
       </c>
       <c r="C8" s="9">
         <f>'Fundamental Valuation'!D12</f>
         <v/>
       </c>
       <c r="D8" s="8" t="n">
-        <v>11.32165152290333</v>
+        <v>11.12037821977265</v>
       </c>
       <c r="E8" s="10">
         <f>Assumptions!$B$191</f>
@@ -39110,7 +39110,7 @@
         </is>
       </c>
       <c r="B122" s="29" t="n">
-        <v>0.117073</v>
+        <v>0.131707</v>
       </c>
       <c r="C122" s="7" t="inlineStr">
         <is>
@@ -39135,7 +39135,7 @@
         </is>
       </c>
       <c r="B123" s="29" t="n">
-        <v>0.102439</v>
+        <v>0.092683</v>
       </c>
       <c r="C123" s="7" t="inlineStr">
         <is>
@@ -39160,7 +39160,7 @@
         </is>
       </c>
       <c r="B124" s="29" t="n">
-        <v>0.08780499999999999</v>
+        <v>0.063415</v>
       </c>
       <c r="C124" s="7" t="inlineStr">
         <is>
@@ -39185,7 +39185,7 @@
         </is>
       </c>
       <c r="B125" s="29" t="n">
-        <v>0.073171</v>
+        <v>0.04878</v>
       </c>
       <c r="C125" s="7" t="inlineStr">
         <is>
@@ -39210,7 +39210,7 @@
         </is>
       </c>
       <c r="B126" s="29" t="n">
-        <v>0.06829300000000001</v>
+        <v>0.043902</v>
       </c>
       <c r="C126" s="7" t="inlineStr">
         <is>
@@ -40228,14 +40228,14 @@
         </is>
       </c>
     </row>
-    <row r="167" ht="30" customHeight="1">
+    <row r="167" ht="70" customHeight="1">
       <c r="A167" s="7" t="inlineStr">
         <is>
           <t>Egyptian inflation factor, 2026E</t>
         </is>
       </c>
       <c r="B167" s="28" t="n">
-        <v>1.145</v>
+        <v>1.16</v>
       </c>
       <c r="C167" s="7" t="inlineStr">
         <is>
@@ -40244,23 +40244,23 @@
       </c>
       <c r="D167" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="E167" s="4" t="inlineStr">
         <is>
-          <t>Cumulative-year Egyptian inflation factors applied to the pound-denominated cost legs — salaries inside cost of sales, the other line, administrative and marketing expense, and capital expenditure. Historical years as printed, easing toward the central bank's published target thereafter</t>
-        </is>
-      </c>
-    </row>
-    <row r="168" ht="30" customHeight="1">
+          <t>Cumulative-year Egyptian inflation factors applied to the pound-denominated cost legs — salaries inside cost of sales, the other line, administrative and marketing expense, and capital expenditure. The three HISTORICAL years are as printed. The five FORECAST years are the single Egyptian inflation path this series uses for every Egyptian company it values, read from that path rather than set for this study: no valuation here sets an inflation rate of its own, because a company cannot be valued in an economy the study beside it does not recognise. The path is the central bank's published disinflation ladder, and the years between published points are labelled as interpolated where they are</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="70" customHeight="1">
       <c r="A168" s="7" t="inlineStr">
         <is>
           <t>Egyptian inflation factor, 2027E</t>
         </is>
       </c>
       <c r="B168" s="28" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="C168" s="7" t="inlineStr">
         <is>
@@ -40269,23 +40269,23 @@
       </c>
       <c r="D168" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="E168" s="4" t="inlineStr">
         <is>
-          <t>Cumulative-year Egyptian inflation factors applied to the pound-denominated cost legs — salaries inside cost of sales, the other line, administrative and marketing expense, and capital expenditure. Historical years as printed, easing toward the central bank's published target thereafter</t>
-        </is>
-      </c>
-    </row>
-    <row r="169" ht="30" customHeight="1">
+          <t>Cumulative-year Egyptian inflation factors applied to the pound-denominated cost legs — salaries inside cost of sales, the other line, administrative and marketing expense, and capital expenditure. The three HISTORICAL years are as printed. The five FORECAST years are the single Egyptian inflation path this series uses for every Egyptian company it values, read from that path rather than set for this study: no valuation here sets an inflation rate of its own, because a company cannot be valued in an economy the study beside it does not recognise. The path is the central bank's published disinflation ladder, and the years between published points are labelled as interpolated where they are</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="70" customHeight="1">
       <c r="A169" s="7" t="inlineStr">
         <is>
           <t>Egyptian inflation factor, 2028E</t>
         </is>
       </c>
       <c r="B169" s="28" t="n">
-        <v>1.115</v>
+        <v>1.09</v>
       </c>
       <c r="C169" s="7" t="inlineStr">
         <is>
@@ -40294,23 +40294,23 @@
       </c>
       <c r="D169" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="E169" s="4" t="inlineStr">
         <is>
-          <t>Cumulative-year Egyptian inflation factors applied to the pound-denominated cost legs — salaries inside cost of sales, the other line, administrative and marketing expense, and capital expenditure. Historical years as printed, easing toward the central bank's published target thereafter</t>
-        </is>
-      </c>
-    </row>
-    <row r="170" ht="30" customHeight="1">
+          <t>Cumulative-year Egyptian inflation factors applied to the pound-denominated cost legs — salaries inside cost of sales, the other line, administrative and marketing expense, and capital expenditure. The three HISTORICAL years are as printed. The five FORECAST years are the single Egyptian inflation path this series uses for every Egyptian company it values, read from that path rather than set for this study: no valuation here sets an inflation rate of its own, because a company cannot be valued in an economy the study beside it does not recognise. The path is the central bank's published disinflation ladder, and the years between published points are labelled as interpolated where they are</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="70" customHeight="1">
       <c r="A170" s="7" t="inlineStr">
         <is>
           <t>Egyptian inflation factor, 2029E</t>
         </is>
       </c>
       <c r="B170" s="28" t="n">
-        <v>1.1</v>
+        <v>1.075</v>
       </c>
       <c r="C170" s="7" t="inlineStr">
         <is>
@@ -40319,23 +40319,23 @@
       </c>
       <c r="D170" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="E170" s="4" t="inlineStr">
         <is>
-          <t>Cumulative-year Egyptian inflation factors applied to the pound-denominated cost legs — salaries inside cost of sales, the other line, administrative and marketing expense, and capital expenditure. Historical years as printed, easing toward the central bank's published target thereafter</t>
-        </is>
-      </c>
-    </row>
-    <row r="171" ht="30" customHeight="1">
+          <t>Cumulative-year Egyptian inflation factors applied to the pound-denominated cost legs — salaries inside cost of sales, the other line, administrative and marketing expense, and capital expenditure. The three HISTORICAL years are as printed. The five FORECAST years are the single Egyptian inflation path this series uses for every Egyptian company it values, read from that path rather than set for this study: no valuation here sets an inflation rate of its own, because a company cannot be valued in an economy the study beside it does not recognise. The path is the central bank's published disinflation ladder, and the years between published points are labelled as interpolated where they are</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="70" customHeight="1">
       <c r="A171" s="7" t="inlineStr">
         <is>
           <t>Egyptian inflation factor, 2030E</t>
         </is>
       </c>
       <c r="B171" s="28" t="n">
-        <v>1.095</v>
+        <v>1.07</v>
       </c>
       <c r="C171" s="7" t="inlineStr">
         <is>
@@ -40344,12 +40344,12 @@
       </c>
       <c r="D171" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="E171" s="4" t="inlineStr">
         <is>
-          <t>Cumulative-year Egyptian inflation factors applied to the pound-denominated cost legs — salaries inside cost of sales, the other line, administrative and marketing expense, and capital expenditure. Historical years as printed, easing toward the central bank's published target thereafter</t>
+          <t>Cumulative-year Egyptian inflation factors applied to the pound-denominated cost legs — salaries inside cost of sales, the other line, administrative and marketing expense, and capital expenditure. The three HISTORICAL years are as printed. The five FORECAST years are the single Egyptian inflation path this series uses for every Egyptian company it values, read from that path rather than set for this study: no valuation here sets an inflation rate of its own, because a company cannot be valued in an economy the study beside it does not recognise. The path is the central bank's published disinflation ladder, and the years between published points are labelled as interpolated where they are</t>
         </is>
       </c>
     </row>

--- a/engine/amoc_study/AMOC_Valuation_Model_03092026_public.xlsx
+++ b/engine/amoc_study/AMOC_Valuation_Model_03092026_public.xlsx
@@ -2786,14 +2786,14 @@
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   grid point 3: 0.9080</t>
+          <t xml:space="preserve">   grid point 3: 0.9063</t>
         </is>
       </c>
       <c r="F29" s="29" t="n">
-        <v>0.2745428</v>
+        <v>0.2743872044180305</v>
       </c>
       <c r="G29" s="29" t="n">
-        <v>0.181386185805472</v>
+        <v>0.1812820144806677</v>
       </c>
       <c r="I29" s="22">
         <f>B928</f>
@@ -21216,7 +21216,7 @@
     <row r="882">
       <c r="A882" s="6" t="inlineStr">
         <is>
-          <t>Beta — 0.9080</t>
+          <t>Beta — 0.9063</t>
         </is>
       </c>
       <c r="B882" s="6" t="inlineStr">
@@ -35772,14 +35772,14 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>1.673203365046849</v>
+        <v>1.673138100467843</v>
       </c>
       <c r="C6" s="9">
         <f>'Fundamental Valuation'!B10</f>
         <v/>
       </c>
       <c r="D6" s="8" t="n">
-        <v>23.90485159462365</v>
+        <v>23.92709520373801</v>
       </c>
       <c r="E6" s="10">
         <f>Assumptions!$B$189</f>
@@ -35814,14 +35814,14 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>7.007467250043815</v>
+        <v>9.882803105057718</v>
       </c>
       <c r="C8" s="9">
         <f>'Fundamental Valuation'!D12</f>
         <v/>
       </c>
       <c r="D8" s="8" t="n">
-        <v>11.12037821977265</v>
+        <v>16.08686742388758</v>
       </c>
       <c r="E8" s="10">
         <f>Assumptions!$B$191</f>
@@ -35835,14 +35835,14 @@
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>4.735521527125914</v>
+        <v>4.738831402909378</v>
       </c>
       <c r="C9" s="9">
         <f>'Fundamental Valuation'!E13</f>
         <v/>
       </c>
       <c r="D9" s="8" t="n">
-        <v>7.116643453998376</v>
+        <v>7.122873938825641</v>
       </c>
       <c r="E9" s="10">
         <f>Assumptions!$B$192</f>
@@ -36140,7 +36140,7 @@
         <v/>
       </c>
       <c r="C13" s="24">
-        <f>0.2285092330</f>
+        <f>0.2283705826</f>
         <v/>
       </c>
       <c r="D13" s="20">
@@ -39228,7 +39228,7 @@
         </is>
       </c>
     </row>
-    <row r="127" ht="100" customHeight="1">
+    <row r="127" ht="170" customHeight="1">
       <c r="A127" s="7" t="inlineStr">
         <is>
           <t>Volume growth — Base and special oils, 2026E</t>
@@ -39249,11 +39249,11 @@
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 (gas oil -8.3% a year, naphtha -7.4%, fuel oil -6.4%, heavy fuel oil -28.2%; only wax +1.1% and LPG +1.7% grew). FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case reverts toward the five-year mean and the lever is sensitised end to end</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="100" customHeight="1">
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="170" customHeight="1">
       <c r="A128" s="7" t="inlineStr">
         <is>
           <t>Volume growth — Base and special oils, 2027E</t>
@@ -39274,11 +39274,11 @@
       </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 (gas oil -8.3% a year, naphtha -7.4%, fuel oil -6.4%, heavy fuel oil -28.2%; only wax +1.1% and LPG +1.7% grew). FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case reverts toward the five-year mean and the lever is sensitised end to end</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="100" customHeight="1">
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="170" customHeight="1">
       <c r="A129" s="7" t="inlineStr">
         <is>
           <t>Volume growth — Base and special oils, 2028E</t>
@@ -39299,11 +39299,11 @@
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 (gas oil -8.3% a year, naphtha -7.4%, fuel oil -6.4%, heavy fuel oil -28.2%; only wax +1.1% and LPG +1.7% grew). FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case reverts toward the five-year mean and the lever is sensitised end to end</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="100" customHeight="1">
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="170" customHeight="1">
       <c r="A130" s="7" t="inlineStr">
         <is>
           <t>Volume growth — Base and special oils, 2029E</t>
@@ -39324,11 +39324,11 @@
       </c>
       <c r="E130" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 (gas oil -8.3% a year, naphtha -7.4%, fuel oil -6.4%, heavy fuel oil -28.2%; only wax +1.1% and LPG +1.7% grew). FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case reverts toward the five-year mean and the lever is sensitised end to end</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="100" customHeight="1">
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="170" customHeight="1">
       <c r="A131" s="7" t="inlineStr">
         <is>
           <t>Volume growth — Base and special oils, 2030E</t>
@@ -39349,11 +39349,11 @@
       </c>
       <c r="E131" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 (gas oil -8.3% a year, naphtha -7.4%, fuel oil -6.4%, heavy fuel oil -28.2%; only wax +1.1% and LPG +1.7% grew). FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case reverts toward the five-year mean and the lever is sensitised end to end</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="100" customHeight="1">
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="170" customHeight="1">
       <c r="A132" s="7" t="inlineStr">
         <is>
           <t>Volume growth — Paraffin wax, 2026E</t>
@@ -39374,11 +39374,11 @@
       </c>
       <c r="E132" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 (gas oil -8.3% a year, naphtha -7.4%, fuel oil -6.4%, heavy fuel oil -28.2%; only wax +1.1% and LPG +1.7% grew). FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case reverts toward the five-year mean and the lever is sensitised end to end</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="100" customHeight="1">
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="170" customHeight="1">
       <c r="A133" s="7" t="inlineStr">
         <is>
           <t>Volume growth — Paraffin wax, 2027E</t>
@@ -39399,11 +39399,11 @@
       </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 (gas oil -8.3% a year, naphtha -7.4%, fuel oil -6.4%, heavy fuel oil -28.2%; only wax +1.1% and LPG +1.7% grew). FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case reverts toward the five-year mean and the lever is sensitised end to end</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="100" customHeight="1">
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="170" customHeight="1">
       <c r="A134" s="7" t="inlineStr">
         <is>
           <t>Volume growth — Paraffin wax, 2028E</t>
@@ -39424,11 +39424,11 @@
       </c>
       <c r="E134" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 (gas oil -8.3% a year, naphtha -7.4%, fuel oil -6.4%, heavy fuel oil -28.2%; only wax +1.1% and LPG +1.7% grew). FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case reverts toward the five-year mean and the lever is sensitised end to end</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="100" customHeight="1">
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="170" customHeight="1">
       <c r="A135" s="7" t="inlineStr">
         <is>
           <t>Volume growth — Paraffin wax, 2029E</t>
@@ -39449,11 +39449,11 @@
       </c>
       <c r="E135" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 (gas oil -8.3% a year, naphtha -7.4%, fuel oil -6.4%, heavy fuel oil -28.2%; only wax +1.1% and LPG +1.7% grew). FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case reverts toward the five-year mean and the lever is sensitised end to end</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" ht="100" customHeight="1">
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="170" customHeight="1">
       <c r="A136" s="7" t="inlineStr">
         <is>
           <t>Volume growth — Paraffin wax, 2030E</t>
@@ -39474,11 +39474,11 @@
       </c>
       <c r="E136" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 (gas oil -8.3% a year, naphtha -7.4%, fuel oil -6.4%, heavy fuel oil -28.2%; only wax +1.1% and LPG +1.7% grew). FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case reverts toward the five-year mean and the lever is sensitised end to end</t>
-        </is>
-      </c>
-    </row>
-    <row r="137" ht="100" customHeight="1">
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="170" customHeight="1">
       <c r="A137" s="7" t="inlineStr">
         <is>
           <t>Volume growth — Gas oil, 2026E</t>
@@ -39499,11 +39499,11 @@
       </c>
       <c r="E137" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 (gas oil -8.3% a year, naphtha -7.4%, fuel oil -6.4%, heavy fuel oil -28.2%; only wax +1.1% and LPG +1.7% grew). FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case reverts toward the five-year mean and the lever is sensitised end to end</t>
-        </is>
-      </c>
-    </row>
-    <row r="138" ht="100" customHeight="1">
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="170" customHeight="1">
       <c r="A138" s="7" t="inlineStr">
         <is>
           <t>Volume growth — Gas oil, 2027E</t>
@@ -39524,11 +39524,11 @@
       </c>
       <c r="E138" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 (gas oil -8.3% a year, naphtha -7.4%, fuel oil -6.4%, heavy fuel oil -28.2%; only wax +1.1% and LPG +1.7% grew). FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case reverts toward the five-year mean and the lever is sensitised end to end</t>
-        </is>
-      </c>
-    </row>
-    <row r="139" ht="100" customHeight="1">
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="170" customHeight="1">
       <c r="A139" s="7" t="inlineStr">
         <is>
           <t>Volume growth — Gas oil, 2028E</t>
@@ -39549,11 +39549,11 @@
       </c>
       <c r="E139" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 (gas oil -8.3% a year, naphtha -7.4%, fuel oil -6.4%, heavy fuel oil -28.2%; only wax +1.1% and LPG +1.7% grew). FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case reverts toward the five-year mean and the lever is sensitised end to end</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="100" customHeight="1">
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="170" customHeight="1">
       <c r="A140" s="7" t="inlineStr">
         <is>
           <t>Volume growth — Gas oil, 2029E</t>
@@ -39574,11 +39574,11 @@
       </c>
       <c r="E140" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 (gas oil -8.3% a year, naphtha -7.4%, fuel oil -6.4%, heavy fuel oil -28.2%; only wax +1.1% and LPG +1.7% grew). FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case reverts toward the five-year mean and the lever is sensitised end to end</t>
-        </is>
-      </c>
-    </row>
-    <row r="141" ht="100" customHeight="1">
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="170" customHeight="1">
       <c r="A141" s="7" t="inlineStr">
         <is>
           <t>Volume growth — Gas oil, 2030E</t>
@@ -39599,11 +39599,11 @@
       </c>
       <c r="E141" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 (gas oil -8.3% a year, naphtha -7.4%, fuel oil -6.4%, heavy fuel oil -28.2%; only wax +1.1% and LPG +1.7% grew). FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case reverts toward the five-year mean and the lever is sensitised end to end</t>
-        </is>
-      </c>
-    </row>
-    <row r="142" ht="100" customHeight="1">
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="170" customHeight="1">
       <c r="A142" s="7" t="inlineStr">
         <is>
           <t>Volume growth — Naphtha, 2026E</t>
@@ -39624,11 +39624,11 @@
       </c>
       <c r="E142" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 (gas oil -8.3% a year, naphtha -7.4%, fuel oil -6.4%, heavy fuel oil -28.2%; only wax +1.1% and LPG +1.7% grew). FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case reverts toward the five-year mean and the lever is sensitised end to end</t>
-        </is>
-      </c>
-    </row>
-    <row r="143" ht="100" customHeight="1">
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="170" customHeight="1">
       <c r="A143" s="7" t="inlineStr">
         <is>
           <t>Volume growth — Naphtha, 2027E</t>
@@ -39649,11 +39649,11 @@
       </c>
       <c r="E143" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 (gas oil -8.3% a year, naphtha -7.4%, fuel oil -6.4%, heavy fuel oil -28.2%; only wax +1.1% and LPG +1.7% grew). FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case reverts toward the five-year mean and the lever is sensitised end to end</t>
-        </is>
-      </c>
-    </row>
-    <row r="144" ht="100" customHeight="1">
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="170" customHeight="1">
       <c r="A144" s="7" t="inlineStr">
         <is>
           <t>Volume growth — Naphtha, 2028E</t>
@@ -39674,11 +39674,11 @@
       </c>
       <c r="E144" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 (gas oil -8.3% a year, naphtha -7.4%, fuel oil -6.4%, heavy fuel oil -28.2%; only wax +1.1% and LPG +1.7% grew). FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case reverts toward the five-year mean and the lever is sensitised end to end</t>
-        </is>
-      </c>
-    </row>
-    <row r="145" ht="100" customHeight="1">
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="170" customHeight="1">
       <c r="A145" s="7" t="inlineStr">
         <is>
           <t>Volume growth — Naphtha, 2029E</t>
@@ -39699,11 +39699,11 @@
       </c>
       <c r="E145" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 (gas oil -8.3% a year, naphtha -7.4%, fuel oil -6.4%, heavy fuel oil -28.2%; only wax +1.1% and LPG +1.7% grew). FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case reverts toward the five-year mean and the lever is sensitised end to end</t>
-        </is>
-      </c>
-    </row>
-    <row r="146" ht="100" customHeight="1">
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="170" customHeight="1">
       <c r="A146" s="7" t="inlineStr">
         <is>
           <t>Volume growth — Naphtha, 2030E</t>
@@ -39724,11 +39724,11 @@
       </c>
       <c r="E146" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 (gas oil -8.3% a year, naphtha -7.4%, fuel oil -6.4%, heavy fuel oil -28.2%; only wax +1.1% and LPG +1.7% grew). FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case reverts toward the five-year mean and the lever is sensitised end to end</t>
-        </is>
-      </c>
-    </row>
-    <row r="147" ht="100" customHeight="1">
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="170" customHeight="1">
       <c r="A147" s="7" t="inlineStr">
         <is>
           <t>Volume growth — Liquefied petroleum gas, 2026E</t>
@@ -39749,11 +39749,11 @@
       </c>
       <c r="E147" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 (gas oil -8.3% a year, naphtha -7.4%, fuel oil -6.4%, heavy fuel oil -28.2%; only wax +1.1% and LPG +1.7% grew). FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case reverts toward the five-year mean and the lever is sensitised end to end</t>
-        </is>
-      </c>
-    </row>
-    <row r="148" ht="100" customHeight="1">
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="170" customHeight="1">
       <c r="A148" s="7" t="inlineStr">
         <is>
           <t>Volume growth — Liquefied petroleum gas, 2027E</t>
@@ -39774,11 +39774,11 @@
       </c>
       <c r="E148" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 (gas oil -8.3% a year, naphtha -7.4%, fuel oil -6.4%, heavy fuel oil -28.2%; only wax +1.1% and LPG +1.7% grew). FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case reverts toward the five-year mean and the lever is sensitised end to end</t>
-        </is>
-      </c>
-    </row>
-    <row r="149" ht="100" customHeight="1">
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="170" customHeight="1">
       <c r="A149" s="7" t="inlineStr">
         <is>
           <t>Volume growth — Liquefied petroleum gas, 2028E</t>
@@ -39799,11 +39799,11 @@
       </c>
       <c r="E149" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 (gas oil -8.3% a year, naphtha -7.4%, fuel oil -6.4%, heavy fuel oil -28.2%; only wax +1.1% and LPG +1.7% grew). FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case reverts toward the five-year mean and the lever is sensitised end to end</t>
-        </is>
-      </c>
-    </row>
-    <row r="150" ht="100" customHeight="1">
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="170" customHeight="1">
       <c r="A150" s="7" t="inlineStr">
         <is>
           <t>Volume growth — Liquefied petroleum gas, 2029E</t>
@@ -39824,11 +39824,11 @@
       </c>
       <c r="E150" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 (gas oil -8.3% a year, naphtha -7.4%, fuel oil -6.4%, heavy fuel oil -28.2%; only wax +1.1% and LPG +1.7% grew). FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case reverts toward the five-year mean and the lever is sensitised end to end</t>
-        </is>
-      </c>
-    </row>
-    <row r="151" ht="100" customHeight="1">
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="170" customHeight="1">
       <c r="A151" s="7" t="inlineStr">
         <is>
           <t>Volume growth — Liquefied petroleum gas, 2030E</t>
@@ -39849,11 +39849,11 @@
       </c>
       <c r="E151" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 (gas oil -8.3% a year, naphtha -7.4%, fuel oil -6.4%, heavy fuel oil -28.2%; only wax +1.1% and LPG +1.7% grew). FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case reverts toward the five-year mean and the lever is sensitised end to end</t>
-        </is>
-      </c>
-    </row>
-    <row r="152" ht="100" customHeight="1">
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="170" customHeight="1">
       <c r="A152" s="7" t="inlineStr">
         <is>
           <t>Volume growth — Fuel oil (mix), 2026E</t>
@@ -39874,11 +39874,11 @@
       </c>
       <c r="E152" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 (gas oil -8.3% a year, naphtha -7.4%, fuel oil -6.4%, heavy fuel oil -28.2%; only wax +1.1% and LPG +1.7% grew). FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case reverts toward the five-year mean and the lever is sensitised end to end</t>
-        </is>
-      </c>
-    </row>
-    <row r="153" ht="100" customHeight="1">
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="170" customHeight="1">
       <c r="A153" s="7" t="inlineStr">
         <is>
           <t>Volume growth — Fuel oil (mix), 2027E</t>
@@ -39899,11 +39899,11 @@
       </c>
       <c r="E153" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 (gas oil -8.3% a year, naphtha -7.4%, fuel oil -6.4%, heavy fuel oil -28.2%; only wax +1.1% and LPG +1.7% grew). FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case reverts toward the five-year mean and the lever is sensitised end to end</t>
-        </is>
-      </c>
-    </row>
-    <row r="154" ht="100" customHeight="1">
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="170" customHeight="1">
       <c r="A154" s="7" t="inlineStr">
         <is>
           <t>Volume growth — Fuel oil (mix), 2028E</t>
@@ -39924,11 +39924,11 @@
       </c>
       <c r="E154" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 (gas oil -8.3% a year, naphtha -7.4%, fuel oil -6.4%, heavy fuel oil -28.2%; only wax +1.1% and LPG +1.7% grew). FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case reverts toward the five-year mean and the lever is sensitised end to end</t>
-        </is>
-      </c>
-    </row>
-    <row r="155" ht="100" customHeight="1">
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="170" customHeight="1">
       <c r="A155" s="7" t="inlineStr">
         <is>
           <t>Volume growth — Fuel oil (mix), 2029E</t>
@@ -39949,11 +39949,11 @@
       </c>
       <c r="E155" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 (gas oil -8.3% a year, naphtha -7.4%, fuel oil -6.4%, heavy fuel oil -28.2%; only wax +1.1% and LPG +1.7% grew). FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case reverts toward the five-year mean and the lever is sensitised end to end</t>
-        </is>
-      </c>
-    </row>
-    <row r="156" ht="100" customHeight="1">
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="170" customHeight="1">
       <c r="A156" s="7" t="inlineStr">
         <is>
           <t>Volume growth — Fuel oil (mix), 2030E</t>
@@ -39974,11 +39974,11 @@
       </c>
       <c r="E156" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 (gas oil -8.3% a year, naphtha -7.4%, fuel oil -6.4%, heavy fuel oil -28.2%; only wax +1.1% and LPG +1.7% grew). FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case reverts toward the five-year mean and the lever is sensitised end to end</t>
-        </is>
-      </c>
-    </row>
-    <row r="157" ht="100" customHeight="1">
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="170" customHeight="1">
       <c r="A157" s="7" t="inlineStr">
         <is>
           <t>Volume growth — Heavy fuel oil, 2026E</t>
@@ -39999,11 +39999,11 @@
       </c>
       <c r="E157" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 (gas oil -8.3% a year, naphtha -7.4%, fuel oil -6.4%, heavy fuel oil -28.2%; only wax +1.1% and LPG +1.7% grew). FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case reverts toward the five-year mean and the lever is sensitised end to end</t>
-        </is>
-      </c>
-    </row>
-    <row r="158" ht="100" customHeight="1">
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="170" customHeight="1">
       <c r="A158" s="7" t="inlineStr">
         <is>
           <t>Volume growth — Heavy fuel oil, 2027E</t>
@@ -40024,11 +40024,11 @@
       </c>
       <c r="E158" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 (gas oil -8.3% a year, naphtha -7.4%, fuel oil -6.4%, heavy fuel oil -28.2%; only wax +1.1% and LPG +1.7% grew). FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case reverts toward the five-year mean and the lever is sensitised end to end</t>
-        </is>
-      </c>
-    </row>
-    <row r="159" ht="100" customHeight="1">
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="170" customHeight="1">
       <c r="A159" s="7" t="inlineStr">
         <is>
           <t>Volume growth — Heavy fuel oil, 2028E</t>
@@ -40049,11 +40049,11 @@
       </c>
       <c r="E159" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 (gas oil -8.3% a year, naphtha -7.4%, fuel oil -6.4%, heavy fuel oil -28.2%; only wax +1.1% and LPG +1.7% grew). FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case reverts toward the five-year mean and the lever is sensitised end to end</t>
-        </is>
-      </c>
-    </row>
-    <row r="160" ht="100" customHeight="1">
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="170" customHeight="1">
       <c r="A160" s="7" t="inlineStr">
         <is>
           <t>Volume growth — Heavy fuel oil, 2029E</t>
@@ -40074,11 +40074,11 @@
       </c>
       <c r="E160" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 (gas oil -8.3% a year, naphtha -7.4%, fuel oil -6.4%, heavy fuel oil -28.2%; only wax +1.1% and LPG +1.7% grew). FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case reverts toward the five-year mean and the lever is sensitised end to end</t>
-        </is>
-      </c>
-    </row>
-    <row r="161" ht="100" customHeight="1">
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="170" customHeight="1">
       <c r="A161" s="7" t="inlineStr">
         <is>
           <t>Volume growth — Heavy fuel oil, 2030E</t>
@@ -40099,11 +40099,11 @@
       </c>
       <c r="E161" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 (gas oil -8.3% a year, naphtha -7.4%, fuel oil -6.4%, heavy fuel oil -28.2%; only wax +1.1% and LPG +1.7% grew). FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case reverts toward the five-year mean and the lever is sensitised end to end</t>
-        </is>
-      </c>
-    </row>
-    <row r="162" ht="100" customHeight="1">
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="170" customHeight="1">
       <c r="A162" s="7" t="inlineStr">
         <is>
           <t>Volume growth — Waste, 2026E</t>
@@ -40124,11 +40124,11 @@
       </c>
       <c r="E162" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 (gas oil -8.3% a year, naphtha -7.4%, fuel oil -6.4%, heavy fuel oil -28.2%; only wax +1.1% and LPG +1.7% grew). FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case reverts toward the five-year mean and the lever is sensitised end to end</t>
-        </is>
-      </c>
-    </row>
-    <row r="163" ht="100" customHeight="1">
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="170" customHeight="1">
       <c r="A163" s="7" t="inlineStr">
         <is>
           <t>Volume growth — Waste, 2027E</t>
@@ -40149,11 +40149,11 @@
       </c>
       <c r="E163" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 (gas oil -8.3% a year, naphtha -7.4%, fuel oil -6.4%, heavy fuel oil -28.2%; only wax +1.1% and LPG +1.7% grew). FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case reverts toward the five-year mean and the lever is sensitised end to end</t>
-        </is>
-      </c>
-    </row>
-    <row r="164" ht="100" customHeight="1">
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="170" customHeight="1">
       <c r="A164" s="7" t="inlineStr">
         <is>
           <t>Volume growth — Waste, 2028E</t>
@@ -40174,11 +40174,11 @@
       </c>
       <c r="E164" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 (gas oil -8.3% a year, naphtha -7.4%, fuel oil -6.4%, heavy fuel oil -28.2%; only wax +1.1% and LPG +1.7% grew). FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case reverts toward the five-year mean and the lever is sensitised end to end</t>
-        </is>
-      </c>
-    </row>
-    <row r="165" ht="100" customHeight="1">
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="170" customHeight="1">
       <c r="A165" s="7" t="inlineStr">
         <is>
           <t>Volume growth — Waste, 2029E</t>
@@ -40199,11 +40199,11 @@
       </c>
       <c r="E165" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 (gas oil -8.3% a year, naphtha -7.4%, fuel oil -6.4%, heavy fuel oil -28.2%; only wax +1.1% and LPG +1.7% grew). FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case reverts toward the five-year mean and the lever is sensitised end to end</t>
-        </is>
-      </c>
-    </row>
-    <row r="166" ht="100" customHeight="1">
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="170" customHeight="1">
       <c r="A166" s="7" t="inlineStr">
         <is>
           <t>Volume growth — Waste, 2030E</t>
@@ -40224,7 +40224,7 @@
       </c>
       <c r="E166" s="4" t="inlineStr">
         <is>
-          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 (gas oil -8.3% a year, naphtha -7.4%, fuel oil -6.4%, heavy fuel oil -28.2%; only wax +1.1% and LPG +1.7% grew). FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case reverts toward the five-year mean and the lever is sensitised end to end</t>
+          <t>Volume growth by audited product line: FLAT, every line, every year. The previous edition grew every line (oils +4.5%, wax +7.0%, fuel oil +3.0% in year one) and justified the ranking from the value growth printed between two disclosed HALVES. The company's own audited annual record for FY2021-FY2025 says the opposite: total sales tonnage ran 1,492 / 1,548 / 1,449 / 1,433 / 1,262 thousand tonnes, a fall of 18.5% from the FY2022 peak, and six of the eight lines shrank over FY2022-FY2025 while wax and LPG grew. THE PER-LINE COMPOUND RATES ARE NO LONGER PRINTED [08-09-2026]. This note used to give four of them to a decimal place, and NOTHING IN THIS REPOSITORY CARRIES THE SERIES THEY COME FROM: the three committed filings are two December-2025 statements and one June-2025, note 14-A gives one half's tonnage by line with a value-only comparative, and FY2022 to FY2024 per-line tonnage is in filings this study does not hold. The prose check caught one of the four and the other three were unflagged rather than verified. Under SIGCM a figure this desk cannot source is a figure it does not print, so the DIRECTION survives — six lines down, two up, and that is what the argument needs — and the decimals go. The five annual totals above stand on the same footing and are ESCALATED rather than removed, because the bear case is anchored to them. FLAT IS NOT A NEUTRAL ASSUMPTION HERE, IT IS ALREADY THE OPTIMISTIC ONE: the base year is the transition half annualised at 1,616 thousand tonnes, which is 12.5% ABOVE the five-year mean of 1,437 and above every full year in the record. Holding it flat assumes the rebound printed in one half persists. The bear case cuts tonnage harder than that mean requires and the lever is sensitised end to end</t>
         </is>
       </c>
     </row>
@@ -40447,7 +40447,7 @@
         </is>
       </c>
       <c r="B176" s="28" t="n">
-        <v>0.908</v>
+        <v>0.9063464869078695</v>
       </c>
       <c r="C176" s="7" t="inlineStr">
         <is>
@@ -40456,12 +40456,12 @@
       </c>
       <c r="D176" s="7" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="E176" s="4" t="inlineStr">
         <is>
-          <t>Own-stock tier-1 regression, AMOC weekly log-returns against the EGX30 — the published index of the exchange AMOC is listed on, series as of 22 July 2026. R-squared 0.259, n = 253, standard error 0.165, 90% confidence interval [0.637, 1.179], Blume cross-check 0.939. Passes the usability gate. THIS REPLACES the previous edition's 0.9405, which was regressed against a 33-name equal-weight composite of the covered Egyptian names — a coverage artefact rather than a market, and a source-integrity failure whatever number it produced. The correction is small on this name, -3.5% on beta and under a percent on fair value; it is made because the provenance was wrong, not because the answer was</t>
+          <t>Own-stock tier-1 regression, AMOC weekly log-returns against raw_indices/EG/EGX30.csv — the published index of the exchange AMOC is listed on, series as of 2026-09-08, resolved by beta_regression.own_stock_beta() rather than hand-rolled. R-squared 0.236, n = 256, standard error 0.175, 90% confidence interval [0.619, 1.193]. Passes the usability gate. THIS REPLACES the previous edition's 0.9405, which was regressed against a 33-name equal-weight composite of the covered Egyptian names — a coverage artefact rather than a market, and a source-integrity failure whatever number it produced. The correction is small on this name and it is made because the provenance was wrong, not because the answer was.</t>
         </is>
       </c>
     </row>
